--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -2895,38 +2895,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073064</v>
+        <v>129079151</v>
       </c>
       <c r="B22" t="n">
-        <v>100839</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488441</v>
+        <v>488670</v>
       </c>
       <c r="R22" t="n">
-        <v>7014545</v>
+        <v>7014411</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,6 +2973,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2985,6 +2990,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3002,38 +3027,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129079151</v>
+        <v>129073064</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>100839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3042,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488670</v>
+        <v>488441</v>
       </c>
       <c r="R23" t="n">
-        <v>7014411</v>
+        <v>7014545</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3080,11 +3105,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3097,26 +3117,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -5899,48 +5899,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080537</v>
+        <v>129077994</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>100839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488632</v>
+        <v>488544</v>
       </c>
       <c r="R47" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5972,11 +5977,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5989,26 +5989,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6026,7 +6006,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129072070</v>
+        <v>129080537</v>
       </c>
       <c r="B48" t="n">
         <v>79034</v>
@@ -6061,10 +6041,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488455</v>
+        <v>488632</v>
       </c>
       <c r="R48" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -6097,6 +6077,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6148,10 +6133,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129076866</v>
+        <v>129072070</v>
       </c>
       <c r="B49" t="n">
-        <v>91805</v>
+        <v>79034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6159,42 +6144,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488575</v>
+        <v>488455</v>
       </c>
       <c r="R49" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6226,11 +6206,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6257,12 +6232,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6280,38 +6255,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129077994</v>
+        <v>129076866</v>
       </c>
       <c r="B50" t="n">
-        <v>100839</v>
+        <v>91805</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6320,13 +6295,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488544</v>
+        <v>488575</v>
       </c>
       <c r="R50" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6358,6 +6333,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6370,6 +6350,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6387,53 +6387,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129072360</v>
+        <v>129070117</v>
       </c>
       <c r="B51" t="n">
-        <v>100839</v>
+        <v>79034</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488465</v>
+        <v>488317</v>
       </c>
       <c r="R51" t="n">
-        <v>7014498</v>
+        <v>7014450</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6460,11 +6455,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I gammal granskog med gott om död ved.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6477,6 +6487,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6494,48 +6524,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129070117</v>
+        <v>129081155</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488317</v>
+        <v>488569</v>
       </c>
       <c r="R52" t="n">
-        <v>7014450</v>
+        <v>7014529</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6562,24 +6597,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6598,22 +6623,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6631,10 +6656,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129081155</v>
+        <v>129072360</v>
       </c>
       <c r="B53" t="n">
-        <v>80175</v>
+        <v>100839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6642,27 +6667,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6671,10 +6696,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488569</v>
+        <v>488465</v>
       </c>
       <c r="R53" t="n">
-        <v>7014529</v>
+        <v>7014498</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -6709,11 +6734,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6726,26 +6746,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8315,38 +8315,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129074640</v>
+        <v>129073694</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>100839</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8355,13 +8355,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488472</v>
+        <v>488426</v>
       </c>
       <c r="R66" t="n">
-        <v>7014599</v>
+        <v>7014494</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8393,11 +8393,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8410,26 +8405,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8447,43 +8422,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129078537</v>
+        <v>129072652</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>100839</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8492,13 +8462,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488573</v>
+        <v>488514</v>
       </c>
       <c r="R67" t="n">
-        <v>7014399</v>
+        <v>7014547</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8530,11 +8500,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8547,26 +8512,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8584,7 +8529,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129079063</v>
+        <v>129074640</v>
       </c>
       <c r="B68" t="n">
         <v>57723</v>
@@ -8624,13 +8569,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488655</v>
+        <v>488472</v>
       </c>
       <c r="R68" t="n">
-        <v>7014417</v>
+        <v>7014599</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8664,7 +8609,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8716,38 +8661,43 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129078147</v>
+        <v>129078537</v>
       </c>
       <c r="B69" t="n">
-        <v>103173</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8756,13 +8706,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488557</v>
+        <v>488573</v>
       </c>
       <c r="R69" t="n">
-        <v>7014445</v>
+        <v>7014399</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8789,19 +8739,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8816,6 +8761,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8833,38 +8798,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129073694</v>
+        <v>129079063</v>
       </c>
       <c r="B70" t="n">
-        <v>100839</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8873,10 +8838,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488426</v>
+        <v>488655</v>
       </c>
       <c r="R70" t="n">
-        <v>7014494</v>
+        <v>7014417</v>
       </c>
       <c r="S70" t="n">
         <v>11</v>
@@ -8911,6 +8876,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8923,6 +8893,26 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8940,10 +8930,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129072652</v>
+        <v>129078147</v>
       </c>
       <c r="B71" t="n">
-        <v>100839</v>
+        <v>103173</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8951,27 +8941,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8980,13 +8970,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488514</v>
+        <v>488557</v>
       </c>
       <c r="R71" t="n">
-        <v>7014547</v>
+        <v>7014445</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9013,9 +9003,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,38 +2895,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129079151</v>
+        <v>129073064</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>100844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488670</v>
+        <v>488441</v>
       </c>
       <c r="R22" t="n">
-        <v>7014411</v>
+        <v>7014545</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,11 +2973,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2990,26 +2985,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,38 +3002,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129073064</v>
+        <v>129079151</v>
       </c>
       <c r="B23" t="n">
-        <v>100839</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3067,13 +3042,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488441</v>
+        <v>488670</v>
       </c>
       <c r="R23" t="n">
-        <v>7014545</v>
+        <v>7014411</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3105,6 +3080,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3117,6 +3097,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3256,43 +3256,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129072249</v>
+        <v>129075203</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>100844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3301,13 +3296,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488459</v>
+        <v>488533</v>
       </c>
       <c r="R25" t="n">
-        <v>7014467</v>
+        <v>7014663</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3339,11 +3334,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3356,26 +3346,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3393,38 +3363,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129071736</v>
+        <v>129072249</v>
       </c>
       <c r="B26" t="n">
-        <v>100839</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3433,13 +3408,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488410</v>
+        <v>488459</v>
       </c>
       <c r="R26" t="n">
-        <v>7014448</v>
+        <v>7014467</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3471,6 +3446,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3483,6 +3463,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3500,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129075203</v>
+        <v>129071736</v>
       </c>
       <c r="B27" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,13 +3540,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488533</v>
+        <v>488410</v>
       </c>
       <c r="R27" t="n">
-        <v>7014663</v>
+        <v>7014448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>129077703</v>
       </c>
       <c r="B28" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3749,53 +3749,58 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129078582</v>
+        <v>129073330</v>
       </c>
       <c r="B29" t="n">
-        <v>91975</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488570</v>
+        <v>488408</v>
       </c>
       <c r="R29" t="n">
-        <v>7014409</v>
+        <v>7014549</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3827,6 +3832,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3853,12 +3863,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3876,58 +3886,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129073330</v>
+        <v>129078582</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>91978</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488408</v>
+        <v>488570</v>
       </c>
       <c r="R30" t="n">
-        <v>7014549</v>
+        <v>7014409</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3959,11 +3964,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3990,12 +3990,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4013,48 +4013,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129080078</v>
+        <v>129078041</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>98990</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488760</v>
+        <v>488550</v>
       </c>
       <c r="R31" t="n">
-        <v>7014511</v>
+        <v>7014460</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4098,26 +4103,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4135,7 +4120,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129079878</v>
+        <v>129080078</v>
       </c>
       <c r="B32" t="n">
         <v>79034</v>
@@ -4170,13 +4155,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488787</v>
+        <v>488760</v>
       </c>
       <c r="R32" t="n">
-        <v>7014483</v>
+        <v>7014511</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4257,10 +4242,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129081091</v>
+        <v>129079878</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,42 +4253,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488575</v>
+        <v>488787</v>
       </c>
       <c r="R33" t="n">
-        <v>7014525</v>
+        <v>7014483</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4335,11 +4315,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4356,22 +4331,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4389,10 +4364,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129071599</v>
+        <v>129081091</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,56 +4375,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488409</v>
+        <v>488575</v>
       </c>
       <c r="R34" t="n">
-        <v>7014470</v>
+        <v>7014525</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4476,24 +4437,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4508,6 +4459,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4525,53 +4496,67 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129078041</v>
+        <v>129071599</v>
       </c>
       <c r="B35" t="n">
-        <v>98985</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488550</v>
+        <v>488409</v>
       </c>
       <c r="R35" t="n">
-        <v>7014460</v>
+        <v>7014470</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4598,9 +4583,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4635,7 +4635,7 @@
         <v>129076105</v>
       </c>
       <c r="B36" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>129073989</v>
       </c>
       <c r="B37" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>129081210</v>
       </c>
       <c r="B38" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129074467</v>
       </c>
       <c r="B39" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129072614</v>
+        <v>129072477</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,34 +5071,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488504</v>
+        <v>488495</v>
       </c>
       <c r="R40" t="n">
-        <v>7014520</v>
+        <v>7014499</v>
       </c>
       <c r="S40" t="n">
         <v>8</v>
@@ -5135,7 +5140,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5164,12 +5169,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5187,48 +5192,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129072008</v>
+        <v>129074733</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>100844</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488442</v>
+        <v>488496</v>
       </c>
       <c r="R41" t="n">
-        <v>7014464</v>
+        <v>7014610</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5272,26 +5282,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5309,10 +5299,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129072477</v>
+        <v>129072614</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5320,39 +5310,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488495</v>
+        <v>488504</v>
       </c>
       <c r="R42" t="n">
-        <v>7014499</v>
+        <v>7014520</v>
       </c>
       <c r="S42" t="n">
         <v>8</v>
@@ -5389,7 +5374,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5418,12 +5403,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5441,53 +5426,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129074733</v>
+        <v>129072008</v>
       </c>
       <c r="B43" t="n">
-        <v>100839</v>
+        <v>79034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488496</v>
+        <v>488442</v>
       </c>
       <c r="R43" t="n">
-        <v>7014610</v>
+        <v>7014464</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5531,6 +5511,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5795,7 +5795,7 @@
         <v>129073539</v>
       </c>
       <c r="B46" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5899,38 +5899,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129077994</v>
+        <v>129076866</v>
       </c>
       <c r="B47" t="n">
-        <v>100839</v>
+        <v>91808</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5939,13 +5939,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488544</v>
+        <v>488575</v>
       </c>
       <c r="R47" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5977,6 +5977,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5989,6 +5994,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6255,38 +6280,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129076866</v>
+        <v>129077994</v>
       </c>
       <c r="B50" t="n">
-        <v>91805</v>
+        <v>100844</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6295,13 +6320,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488575</v>
+        <v>488544</v>
       </c>
       <c r="R50" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6333,11 +6358,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6350,26 +6370,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6387,48 +6387,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129070117</v>
+        <v>129081155</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488317</v>
+        <v>488569</v>
       </c>
       <c r="R51" t="n">
-        <v>7014450</v>
+        <v>7014529</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6455,24 +6460,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6491,22 +6486,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6524,10 +6519,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129081155</v>
+        <v>129072360</v>
       </c>
       <c r="B52" t="n">
-        <v>80175</v>
+        <v>100844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,27 +6530,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6564,10 +6559,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488569</v>
+        <v>488465</v>
       </c>
       <c r="R52" t="n">
-        <v>7014529</v>
+        <v>7014498</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -6602,11 +6597,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6619,26 +6609,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6656,53 +6626,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129072360</v>
+        <v>129070117</v>
       </c>
       <c r="B53" t="n">
-        <v>100839</v>
+        <v>79034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488465</v>
+        <v>488317</v>
       </c>
       <c r="R53" t="n">
-        <v>7014498</v>
+        <v>7014450</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6729,11 +6694,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>I gammal granskog med gott om död ved.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6746,6 +6726,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129071884</v>
+        <v>129074346</v>
       </c>
       <c r="B55" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,42 +6911,47 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488391</v>
+        <v>488392</v>
       </c>
       <c r="R55" t="n">
-        <v>7014430</v>
+        <v>7014675</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6973,14 +6978,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7009,12 +7019,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7032,32 +7042,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B56" t="n">
-        <v>91975</v>
+        <v>91808</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7072,10 +7082,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R56" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -7108,6 +7118,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7159,58 +7174,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129074346</v>
+        <v>129071923</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>91978</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488392</v>
+        <v>488400</v>
       </c>
       <c r="R57" t="n">
-        <v>7014675</v>
+        <v>7014435</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7237,21 +7247,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7278,12 +7278,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7304,7 +7304,7 @@
         <v>129077981</v>
       </c>
       <c r="B58" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7432,53 +7432,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B59" t="n">
-        <v>92218</v>
+        <v>79034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R59" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7536,12 +7531,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7559,48 +7554,67 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129076063</v>
+        <v>129074868</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>98555</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>219795</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488532</v>
+        <v>488487</v>
       </c>
       <c r="R60" t="n">
-        <v>7014618</v>
+        <v>7014620</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7627,11 +7641,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2 plantor med fröställningar inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7644,26 +7673,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7681,10 +7690,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129074868</v>
+        <v>129074080</v>
       </c>
       <c r="B61" t="n">
-        <v>98550</v>
+        <v>92223</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7692,41 +7701,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219795</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7735,10 +7730,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488487</v>
+        <v>488394</v>
       </c>
       <c r="R61" t="n">
-        <v>7014620</v>
+        <v>7014593</v>
       </c>
       <c r="S61" t="n">
         <v>8</v>
@@ -7768,26 +7763,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>2 plantor med fröställningar inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7800,6 +7780,26 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8069,7 +8069,7 @@
         <v>129070439</v>
       </c>
       <c r="B64" t="n">
-        <v>103173</v>
+        <v>103178</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>129073694</v>
       </c>
       <c r="B66" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>129072652</v>
       </c>
       <c r="B67" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8529,38 +8529,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129074640</v>
+        <v>129078147</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>103178</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8569,13 +8569,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488472</v>
+        <v>488557</v>
       </c>
       <c r="R68" t="n">
-        <v>7014599</v>
+        <v>7014445</v>
       </c>
       <c r="S68" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8602,14 +8602,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8624,26 +8629,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8661,7 +8646,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129078537</v>
+        <v>129074640</v>
       </c>
       <c r="B69" t="n">
         <v>57723</v>
@@ -8695,24 +8680,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488573</v>
+        <v>488472</v>
       </c>
       <c r="R69" t="n">
-        <v>7014399</v>
+        <v>7014599</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8746,7 +8726,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8775,12 +8755,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8798,7 +8778,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129079063</v>
+        <v>129078537</v>
       </c>
       <c r="B70" t="n">
         <v>57723</v>
@@ -8832,19 +8812,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488655</v>
+        <v>488573</v>
       </c>
       <c r="R70" t="n">
-        <v>7014417</v>
+        <v>7014399</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8878,7 +8863,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8907,12 +8892,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8930,38 +8915,38 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129078147</v>
+        <v>129079063</v>
       </c>
       <c r="B71" t="n">
-        <v>103173</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8970,13 +8955,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488557</v>
+        <v>488655</v>
       </c>
       <c r="R71" t="n">
-        <v>7014445</v>
+        <v>7014417</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9003,19 +8988,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9030,6 +9010,26 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9182,7 +9182,7 @@
         <v>129077294</v>
       </c>
       <c r="B73" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129072984</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129076254</v>
+        <v>129079967</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488581</v>
+        <v>488745</v>
       </c>
       <c r="R14" t="n">
-        <v>7014597</v>
+        <v>7014497</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,11 +1982,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2003,12 +1998,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2018,7 +2013,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2036,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129080431</v>
+        <v>129074228</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,37 +2042,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488667</v>
+        <v>488431</v>
       </c>
       <c r="R15" t="n">
-        <v>7014453</v>
+        <v>7014633</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2104,11 +2109,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2135,12 +2155,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2158,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129074673</v>
+        <v>129076254</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,13 +2213,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488470</v>
+        <v>488581</v>
       </c>
       <c r="R16" t="n">
-        <v>7014593</v>
+        <v>7014597</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,6 +2251,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2247,12 +2272,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -2262,7 +2287,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2280,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079967</v>
+        <v>129080431</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488745</v>
+        <v>488667</v>
       </c>
       <c r="R17" t="n">
-        <v>7014497</v>
+        <v>7014453</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074228</v>
+        <v>129074673</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,47 +2438,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488431</v>
+        <v>488470</v>
       </c>
       <c r="R18" t="n">
-        <v>7014633</v>
+        <v>7014593</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2480,26 +2495,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2552,7 +2552,7 @@
         <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>129081134</v>
       </c>
       <c r="B21" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,38 +2895,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129073064</v>
+        <v>129079151</v>
       </c>
       <c r="B22" t="n">
-        <v>100844</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488441</v>
+        <v>488670</v>
       </c>
       <c r="R22" t="n">
-        <v>7014545</v>
+        <v>7014411</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,6 +2973,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2985,6 +2990,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3002,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129079151</v>
+        <v>129076465</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,39 +3038,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488670</v>
+        <v>488543</v>
       </c>
       <c r="R23" t="n">
-        <v>7014411</v>
+        <v>7014684</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3080,11 +3100,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3101,22 +3116,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3134,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129076465</v>
+        <v>129072249</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,37 +3160,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488543</v>
+        <v>488459</v>
       </c>
       <c r="R24" t="n">
-        <v>7014684</v>
+        <v>7014467</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3207,6 +3232,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3223,22 +3253,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3256,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129075203</v>
+        <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,13 +3326,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488533</v>
+        <v>488410</v>
       </c>
       <c r="R25" t="n">
-        <v>7014663</v>
+        <v>7014448</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,43 +3393,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129072249</v>
+        <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3408,13 +3433,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488459</v>
+        <v>488533</v>
       </c>
       <c r="R26" t="n">
-        <v>7014467</v>
+        <v>7014663</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,11 +3471,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3463,26 +3483,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3500,38 +3500,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129071736</v>
+        <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>100844</v>
+        <v>91981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488410</v>
+        <v>488529</v>
       </c>
       <c r="R27" t="n">
-        <v>7014448</v>
+        <v>7014483</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -3573,11 +3573,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikliga mängder liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3590,6 +3605,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3607,53 +3642,58 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129077703</v>
+        <v>129073330</v>
       </c>
       <c r="B28" t="n">
-        <v>91978</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488529</v>
+        <v>488408</v>
       </c>
       <c r="R28" t="n">
-        <v>7014483</v>
+        <v>7014549</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3680,24 +3720,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikliga mängder liggande död ved på fyndplatsen.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,12 +3756,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3749,58 +3779,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129073330</v>
+        <v>129078582</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488408</v>
+        <v>488570</v>
       </c>
       <c r="R29" t="n">
-        <v>7014549</v>
+        <v>7014409</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3832,11 +3857,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3863,12 +3883,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3886,53 +3906,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129078582</v>
+        <v>129079878</v>
       </c>
       <c r="B30" t="n">
-        <v>91978</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488570</v>
+        <v>488787</v>
       </c>
       <c r="R30" t="n">
-        <v>7014409</v>
+        <v>7014483</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3990,12 +4005,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4016,7 +4031,7 @@
         <v>129078041</v>
       </c>
       <c r="B31" t="n">
-        <v>98990</v>
+        <v>98993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,10 +4135,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129080078</v>
+        <v>129081091</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>80141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4131,37 +4146,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488760</v>
+        <v>488575</v>
       </c>
       <c r="R32" t="n">
-        <v>7014511</v>
+        <v>7014525</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4193,6 +4213,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4209,22 +4234,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4242,10 +4267,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129079878</v>
+        <v>129080078</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,13 +4302,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488787</v>
+        <v>488760</v>
       </c>
       <c r="R33" t="n">
-        <v>7014483</v>
+        <v>7014511</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4364,10 +4389,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129081091</v>
+        <v>129071599</v>
       </c>
       <c r="B34" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4375,42 +4400,56 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488575</v>
+        <v>488409</v>
       </c>
       <c r="R34" t="n">
-        <v>7014525</v>
+        <v>7014470</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4437,14 +4476,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4459,26 +4508,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4496,64 +4525,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129071599</v>
+        <v>129076105</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488409</v>
+        <v>488531</v>
       </c>
       <c r="R35" t="n">
-        <v>7014470</v>
+        <v>7014566</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4583,24 +4598,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4632,10 +4632,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129076105</v>
+        <v>129073989</v>
       </c>
       <c r="B36" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488531</v>
+        <v>488436</v>
       </c>
       <c r="R36" t="n">
-        <v>7014566</v>
+        <v>7014587</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129073989</v>
+        <v>129081210</v>
       </c>
       <c r="B37" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488436</v>
+        <v>488580</v>
       </c>
       <c r="R37" t="n">
-        <v>7014587</v>
+        <v>7014585</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129081210</v>
+        <v>129074467</v>
       </c>
       <c r="B38" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488580</v>
+        <v>488447</v>
       </c>
       <c r="R38" t="n">
-        <v>7014585</v>
+        <v>7014717</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4953,38 +4953,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129074467</v>
+        <v>129072477</v>
       </c>
       <c r="B39" t="n">
-        <v>100844</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488447</v>
+        <v>488495</v>
       </c>
       <c r="R39" t="n">
-        <v>7014717</v>
+        <v>7014499</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5031,6 +5031,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5043,6 +5048,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5060,38 +5085,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129072477</v>
+        <v>129074733</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5100,13 +5125,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488495</v>
+        <v>488496</v>
       </c>
       <c r="R40" t="n">
-        <v>7014499</v>
+        <v>7014610</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5138,11 +5163,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5155,26 +5175,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5192,53 +5192,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129074733</v>
+        <v>129072614</v>
       </c>
       <c r="B41" t="n">
-        <v>100844</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488496</v>
+        <v>488504</v>
       </c>
       <c r="R41" t="n">
-        <v>7014610</v>
+        <v>7014520</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5270,6 +5265,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5282,6 +5282,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5299,10 +5319,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129072614</v>
+        <v>129072008</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5334,13 +5354,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488504</v>
+        <v>488442</v>
       </c>
       <c r="R42" t="n">
-        <v>7014520</v>
+        <v>7014464</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5370,11 +5390,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5426,48 +5441,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129072008</v>
+        <v>129073539</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>100847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488442</v>
+        <v>488418</v>
       </c>
       <c r="R43" t="n">
-        <v>7014464</v>
+        <v>7014546</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5511,26 +5531,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5551,7 +5551,7 @@
         <v>129076722</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>129076936</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5792,10 +5792,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129073539</v>
+        <v>129077994</v>
       </c>
       <c r="B46" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488418</v>
+        <v>488544</v>
       </c>
       <c r="R46" t="n">
-        <v>7014546</v>
+        <v>7014457</v>
       </c>
       <c r="S46" t="n">
         <v>8</v>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129076866</v>
+        <v>129080537</v>
       </c>
       <c r="B47" t="n">
-        <v>91808</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5910,42 +5910,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488575</v>
+        <v>488632</v>
       </c>
       <c r="R47" t="n">
-        <v>7014596</v>
+        <v>7014478</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5979,7 +5974,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6008,12 +6003,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6031,10 +6026,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129080537</v>
+        <v>129072070</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6066,10 +6061,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488632</v>
+        <v>488455</v>
       </c>
       <c r="R48" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -6102,11 +6097,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6158,10 +6148,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129072070</v>
+        <v>129076866</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>91811</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6169,37 +6159,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488455</v>
+        <v>488575</v>
       </c>
       <c r="R49" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6231,6 +6226,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129077994</v>
+        <v>129072360</v>
       </c>
       <c r="B50" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488544</v>
+        <v>488465</v>
       </c>
       <c r="R50" t="n">
-        <v>7014457</v>
+        <v>7014498</v>
       </c>
       <c r="S50" t="n">
         <v>8</v>
@@ -6387,53 +6387,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129081155</v>
+        <v>129070117</v>
       </c>
       <c r="B51" t="n">
-        <v>80175</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488569</v>
+        <v>488317</v>
       </c>
       <c r="R51" t="n">
-        <v>7014529</v>
+        <v>7014450</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6460,14 +6455,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
+          <t>I gammal granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6486,22 +6491,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6519,38 +6524,43 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129072360</v>
+        <v>129079479</v>
       </c>
       <c r="B52" t="n">
-        <v>100844</v>
+        <v>57723</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6559,13 +6569,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488465</v>
+        <v>488806</v>
       </c>
       <c r="R52" t="n">
-        <v>7014498</v>
+        <v>7014416</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6597,6 +6607,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6609,6 +6624,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6626,48 +6661,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129070117</v>
+        <v>129081155</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>80176</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488317</v>
+        <v>488569</v>
       </c>
       <c r="R53" t="n">
-        <v>7014450</v>
+        <v>7014529</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6694,24 +6734,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6730,22 +6760,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6763,43 +6793,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129079479</v>
+        <v>129071923</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6808,13 +6833,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488806</v>
+        <v>488400</v>
       </c>
       <c r="R54" t="n">
-        <v>7014416</v>
+        <v>7014435</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6846,11 +6871,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6877,12 +6897,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6900,10 +6920,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129074346</v>
+        <v>129071884</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6911,47 +6931,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488392</v>
+        <v>488391</v>
       </c>
       <c r="R55" t="n">
-        <v>7014675</v>
+        <v>7014430</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6978,19 +6993,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7019,12 +7029,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7042,38 +7052,47 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129071884</v>
+        <v>129077981</v>
       </c>
       <c r="B56" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7082,13 +7101,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488391</v>
+        <v>488516</v>
       </c>
       <c r="R56" t="n">
-        <v>7014430</v>
+        <v>7014462</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7115,14 +7134,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7137,26 +7166,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7174,32 +7183,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129071923</v>
+        <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>91978</v>
+        <v>92226</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7214,13 +7223,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488400</v>
+        <v>488394</v>
       </c>
       <c r="R57" t="n">
-        <v>7014435</v>
+        <v>7014593</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7278,12 +7287,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7301,62 +7310,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129077981</v>
+        <v>129076063</v>
       </c>
       <c r="B58" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488516</v>
+        <v>488532</v>
       </c>
       <c r="R58" t="n">
-        <v>7014462</v>
+        <v>7014618</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7383,26 +7378,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7415,6 +7395,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129076063</v>
+        <v>129073935</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7467,13 +7467,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488532</v>
+        <v>488409</v>
       </c>
       <c r="R59" t="n">
-        <v>7014618</v>
+        <v>7014521</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7554,47 +7554,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129074868</v>
+        <v>129073198</v>
       </c>
       <c r="B60" t="n">
-        <v>98555</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -7604,17 +7595,17 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488487</v>
+        <v>488422</v>
       </c>
       <c r="R60" t="n">
-        <v>7014620</v>
+        <v>7014530</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7641,24 +7632,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>2 plantor med fröställningar inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7673,6 +7654,16 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7690,10 +7681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129074080</v>
+        <v>129070439</v>
       </c>
       <c r="B61" t="n">
-        <v>92223</v>
+        <v>103181</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7701,27 +7692,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>222002</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7730,13 +7721,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488394</v>
+        <v>488363</v>
       </c>
       <c r="R61" t="n">
-        <v>7014593</v>
+        <v>7014442</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7763,11 +7754,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7780,26 +7786,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7817,10 +7803,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129073935</v>
+        <v>129076561</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7852,13 +7838,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488409</v>
+        <v>488553</v>
       </c>
       <c r="R62" t="n">
-        <v>7014521</v>
+        <v>7014682</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7888,6 +7874,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7939,7 +7930,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129073198</v>
+        <v>129074640</v>
       </c>
       <c r="B63" t="n">
         <v>57723</v>
@@ -7973,21 +7964,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488422</v>
+        <v>488472</v>
       </c>
       <c r="R63" t="n">
-        <v>7014530</v>
+        <v>7014599</v>
       </c>
       <c r="S63" t="n">
         <v>12</v>
@@ -8024,7 +8010,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8041,14 +8027,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8066,38 +8062,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129070439</v>
+        <v>129078537</v>
       </c>
       <c r="B64" t="n">
-        <v>103178</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8106,13 +8107,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488363</v>
+        <v>488573</v>
       </c>
       <c r="R64" t="n">
-        <v>7014442</v>
+        <v>7014399</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8139,24 +8140,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8171,6 +8162,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8188,10 +8199,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129076561</v>
+        <v>129079063</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8199,37 +8210,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488553</v>
+        <v>488655</v>
       </c>
       <c r="R65" t="n">
-        <v>7014682</v>
+        <v>7014417</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8263,7 +8279,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8292,12 +8308,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8318,7 +8334,7 @@
         <v>129073694</v>
       </c>
       <c r="B66" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8425,7 +8441,7 @@
         <v>129072652</v>
       </c>
       <c r="B67" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8532,7 +8548,7 @@
         <v>129078147</v>
       </c>
       <c r="B68" t="n">
-        <v>103178</v>
+        <v>103181</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8646,7 +8662,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129074640</v>
+        <v>129079226</v>
       </c>
       <c r="B69" t="n">
         <v>57723</v>
@@ -8686,13 +8702,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488472</v>
+        <v>488679</v>
       </c>
       <c r="R69" t="n">
-        <v>7014599</v>
+        <v>7014391</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8726,7 +8742,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8778,38 +8794,47 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129078537</v>
+        <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8823,13 +8848,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488573</v>
+        <v>488548</v>
       </c>
       <c r="R70" t="n">
-        <v>7014399</v>
+        <v>7014573</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8856,14 +8881,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8878,26 +8913,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8915,38 +8930,38 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129079063</v>
+        <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8955,13 +8970,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488655</v>
+        <v>488441</v>
       </c>
       <c r="R71" t="n">
-        <v>7014417</v>
+        <v>7014545</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8993,11 +9008,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9010,26 +9020,6 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9047,53 +9037,63 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129079226</v>
+        <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>57723</v>
+        <v>92464</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488679</v>
+        <v>488614</v>
       </c>
       <c r="R72" t="n">
-        <v>7014391</v>
+        <v>7014406</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9125,43 +9125,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9179,47 +9155,40 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129077294</v>
+        <v>129074346</v>
       </c>
       <c r="B73" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -9229,17 +9198,17 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488548</v>
+        <v>488392</v>
       </c>
       <c r="R73" t="n">
-        <v>7014573</v>
+        <v>7014675</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9268,7 +9237,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9278,12 +9247,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9298,6 +9267,26 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9312,6 +9301,144 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129074868</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98558</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>488487</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7014620</v>
+      </c>
+      <c r="S74" t="n">
+        <v>8</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>3 plantor med fröställningar inom ca 2 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129057979</v>
+        <v>129057988</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488344</v>
+        <v>488339</v>
       </c>
       <c r="R2" t="n">
-        <v>7014426</v>
+        <v>7014419</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129057988</v>
+        <v>129057979</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488339</v>
+        <v>488344</v>
       </c>
       <c r="R3" t="n">
-        <v>7014419</v>
+        <v>7014426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -5792,53 +5792,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129077994</v>
+        <v>129080537</v>
       </c>
       <c r="B46" t="n">
-        <v>100847</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488544</v>
+        <v>488632</v>
       </c>
       <c r="R46" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5870,6 +5865,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5882,6 +5882,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5899,10 +5919,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129076866</v>
+        <v>129072070</v>
       </c>
       <c r="B47" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5910,42 +5930,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488575</v>
+        <v>488455</v>
       </c>
       <c r="R47" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5977,11 +5992,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6008,12 +6018,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6031,10 +6041,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129080537</v>
+        <v>129076866</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6042,37 +6052,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488632</v>
+        <v>488575</v>
       </c>
       <c r="R48" t="n">
-        <v>7014478</v>
+        <v>7014596</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6106,7 +6121,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6135,12 +6150,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6158,48 +6173,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129072070</v>
+        <v>129077994</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>100847</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488455</v>
+        <v>488544</v>
       </c>
       <c r="R49" t="n">
         <v>7014457</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6243,26 +6263,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6280,53 +6280,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129072360</v>
+        <v>129070117</v>
       </c>
       <c r="B50" t="n">
-        <v>100847</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488465</v>
+        <v>488317</v>
       </c>
       <c r="R50" t="n">
-        <v>7014498</v>
+        <v>7014450</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6353,11 +6348,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>I gammal granskog med gott om död ved.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6370,6 +6380,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6387,48 +6417,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129070117</v>
+        <v>129081155</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>80176</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488317</v>
+        <v>488569</v>
       </c>
       <c r="R51" t="n">
-        <v>7014450</v>
+        <v>7014529</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6455,24 +6490,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6491,22 +6516,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6524,10 +6549,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129081155</v>
+        <v>129072360</v>
       </c>
       <c r="B52" t="n">
-        <v>80176</v>
+        <v>100847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,27 +6560,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6564,10 +6589,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488569</v>
+        <v>488465</v>
       </c>
       <c r="R52" t="n">
-        <v>7014529</v>
+        <v>7014498</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -6602,11 +6627,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6619,26 +6639,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -9442,48 +9442,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215411</v>
+        <v>129213773</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>91981</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488525</v>
+        <v>488662</v>
       </c>
       <c r="R75" t="n">
-        <v>7014363</v>
+        <v>7014466</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9512,7 +9517,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9522,12 +9527,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129210501</v>
+        <v>129215411</v>
       </c>
       <c r="B76" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9590,47 +9590,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488472</v>
+        <v>488525</v>
       </c>
       <c r="R76" t="n">
-        <v>7014695</v>
+        <v>7014363</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9659,7 +9649,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9669,12 +9659,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9703,12 +9693,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9726,53 +9716,58 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129213773</v>
+        <v>129210501</v>
       </c>
       <c r="B77" t="n">
-        <v>91981</v>
+        <v>57723</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488662</v>
+        <v>488472</v>
       </c>
       <c r="R77" t="n">
-        <v>7014466</v>
+        <v>7014695</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9801,7 +9796,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9811,7 +9806,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10136,7 +10136,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129211802</v>
+        <v>129212598</v>
       </c>
       <c r="B80" t="n">
         <v>79035</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488591</v>
+        <v>488580</v>
       </c>
       <c r="R80" t="n">
-        <v>7014632</v>
+        <v>7014484</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10216,7 +10216,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10245,12 +10250,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10268,10 +10273,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129214932</v>
+        <v>129211802</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10279,42 +10284,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488526</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7014439</v>
+        <v>7014632</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10353,12 +10353,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10387,12 +10382,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10410,38 +10405,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129212656</v>
+        <v>129214932</v>
       </c>
       <c r="B82" t="n">
-        <v>100847</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10450,13 +10445,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488569</v>
+        <v>488526</v>
       </c>
       <c r="R82" t="n">
-        <v>7014485</v>
+        <v>7014439</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10485,7 +10480,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10495,7 +10490,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10510,6 +10510,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10527,45 +10547,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129212598</v>
+        <v>129212656</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>100847</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488580</v>
+        <v>488569</v>
       </c>
       <c r="R83" t="n">
-        <v>7014484</v>
+        <v>7014485</v>
       </c>
       <c r="S83" t="n">
         <v>9</v>
@@ -10597,7 +10622,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10607,12 +10632,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10627,26 +10647,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11294,38 +11294,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129214590</v>
+        <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>98993</v>
+        <v>91544</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11334,10 +11334,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488566</v>
+        <v>488495</v>
       </c>
       <c r="R89" t="n">
-        <v>7014423</v>
+        <v>7014661</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11394,6 +11394,26 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11523,10 +11543,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129209204</v>
+        <v>129215504</v>
       </c>
       <c r="B91" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11534,42 +11554,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488495</v>
+        <v>488457</v>
       </c>
       <c r="R91" t="n">
-        <v>7014661</v>
+        <v>7014436</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11598,7 +11613,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11608,7 +11623,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11623,26 +11638,6 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11660,10 +11655,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129213105</v>
+        <v>129214590</v>
       </c>
       <c r="B92" t="n">
-        <v>100847</v>
+        <v>98993</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11671,27 +11666,27 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11700,10 +11695,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488627</v>
+        <v>488566</v>
       </c>
       <c r="R92" t="n">
-        <v>7014454</v>
+        <v>7014423</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11735,7 +11730,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11745,7 +11740,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11913,48 +11908,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215504</v>
+        <v>129213105</v>
       </c>
       <c r="B94" t="n">
-        <v>79035</v>
+        <v>100847</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488457</v>
+        <v>488627</v>
       </c>
       <c r="R94" t="n">
-        <v>7014436</v>
+        <v>7014454</v>
       </c>
       <c r="S94" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12025,7 +12025,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129215050</v>
+        <v>129215435</v>
       </c>
       <c r="B95" t="n">
         <v>100847</v>
@@ -12065,13 +12065,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488488</v>
+        <v>488485</v>
       </c>
       <c r="R95" t="n">
-        <v>7014432</v>
+        <v>7014376</v>
       </c>
       <c r="S95" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12110,7 +12110,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12142,7 +12142,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129215435</v>
+        <v>129215050</v>
       </c>
       <c r="B96" t="n">
         <v>100847</v>
@@ -12182,13 +12182,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488485</v>
+        <v>488488</v>
       </c>
       <c r="R96" t="n">
-        <v>7014376</v>
+        <v>7014432</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13187,43 +13187,38 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129213886</v>
+        <v>129212827</v>
       </c>
       <c r="B104" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -13232,13 +13227,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488671</v>
+        <v>488535</v>
       </c>
       <c r="R104" t="n">
-        <v>7014435</v>
+        <v>7014455</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13267,7 +13262,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13277,12 +13272,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13311,12 +13301,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13334,10 +13324,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129211708</v>
+        <v>129213886</v>
       </c>
       <c r="B105" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13345,31 +13335,27 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -13383,13 +13369,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488586</v>
+        <v>488671</v>
       </c>
       <c r="R105" t="n">
-        <v>7014617</v>
+        <v>7014435</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13418,7 +13404,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13428,12 +13414,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Synobservation av 1 talltita i flerskiktad gammal granskog.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13448,6 +13434,26 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13465,50 +13471,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129209238</v>
+        <v>129213534</v>
       </c>
       <c r="B106" t="n">
-        <v>100847</v>
+        <v>79035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488489</v>
+        <v>488675</v>
       </c>
       <c r="R106" t="n">
-        <v>7014656</v>
+        <v>7014494</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13540,7 +13541,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13550,7 +13551,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13565,6 +13566,26 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13582,10 +13603,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129213534</v>
+        <v>129211708</v>
       </c>
       <c r="B107" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13593,34 +13614,48 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488675</v>
+        <v>488586</v>
       </c>
       <c r="R107" t="n">
-        <v>7014494</v>
+        <v>7014617</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13652,7 +13687,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13662,7 +13697,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 talltita i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13677,26 +13717,6 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13714,38 +13734,38 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129212827</v>
+        <v>129209238</v>
       </c>
       <c r="B108" t="n">
-        <v>91981</v>
+        <v>100847</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -13754,13 +13774,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488535</v>
+        <v>488489</v>
       </c>
       <c r="R108" t="n">
-        <v>7014455</v>
+        <v>7014656</v>
       </c>
       <c r="S108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13789,7 +13809,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13799,7 +13819,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13814,26 +13834,6 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13851,67 +13851,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129214838</v>
+        <v>129213440</v>
       </c>
       <c r="B109" t="n">
-        <v>98563</v>
+        <v>79035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488552</v>
+        <v>488638</v>
       </c>
       <c r="R109" t="n">
-        <v>7014410</v>
+        <v>7014529</v>
       </c>
       <c r="S109" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13940,7 +13921,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13950,12 +13931,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>1 planta med fröställning.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13970,6 +13946,26 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -13987,48 +13983,67 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129213440</v>
+        <v>129214838</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>98563</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488638</v>
+        <v>488552</v>
       </c>
       <c r="R110" t="n">
-        <v>7014529</v>
+        <v>7014410</v>
       </c>
       <c r="S110" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14057,7 +14072,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14067,7 +14082,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>1 planta med fröställning.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14082,26 +14102,6 @@
       <c r="AH110" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14535,38 +14535,43 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214896</v>
+        <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14575,13 +14580,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488525</v>
+        <v>488543</v>
       </c>
       <c r="R114" t="n">
-        <v>7014424</v>
+        <v>7014418</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14610,7 +14615,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14620,12 +14625,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14640,26 +14640,6 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14677,43 +14657,38 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B115" t="n">
-        <v>100847</v>
+        <v>57723</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14722,13 +14697,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R115" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14757,7 +14732,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14767,7 +14742,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14782,6 +14762,26 @@
       <c r="AH115" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14931,64 +14931,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129211241</v>
+        <v>129212678</v>
       </c>
       <c r="B117" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488551</v>
+        <v>488572</v>
       </c>
       <c r="R117" t="n">
-        <v>7014630</v>
+        <v>7014469</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15020,7 +15001,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15030,12 +15011,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15050,6 +15026,26 @@
       <c r="AH117" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15067,7 +15063,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129211912</v>
+        <v>129211241</v>
       </c>
       <c r="B118" t="n">
         <v>98659</v>
@@ -15097,7 +15093,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -15121,10 +15117,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488586</v>
+        <v>488551</v>
       </c>
       <c r="R118" t="n">
-        <v>7014626</v>
+        <v>7014630</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15156,7 +15152,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15166,12 +15162,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15203,45 +15199,64 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129212678</v>
+        <v>129211912</v>
       </c>
       <c r="B119" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488572</v>
+        <v>488586</v>
       </c>
       <c r="R119" t="n">
-        <v>7014469</v>
+        <v>7014626</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15273,7 +15288,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15283,7 +15298,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15298,26 +15318,6 @@
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15335,38 +15335,38 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129210698</v>
+        <v>129214468</v>
       </c>
       <c r="B120" t="n">
-        <v>92464</v>
+        <v>57723</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488475</v>
+        <v>488595</v>
       </c>
       <c r="R120" t="n">
-        <v>7014707</v>
+        <v>7014471</v>
       </c>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15420,7 +15420,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15435,6 +15440,26 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15452,38 +15477,38 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129214468</v>
+        <v>129210698</v>
       </c>
       <c r="B121" t="n">
-        <v>57723</v>
+        <v>92464</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -15492,13 +15517,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488595</v>
+        <v>488475</v>
       </c>
       <c r="R121" t="n">
-        <v>7014471</v>
+        <v>7014707</v>
       </c>
       <c r="S121" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15527,7 +15552,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15537,12 +15562,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15557,26 +15577,6 @@
       <c r="AH121" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129057988</v>
+        <v>129057979</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488339</v>
+        <v>488344</v>
       </c>
       <c r="R2" t="n">
-        <v>7014419</v>
+        <v>7014426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129057979</v>
+        <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488344</v>
+        <v>488339</v>
       </c>
       <c r="R3" t="n">
-        <v>7014426</v>
+        <v>7014419</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129076254</v>
+        <v>129074228</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,37 +1920,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488581</v>
+        <v>488431</v>
       </c>
       <c r="R14" t="n">
-        <v>7014597</v>
+        <v>7014633</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,14 +1987,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,22 +2023,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2158,7 +2178,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129074673</v>
+        <v>129079967</v>
       </c>
       <c r="B16" t="n">
         <v>79035</v>
@@ -2193,13 +2213,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488470</v>
+        <v>488745</v>
       </c>
       <c r="R16" t="n">
-        <v>7014593</v>
+        <v>7014497</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079967</v>
+        <v>129074673</v>
       </c>
       <c r="B17" t="n">
         <v>79035</v>
@@ -2315,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488745</v>
+        <v>488470</v>
       </c>
       <c r="R17" t="n">
-        <v>7014497</v>
+        <v>7014593</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074228</v>
+        <v>129076254</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,47 +2433,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488431</v>
+        <v>488581</v>
       </c>
       <c r="R18" t="n">
-        <v>7014633</v>
+        <v>7014597</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2480,24 +2490,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,22 +2516,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129078715</v>
+        <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>100847</v>
+        <v>97530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,42 +2560,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488611</v>
+        <v>488522</v>
       </c>
       <c r="R19" t="n">
-        <v>7014397</v>
+        <v>7014485</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,6 +2620,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129077751</v>
+        <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>97530</v>
+        <v>100847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,37 +2667,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488522</v>
+        <v>488611</v>
       </c>
       <c r="R20" t="n">
-        <v>7014485</v>
+        <v>7014397</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2727,11 +2732,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3149,38 +3149,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129071736</v>
+        <v>129072249</v>
       </c>
       <c r="B24" t="n">
-        <v>100847</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3189,13 +3194,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488410</v>
+        <v>488459</v>
       </c>
       <c r="R24" t="n">
-        <v>7014448</v>
+        <v>7014467</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3227,6 +3232,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3239,6 +3249,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3256,7 +3286,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129075203</v>
+        <v>129071736</v>
       </c>
       <c r="B25" t="n">
         <v>100847</v>
@@ -3296,13 +3326,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488533</v>
+        <v>488410</v>
       </c>
       <c r="R25" t="n">
-        <v>7014663</v>
+        <v>7014448</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,43 +3393,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129072249</v>
+        <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3408,13 +3433,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488459</v>
+        <v>488533</v>
       </c>
       <c r="R26" t="n">
-        <v>7014467</v>
+        <v>7014663</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,11 +3471,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3463,26 +3483,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3642,53 +3642,58 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129078582</v>
+        <v>129073330</v>
       </c>
       <c r="B28" t="n">
-        <v>91981</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488570</v>
+        <v>488408</v>
       </c>
       <c r="R28" t="n">
-        <v>7014409</v>
+        <v>7014549</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3720,6 +3725,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3746,12 +3756,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3769,58 +3779,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129073330</v>
+        <v>129078582</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488408</v>
+        <v>488570</v>
       </c>
       <c r="R29" t="n">
-        <v>7014549</v>
+        <v>7014409</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3852,11 +3857,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129080078</v>
+        <v>129081091</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4053,37 +4053,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488760</v>
+        <v>488575</v>
       </c>
       <c r="R31" t="n">
-        <v>7014511</v>
+        <v>7014525</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4115,6 +4120,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4131,22 +4141,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4164,7 +4174,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129079878</v>
+        <v>129080078</v>
       </c>
       <c r="B32" t="n">
         <v>79035</v>
@@ -4199,13 +4209,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488787</v>
+        <v>488760</v>
       </c>
       <c r="R32" t="n">
-        <v>7014483</v>
+        <v>7014511</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4286,10 +4296,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129081091</v>
+        <v>129079878</v>
       </c>
       <c r="B33" t="n">
-        <v>80141</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,42 +4307,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488575</v>
+        <v>488787</v>
       </c>
       <c r="R33" t="n">
-        <v>7014525</v>
+        <v>7014483</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4364,11 +4369,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4385,22 +4385,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5441,53 +5441,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129073539</v>
+        <v>129076722</v>
       </c>
       <c r="B43" t="n">
-        <v>100847</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488418</v>
+        <v>488602</v>
       </c>
       <c r="R43" t="n">
-        <v>7014546</v>
+        <v>7014595</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5531,6 +5526,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5548,7 +5563,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129076722</v>
+        <v>129076936</v>
       </c>
       <c r="B44" t="n">
         <v>79035</v>
@@ -5583,13 +5598,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488602</v>
+        <v>488552</v>
       </c>
       <c r="R44" t="n">
-        <v>7014595</v>
+        <v>7014587</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5670,48 +5685,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129076936</v>
+        <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>100847</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488552</v>
+        <v>488418</v>
       </c>
       <c r="R45" t="n">
-        <v>7014587</v>
+        <v>7014546</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5755,26 +5775,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080537</v>
+        <v>129072070</v>
       </c>
       <c r="B46" t="n">
         <v>79035</v>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488632</v>
+        <v>488455</v>
       </c>
       <c r="R46" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -5863,11 +5863,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5919,48 +5914,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129072070</v>
+        <v>129077994</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>100847</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488455</v>
+        <v>488544</v>
       </c>
       <c r="R47" t="n">
         <v>7014457</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6004,26 +6004,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6173,53 +6153,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129077994</v>
+        <v>129080537</v>
       </c>
       <c r="B49" t="n">
-        <v>100847</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488544</v>
+        <v>488632</v>
       </c>
       <c r="R49" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6251,6 +6226,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6263,6 +6243,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6280,48 +6280,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129070117</v>
+        <v>129072360</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>100847</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488317</v>
+        <v>488465</v>
       </c>
       <c r="R50" t="n">
-        <v>7014450</v>
+        <v>7014498</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6348,26 +6353,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>I gammal granskog med gott om död ved.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6380,26 +6370,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6417,53 +6387,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129081155</v>
+        <v>129070117</v>
       </c>
       <c r="B51" t="n">
-        <v>80176</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488569</v>
+        <v>488317</v>
       </c>
       <c r="R51" t="n">
-        <v>7014529</v>
+        <v>7014450</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6490,14 +6455,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
+          <t>I gammal granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6516,22 +6491,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6549,10 +6524,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129072360</v>
+        <v>129081155</v>
       </c>
       <c r="B52" t="n">
-        <v>100847</v>
+        <v>80176</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6560,27 +6535,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6589,10 +6564,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488465</v>
+        <v>488569</v>
       </c>
       <c r="R52" t="n">
-        <v>7014498</v>
+        <v>7014529</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -6627,6 +6602,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6639,6 +6619,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6793,32 +6793,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129071884</v>
+        <v>129071923</v>
       </c>
       <c r="B54" t="n">
-        <v>91811</v>
+        <v>91981</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488391</v>
+        <v>488400</v>
       </c>
       <c r="R54" t="n">
-        <v>7014430</v>
+        <v>7014435</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -6869,11 +6869,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6925,32 +6920,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B55" t="n">
-        <v>91981</v>
+        <v>91811</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6965,10 +6960,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R55" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S55" t="n">
         <v>7</v>
@@ -7001,6 +6996,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7183,48 +7183,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>92226</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R57" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7282,12 +7287,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7305,53 +7310,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B58" t="n">
-        <v>92226</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R58" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129073935</v>
+        <v>129073198</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7443,37 +7443,47 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488409</v>
+        <v>488422</v>
       </c>
       <c r="R59" t="n">
-        <v>7014521</v>
+        <v>7014530</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7505,6 +7515,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7519,24 +7534,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7554,53 +7559,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129070439</v>
+        <v>129073935</v>
       </c>
       <c r="B60" t="n">
-        <v>103181</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488363</v>
+        <v>488409</v>
       </c>
       <c r="R60" t="n">
-        <v>7014442</v>
+        <v>7014521</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7627,26 +7627,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7659,6 +7644,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7676,58 +7681,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129073198</v>
+        <v>129070439</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>103181</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488422</v>
+        <v>488363</v>
       </c>
       <c r="R61" t="n">
-        <v>7014530</v>
+        <v>7014442</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7754,14 +7754,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7776,16 +7786,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129073694</v>
+        <v>129079063</v>
       </c>
       <c r="B63" t="n">
-        <v>100847</v>
+        <v>57723</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488426</v>
+        <v>488655</v>
       </c>
       <c r="R63" t="n">
-        <v>7014494</v>
+        <v>7014417</v>
       </c>
       <c r="S63" t="n">
         <v>11</v>
@@ -8008,6 +8008,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8020,6 +8025,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8037,7 +8062,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129072652</v>
+        <v>129073694</v>
       </c>
       <c r="B64" t="n">
         <v>100847</v>
@@ -8077,13 +8102,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488514</v>
+        <v>488426</v>
       </c>
       <c r="R64" t="n">
-        <v>7014547</v>
+        <v>7014494</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8144,10 +8169,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129078147</v>
+        <v>129072652</v>
       </c>
       <c r="B65" t="n">
-        <v>103181</v>
+        <v>100847</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8155,27 +8180,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8184,13 +8209,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488557</v>
+        <v>488514</v>
       </c>
       <c r="R65" t="n">
-        <v>7014445</v>
+        <v>7014547</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8217,19 +8242,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8261,38 +8276,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129074640</v>
+        <v>129078147</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>103181</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8301,13 +8316,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488472</v>
+        <v>488557</v>
       </c>
       <c r="R66" t="n">
-        <v>7014599</v>
+        <v>7014445</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8334,14 +8349,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8356,26 +8376,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8393,7 +8393,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129078537</v>
+        <v>129074640</v>
       </c>
       <c r="B67" t="n">
         <v>57723</v>
@@ -8427,24 +8427,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488573</v>
+        <v>488472</v>
       </c>
       <c r="R67" t="n">
-        <v>7014399</v>
+        <v>7014599</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8478,7 +8473,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8507,12 +8502,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8530,7 +8525,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129079063</v>
+        <v>129078537</v>
       </c>
       <c r="B68" t="n">
         <v>57723</v>
@@ -8564,19 +8559,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488655</v>
+        <v>488573</v>
       </c>
       <c r="R68" t="n">
-        <v>7014417</v>
+        <v>7014399</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8662,52 +8662,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129077294</v>
+        <v>129079226</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8716,13 +8702,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488548</v>
+        <v>488679</v>
       </c>
       <c r="R69" t="n">
-        <v>7014573</v>
+        <v>7014391</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8749,24 +8735,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8781,6 +8757,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8798,38 +8794,52 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129079226</v>
+        <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8838,13 +8848,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488679</v>
+        <v>488548</v>
       </c>
       <c r="R70" t="n">
-        <v>7014391</v>
+        <v>7014573</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8871,14 +8881,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8893,26 +8913,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129213773</v>
+        <v>129213412</v>
       </c>
       <c r="B75" t="n">
-        <v>91981</v>
+        <v>98659</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9453,27 +9453,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9482,13 +9496,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488662</v>
+        <v>488623</v>
       </c>
       <c r="R75" t="n">
-        <v>7014466</v>
+        <v>7014540</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9517,7 +9531,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9527,7 +9541,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9542,26 +9561,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9863,10 +9862,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129213412</v>
+        <v>129213773</v>
       </c>
       <c r="B78" t="n">
-        <v>98659</v>
+        <v>91981</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9874,41 +9873,27 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9917,13 +9902,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488623</v>
+        <v>488662</v>
       </c>
       <c r="R78" t="n">
-        <v>7014540</v>
+        <v>7014466</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9952,7 +9937,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9962,12 +9947,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9982,6 +9962,26 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11294,38 +11294,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129209204</v>
+        <v>129214590</v>
       </c>
       <c r="B89" t="n">
-        <v>91544</v>
+        <v>98993</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11334,10 +11334,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488495</v>
+        <v>488566</v>
       </c>
       <c r="R89" t="n">
-        <v>7014661</v>
+        <v>7014423</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11394,26 +11394,6 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11431,45 +11411,64 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215229</v>
+        <v>129211354</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488501</v>
+        <v>488586</v>
       </c>
       <c r="R90" t="n">
-        <v>7014416</v>
+        <v>7014612</v>
       </c>
       <c r="S90" t="n">
         <v>9</v>
@@ -11501,7 +11500,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11511,7 +11510,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11543,10 +11547,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215504</v>
+        <v>129209204</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11554,37 +11558,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488457</v>
+        <v>488495</v>
       </c>
       <c r="R91" t="n">
-        <v>7014436</v>
+        <v>7014661</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11613,7 +11622,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11623,7 +11632,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11638,6 +11647,26 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11655,53 +11684,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129214590</v>
+        <v>129215229</v>
       </c>
       <c r="B92" t="n">
-        <v>98993</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488566</v>
+        <v>488501</v>
       </c>
       <c r="R92" t="n">
-        <v>7014423</v>
+        <v>7014416</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11730,7 +11754,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11740,7 +11764,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11772,67 +11796,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129211354</v>
+        <v>129215504</v>
       </c>
       <c r="B93" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488586</v>
+        <v>488457</v>
       </c>
       <c r="R93" t="n">
-        <v>7014612</v>
+        <v>7014436</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11861,7 +11866,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11871,12 +11876,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12390,50 +12390,64 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129210843</v>
+        <v>129214807</v>
       </c>
       <c r="B98" t="n">
-        <v>100847</v>
+        <v>98659</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488496</v>
+        <v>488555</v>
       </c>
       <c r="R98" t="n">
-        <v>7014638</v>
+        <v>7014416</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12465,7 +12479,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12475,7 +12489,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12507,64 +12526,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129214807</v>
+        <v>129210843</v>
       </c>
       <c r="B99" t="n">
-        <v>98659</v>
+        <v>100847</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488555</v>
+        <v>488496</v>
       </c>
       <c r="R99" t="n">
-        <v>7014416</v>
+        <v>7014638</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -12596,7 +12601,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12606,12 +12611,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13324,43 +13324,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129213886</v>
+        <v>129209238</v>
       </c>
       <c r="B105" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -13369,13 +13364,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488671</v>
+        <v>488489</v>
       </c>
       <c r="R105" t="n">
-        <v>7014435</v>
+        <v>7014656</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13404,7 +13399,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13414,12 +13409,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13434,26 +13424,6 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13603,10 +13573,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129211708</v>
+        <v>129213886</v>
       </c>
       <c r="B107" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13614,31 +13584,27 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -13652,13 +13618,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488586</v>
+        <v>488671</v>
       </c>
       <c r="R107" t="n">
-        <v>7014617</v>
+        <v>7014435</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13687,7 +13653,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13697,12 +13663,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Synobservation av 1 talltita i flerskiktad gammal granskog.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13717,6 +13683,26 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13734,53 +13720,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129209238</v>
+        <v>129213440</v>
       </c>
       <c r="B108" t="n">
-        <v>100847</v>
+        <v>79035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488489</v>
+        <v>488638</v>
       </c>
       <c r="R108" t="n">
-        <v>7014656</v>
+        <v>7014529</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13809,7 +13790,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13819,7 +13800,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13834,6 +13815,26 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13851,48 +13852,67 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129213440</v>
+        <v>129214838</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>98563</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488638</v>
+        <v>488552</v>
       </c>
       <c r="R109" t="n">
-        <v>7014529</v>
+        <v>7014410</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13921,7 +13941,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13931,7 +13951,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>1 planta med fröställning.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13946,26 +13971,6 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -13983,67 +13988,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129214838</v>
+        <v>129213171</v>
       </c>
       <c r="B110" t="n">
-        <v>98563</v>
+        <v>79035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488552</v>
+        <v>488617</v>
       </c>
       <c r="R110" t="n">
-        <v>7014410</v>
+        <v>7014519</v>
       </c>
       <c r="S110" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -14072,7 +14058,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14082,12 +14068,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>1 planta med fröställning.</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14102,6 +14083,26 @@
       <c r="AH110" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14119,10 +14120,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129213171</v>
+        <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14130,37 +14131,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488617</v>
+        <v>488500</v>
       </c>
       <c r="R111" t="n">
-        <v>7014519</v>
+        <v>7014403</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -14189,7 +14195,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14199,7 +14205,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14228,12 +14234,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14251,10 +14257,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215256</v>
+        <v>129209979</v>
       </c>
       <c r="B112" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14262,27 +14268,32 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -14291,13 +14302,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488500</v>
+        <v>488422</v>
       </c>
       <c r="R112" t="n">
-        <v>7014403</v>
+        <v>7014672</v>
       </c>
       <c r="S112" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -14326,7 +14337,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14336,7 +14347,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran. Vissa ringhack bedöms vara strax över 5 år gamla.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14350,7 +14366,7 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -14365,12 +14381,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14388,38 +14404,38 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129209979</v>
+        <v>129214819</v>
       </c>
       <c r="B113" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -14433,13 +14449,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488422</v>
+        <v>488543</v>
       </c>
       <c r="R113" t="n">
-        <v>7014672</v>
+        <v>7014418</v>
       </c>
       <c r="S113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14468,7 +14484,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14478,12 +14494,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran. Vissa ringhack bedöms vara strax över 5 år gamla.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14497,27 +14508,7 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14535,43 +14526,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B114" t="n">
-        <v>100847</v>
+        <v>57723</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14580,13 +14566,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R114" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14615,7 +14601,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14625,7 +14611,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14640,6 +14631,26 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14657,10 +14668,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129214896</v>
+        <v>129214402</v>
       </c>
       <c r="B115" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14668,42 +14679,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488525</v>
+        <v>488614</v>
       </c>
       <c r="R115" t="n">
-        <v>7014424</v>
+        <v>7014448</v>
       </c>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14732,7 +14738,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14742,12 +14748,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14776,12 +14777,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -14799,7 +14800,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129214402</v>
+        <v>129212678</v>
       </c>
       <c r="B116" t="n">
         <v>79035</v>
@@ -14834,10 +14835,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488614</v>
+        <v>488572</v>
       </c>
       <c r="R116" t="n">
-        <v>7014448</v>
+        <v>7014469</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14869,7 +14870,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14879,7 +14880,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14931,45 +14932,64 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129212678</v>
+        <v>129211241</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488572</v>
+        <v>488551</v>
       </c>
       <c r="R117" t="n">
-        <v>7014469</v>
+        <v>7014630</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15001,7 +15021,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15011,7 +15031,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15026,26 +15051,6 @@
       <c r="AH117" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15063,7 +15068,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129211241</v>
+        <v>129211912</v>
       </c>
       <c r="B118" t="n">
         <v>98659</v>
@@ -15093,7 +15098,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -15117,10 +15122,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488551</v>
+        <v>488586</v>
       </c>
       <c r="R118" t="n">
-        <v>7014630</v>
+        <v>7014626</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15152,7 +15157,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15162,12 +15167,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15199,52 +15204,38 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129211912</v>
+        <v>129214468</v>
       </c>
       <c r="B119" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -15253,13 +15244,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488586</v>
+        <v>488595</v>
       </c>
       <c r="R119" t="n">
-        <v>7014626</v>
+        <v>7014471</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15288,7 +15279,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15298,12 +15289,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15318,6 +15309,26 @@
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15335,38 +15346,38 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129214468</v>
+        <v>129210698</v>
       </c>
       <c r="B120" t="n">
-        <v>57723</v>
+        <v>92464</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15375,13 +15386,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488595</v>
+        <v>488475</v>
       </c>
       <c r="R120" t="n">
-        <v>7014471</v>
+        <v>7014707</v>
       </c>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15410,7 +15421,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15420,12 +15431,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15440,26 +15446,6 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15477,53 +15463,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129210698</v>
+        <v>129209446</v>
       </c>
       <c r="B121" t="n">
-        <v>92464</v>
+        <v>79035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488475</v>
+        <v>488454</v>
       </c>
       <c r="R121" t="n">
-        <v>7014707</v>
+        <v>7014635</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15552,7 +15533,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15562,7 +15543,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15577,6 +15558,26 @@
       <c r="AH121" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15594,7 +15595,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129209446</v>
+        <v>129212992</v>
       </c>
       <c r="B122" t="n">
         <v>79035</v>
@@ -15629,10 +15630,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488454</v>
+        <v>488605</v>
       </c>
       <c r="R122" t="n">
-        <v>7014635</v>
+        <v>7014461</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15664,7 +15665,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15674,7 +15675,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15703,12 +15704,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15726,10 +15727,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129212992</v>
+        <v>129211708</v>
       </c>
       <c r="B123" t="n">
-        <v>79035</v>
+        <v>57885</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15737,34 +15738,54 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488605</v>
+        <v>488586</v>
       </c>
       <c r="R123" t="n">
-        <v>7014461</v>
+        <v>7014617</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15796,7 +15817,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15806,7 +15827,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 talltita i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15821,26 +15847,6 @@
       <c r="AH123" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129057979</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129057983</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129057978</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129057984</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129057976</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>129057982</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>129057975</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>129057981</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129057980</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129072984</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129074228</v>
+        <v>129076254</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,47 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488431</v>
+        <v>488581</v>
       </c>
       <c r="R14" t="n">
-        <v>7014633</v>
+        <v>7014597</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,24 +1977,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2023,22 +2003,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2059,7 +2039,7 @@
         <v>129080431</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129079967</v>
+        <v>129074673</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,13 +2193,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488745</v>
+        <v>488470</v>
       </c>
       <c r="R16" t="n">
-        <v>7014497</v>
+        <v>7014593</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074673</v>
+        <v>129079967</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488470</v>
+        <v>488745</v>
       </c>
       <c r="R17" t="n">
-        <v>7014593</v>
+        <v>7014497</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2422,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129076254</v>
+        <v>129074228</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,37 +2413,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488581</v>
+        <v>488431</v>
       </c>
       <c r="R18" t="n">
-        <v>7014597</v>
+        <v>7014633</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2490,14 +2480,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,22 +2516,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129077751</v>
+        <v>129078715</v>
       </c>
       <c r="B19" t="n">
-        <v>97530</v>
+        <v>100857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,37 +2560,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488522</v>
+        <v>488611</v>
       </c>
       <c r="R19" t="n">
-        <v>7014485</v>
+        <v>7014397</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,11 +2625,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129078715</v>
+        <v>129077751</v>
       </c>
       <c r="B20" t="n">
-        <v>100847</v>
+        <v>97540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,42 +2667,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488611</v>
+        <v>488522</v>
       </c>
       <c r="R20" t="n">
-        <v>7014397</v>
+        <v>7014485</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,6 +2727,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129081134</v>
+        <v>129079151</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,27 +2774,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488567</v>
+        <v>488670</v>
       </c>
       <c r="R21" t="n">
-        <v>7014534</v>
+        <v>7014411</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129079151</v>
+        <v>129081134</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,27 +2906,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488670</v>
+        <v>488567</v>
       </c>
       <c r="R22" t="n">
-        <v>7014411</v>
+        <v>7014534</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,22 +2994,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
         <v>129076465</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>129072249</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,58 +3642,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129073330</v>
+        <v>129078582</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>91988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488408</v>
+        <v>488570</v>
       </c>
       <c r="R28" t="n">
-        <v>7014549</v>
+        <v>7014409</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3725,11 +3720,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3756,12 +3746,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3779,53 +3769,58 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129078582</v>
+        <v>129073330</v>
       </c>
       <c r="B29" t="n">
-        <v>91981</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488570</v>
+        <v>488408</v>
       </c>
       <c r="R29" t="n">
-        <v>7014409</v>
+        <v>7014549</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3857,6 +3852,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129071599</v>
+        <v>129080078</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,56 +3917,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488409</v>
+        <v>488760</v>
       </c>
       <c r="R30" t="n">
-        <v>7014470</v>
+        <v>7014511</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3993,26 +3974,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4025,6 +3991,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4042,10 +4028,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129081091</v>
+        <v>129079878</v>
       </c>
       <c r="B31" t="n">
-        <v>80141</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4053,42 +4039,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488575</v>
+        <v>488787</v>
       </c>
       <c r="R31" t="n">
-        <v>7014525</v>
+        <v>7014483</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4120,11 +4101,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4141,22 +4117,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4174,48 +4150,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129080078</v>
+        <v>129076105</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>100857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488760</v>
+        <v>488531</v>
       </c>
       <c r="R32" t="n">
-        <v>7014511</v>
+        <v>7014566</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4259,26 +4240,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4296,48 +4257,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129079878</v>
+        <v>129073989</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>100857</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488787</v>
+        <v>488436</v>
       </c>
       <c r="R33" t="n">
-        <v>7014483</v>
+        <v>7014587</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4381,26 +4347,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4418,10 +4364,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129076105</v>
+        <v>129081210</v>
       </c>
       <c r="B34" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,13 +4404,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488531</v>
+        <v>488580</v>
       </c>
       <c r="R34" t="n">
-        <v>7014566</v>
+        <v>7014585</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4525,10 +4471,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129073989</v>
+        <v>129074467</v>
       </c>
       <c r="B35" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4565,10 +4511,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488436</v>
+        <v>488447</v>
       </c>
       <c r="R35" t="n">
-        <v>7014587</v>
+        <v>7014717</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -4632,10 +4578,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129081210</v>
+        <v>129078041</v>
       </c>
       <c r="B36" t="n">
-        <v>100847</v>
+        <v>99003</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4643,27 +4589,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4672,13 +4618,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488580</v>
+        <v>488550</v>
       </c>
       <c r="R36" t="n">
-        <v>7014585</v>
+        <v>7014460</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4739,38 +4685,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129074467</v>
+        <v>129081091</v>
       </c>
       <c r="B37" t="n">
-        <v>100847</v>
+        <v>80145</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4779,13 +4725,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488447</v>
+        <v>488575</v>
       </c>
       <c r="R37" t="n">
-        <v>7014717</v>
+        <v>7014525</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4817,6 +4763,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4829,6 +4780,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4846,53 +4817,67 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129078041</v>
+        <v>129071599</v>
       </c>
       <c r="B38" t="n">
-        <v>98993</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488550</v>
+        <v>488409</v>
       </c>
       <c r="R38" t="n">
-        <v>7014460</v>
+        <v>7014470</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4919,9 +4904,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4956,7 +4956,7 @@
         <v>129072614</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>129072008</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>129072477</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129076722</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>129076936</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5792,48 +5792,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129072070</v>
+        <v>129077994</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>100857</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488455</v>
+        <v>488544</v>
       </c>
       <c r="R46" t="n">
         <v>7014457</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5877,26 +5882,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5914,38 +5899,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129077994</v>
+        <v>129076866</v>
       </c>
       <c r="B47" t="n">
-        <v>100847</v>
+        <v>91818</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5954,13 +5939,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488544</v>
+        <v>488575</v>
       </c>
       <c r="R47" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5992,6 +5977,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6004,6 +5994,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6021,10 +6031,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129076866</v>
+        <v>129080537</v>
       </c>
       <c r="B48" t="n">
-        <v>91811</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6032,42 +6042,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488575</v>
+        <v>488632</v>
       </c>
       <c r="R48" t="n">
-        <v>7014596</v>
+        <v>7014478</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6101,7 +6106,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6130,12 +6135,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6153,10 +6158,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129080537</v>
+        <v>129072070</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6188,10 +6193,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488632</v>
+        <v>488455</v>
       </c>
       <c r="R49" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6224,11 +6229,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6280,53 +6280,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129072360</v>
+        <v>129070117</v>
       </c>
       <c r="B50" t="n">
-        <v>100847</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488465</v>
+        <v>488317</v>
       </c>
       <c r="R50" t="n">
-        <v>7014498</v>
+        <v>7014450</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6353,11 +6348,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>I gammal granskog med gott om död ved.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6370,6 +6380,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6387,48 +6417,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129070117</v>
+        <v>129081155</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>80180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488317</v>
+        <v>488569</v>
       </c>
       <c r="R51" t="n">
-        <v>7014450</v>
+        <v>7014529</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6455,24 +6490,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6491,22 +6516,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6524,10 +6549,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129081155</v>
+        <v>129072360</v>
       </c>
       <c r="B52" t="n">
-        <v>80176</v>
+        <v>100857</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,27 +6560,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6564,10 +6589,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488569</v>
+        <v>488465</v>
       </c>
       <c r="R52" t="n">
-        <v>7014529</v>
+        <v>7014498</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -6602,11 +6627,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6619,26 +6639,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6659,7 +6659,7 @@
         <v>129079479</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6793,32 +6793,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B54" t="n">
-        <v>91981</v>
+        <v>91818</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R54" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -6869,6 +6869,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6920,38 +6925,47 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129071884</v>
+        <v>129077981</v>
       </c>
       <c r="B55" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6960,13 +6974,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488391</v>
+        <v>488516</v>
       </c>
       <c r="R55" t="n">
-        <v>7014430</v>
+        <v>7014462</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6993,14 +7007,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7015,26 +7039,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7052,10 +7056,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129077981</v>
+        <v>129071923</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>91988</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7063,36 +7067,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7101,13 +7096,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488516</v>
+        <v>488400</v>
       </c>
       <c r="R56" t="n">
-        <v>7014462</v>
+        <v>7014435</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7134,26 +7129,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7166,6 +7146,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7183,53 +7183,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B57" t="n">
-        <v>92226</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R57" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7287,12 +7282,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7310,48 +7305,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>92233</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R58" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7435,7 +7435,7 @@
         <v>129073198</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,48 +7559,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129073935</v>
+        <v>129070439</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>103191</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488409</v>
+        <v>488363</v>
       </c>
       <c r="R60" t="n">
-        <v>7014521</v>
+        <v>7014442</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7627,11 +7632,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7644,26 +7664,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7681,53 +7681,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129070439</v>
+        <v>129073935</v>
       </c>
       <c r="B61" t="n">
-        <v>103181</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488363</v>
+        <v>488409</v>
       </c>
       <c r="R61" t="n">
-        <v>7014442</v>
+        <v>7014521</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7754,26 +7749,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7786,6 +7766,26 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
         <v>129076561</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129079063</v>
+        <v>129074640</v>
       </c>
       <c r="B63" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488655</v>
+        <v>488472</v>
       </c>
       <c r="R63" t="n">
-        <v>7014417</v>
+        <v>7014599</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8062,38 +8062,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129073694</v>
+        <v>129078537</v>
       </c>
       <c r="B64" t="n">
-        <v>100847</v>
+        <v>57725</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8102,13 +8107,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488426</v>
+        <v>488573</v>
       </c>
       <c r="R64" t="n">
-        <v>7014494</v>
+        <v>7014399</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8140,6 +8145,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8152,6 +8162,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8169,38 +8199,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129072652</v>
+        <v>129079063</v>
       </c>
       <c r="B65" t="n">
-        <v>100847</v>
+        <v>57725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8209,13 +8239,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488514</v>
+        <v>488655</v>
       </c>
       <c r="R65" t="n">
-        <v>7014547</v>
+        <v>7014417</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8247,6 +8277,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8259,6 +8294,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8279,7 +8334,7 @@
         <v>129078147</v>
       </c>
       <c r="B66" t="n">
-        <v>103181</v>
+        <v>103191</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8393,38 +8448,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129074640</v>
+        <v>129073694</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>100857</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8433,13 +8488,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488472</v>
+        <v>488426</v>
       </c>
       <c r="R67" t="n">
-        <v>7014599</v>
+        <v>7014494</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8471,11 +8526,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8488,26 +8538,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8525,43 +8555,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129078537</v>
+        <v>129072652</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>100857</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8570,13 +8595,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488573</v>
+        <v>488514</v>
       </c>
       <c r="R68" t="n">
-        <v>7014399</v>
+        <v>7014547</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8608,11 +8633,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8625,26 +8645,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8665,7 +8665,7 @@
         <v>129079226</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>129074346</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98558</v>
+        <v>98568</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129213412</v>
+        <v>129213773</v>
       </c>
       <c r="B75" t="n">
-        <v>98659</v>
+        <v>91988</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9453,41 +9453,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9496,13 +9482,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488623</v>
+        <v>488662</v>
       </c>
       <c r="R75" t="n">
-        <v>7014540</v>
+        <v>7014466</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9531,7 +9517,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9541,12 +9527,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9561,6 +9542,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9581,7 +9582,7 @@
         <v>129215411</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9718,7 +9719,7 @@
         <v>129210501</v>
       </c>
       <c r="B77" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9862,10 +9863,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129213773</v>
+        <v>129213412</v>
       </c>
       <c r="B78" t="n">
-        <v>91981</v>
+        <v>98669</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9873,27 +9874,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9902,13 +9917,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488662</v>
+        <v>488623</v>
       </c>
       <c r="R78" t="n">
-        <v>7014466</v>
+        <v>7014540</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9937,7 +9952,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9947,7 +9962,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9962,26 +9982,6 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>129212598</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>129211802</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>129214932</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>129212656</v>
       </c>
       <c r="B83" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>129215312</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>129210249</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>129215145</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>129212289</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11294,38 +11294,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129214590</v>
+        <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>98993</v>
+        <v>91551</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11334,10 +11334,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488566</v>
+        <v>488495</v>
       </c>
       <c r="R89" t="n">
-        <v>7014423</v>
+        <v>7014661</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11394,6 +11394,26 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11411,64 +11431,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129211354</v>
+        <v>129215229</v>
       </c>
       <c r="B90" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488586</v>
+        <v>488501</v>
       </c>
       <c r="R90" t="n">
-        <v>7014612</v>
+        <v>7014416</v>
       </c>
       <c r="S90" t="n">
         <v>9</v>
@@ -11500,7 +11501,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11510,12 +11511,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11547,10 +11543,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129209204</v>
+        <v>129215504</v>
       </c>
       <c r="B91" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11558,42 +11554,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488495</v>
+        <v>488457</v>
       </c>
       <c r="R91" t="n">
-        <v>7014661</v>
+        <v>7014436</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11622,7 +11613,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11632,7 +11623,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11647,26 +11638,6 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11684,45 +11655,64 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215229</v>
+        <v>129211354</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488501</v>
+        <v>488586</v>
       </c>
       <c r="R92" t="n">
-        <v>7014416</v>
+        <v>7014612</v>
       </c>
       <c r="S92" t="n">
         <v>9</v>
@@ -11754,7 +11744,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11764,7 +11754,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11796,48 +11791,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215504</v>
+        <v>129213105</v>
       </c>
       <c r="B93" t="n">
-        <v>79035</v>
+        <v>100857</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488457</v>
+        <v>488627</v>
       </c>
       <c r="R93" t="n">
-        <v>7014436</v>
+        <v>7014454</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11908,10 +11908,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129213105</v>
+        <v>129214590</v>
       </c>
       <c r="B94" t="n">
-        <v>100847</v>
+        <v>99003</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11919,27 +11919,27 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11948,10 +11948,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488627</v>
+        <v>488566</v>
       </c>
       <c r="R94" t="n">
-        <v>7014454</v>
+        <v>7014423</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12028,7 +12028,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12259,47 +12259,38 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129212481</v>
+        <v>129210843</v>
       </c>
       <c r="B97" t="n">
-        <v>57720</v>
+        <v>100857</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12308,13 +12299,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488604</v>
+        <v>488496</v>
       </c>
       <c r="R97" t="n">
-        <v>7014527</v>
+        <v>7014638</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12343,7 +12334,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12353,12 +12344,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12390,47 +12376,42 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129214807</v>
+        <v>129212481</v>
       </c>
       <c r="B98" t="n">
-        <v>98659</v>
+        <v>57722</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -12444,13 +12425,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488555</v>
+        <v>488604</v>
       </c>
       <c r="R98" t="n">
-        <v>7014416</v>
+        <v>7014527</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12479,7 +12460,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12489,12 +12470,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12526,50 +12507,64 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129210843</v>
+        <v>129214807</v>
       </c>
       <c r="B99" t="n">
-        <v>100847</v>
+        <v>98669</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488496</v>
+        <v>488555</v>
       </c>
       <c r="R99" t="n">
-        <v>7014638</v>
+        <v>7014416</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -12601,7 +12596,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12611,7 +12606,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12646,7 +12646,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>129212827</v>
       </c>
       <c r="B104" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13324,50 +13324,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129209238</v>
+        <v>129213534</v>
       </c>
       <c r="B105" t="n">
-        <v>100847</v>
+        <v>79039</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488489</v>
+        <v>488675</v>
       </c>
       <c r="R105" t="n">
-        <v>7014656</v>
+        <v>7014494</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13399,7 +13394,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13409,7 +13404,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13424,6 +13419,26 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13441,10 +13456,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129213534</v>
+        <v>129213886</v>
       </c>
       <c r="B106" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13452,37 +13467,47 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488675</v>
+        <v>488671</v>
       </c>
       <c r="R106" t="n">
-        <v>7014494</v>
+        <v>7014435</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13511,7 +13536,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13521,7 +13546,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13550,12 +13580,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13573,43 +13603,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129213886</v>
+        <v>129209238</v>
       </c>
       <c r="B107" t="n">
-        <v>57723</v>
+        <v>100857</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13618,13 +13643,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488671</v>
+        <v>488489</v>
       </c>
       <c r="R107" t="n">
-        <v>7014435</v>
+        <v>7014656</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13653,7 +13678,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13663,12 +13688,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13683,26 +13703,6 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13723,7 +13723,7 @@
         <v>129213440</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>129214838</v>
       </c>
       <c r="B109" t="n">
-        <v>98563</v>
+        <v>98573</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>129213171</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>129209979</v>
       </c>
       <c r="B112" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14404,43 +14404,38 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B113" t="n">
-        <v>100847</v>
+        <v>57725</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14449,13 +14444,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R113" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14484,7 +14479,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14494,7 +14489,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14509,6 +14509,26 @@
       <c r="AH113" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14526,38 +14546,43 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214896</v>
+        <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>57723</v>
+        <v>100857</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14566,13 +14591,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488525</v>
+        <v>488543</v>
       </c>
       <c r="R114" t="n">
-        <v>7014424</v>
+        <v>7014418</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14601,7 +14626,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14611,12 +14636,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14631,26 +14651,6 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14671,7 +14671,7 @@
         <v>129214402</v>
       </c>
       <c r="B115" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14800,45 +14800,64 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129212678</v>
+        <v>129211241</v>
       </c>
       <c r="B116" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488572</v>
+        <v>488551</v>
       </c>
       <c r="R116" t="n">
-        <v>7014469</v>
+        <v>7014630</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14870,7 +14889,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14880,7 +14899,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14895,26 +14919,6 @@
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14932,10 +14936,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129211241</v>
+        <v>129211912</v>
       </c>
       <c r="B117" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14962,7 +14966,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14986,10 +14990,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488551</v>
+        <v>488586</v>
       </c>
       <c r="R117" t="n">
-        <v>7014630</v>
+        <v>7014626</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15021,7 +15025,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15031,12 +15035,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15068,64 +15072,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129211912</v>
+        <v>129212678</v>
       </c>
       <c r="B118" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488586</v>
+        <v>488572</v>
       </c>
       <c r="R118" t="n">
-        <v>7014626</v>
+        <v>7014469</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15157,7 +15142,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15167,12 +15152,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15187,6 +15167,26 @@
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15204,10 +15204,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129214468</v>
+        <v>129212992</v>
       </c>
       <c r="B119" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15215,42 +15215,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488595</v>
+        <v>488605</v>
       </c>
       <c r="R119" t="n">
-        <v>7014471</v>
+        <v>7014461</v>
       </c>
       <c r="S119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15279,7 +15274,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15289,12 +15284,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15323,12 +15313,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15349,7 +15339,7 @@
         <v>129210698</v>
       </c>
       <c r="B120" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15466,7 +15456,7 @@
         <v>129209446</v>
       </c>
       <c r="B121" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15595,10 +15585,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129212992</v>
+        <v>129214468</v>
       </c>
       <c r="B122" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15606,37 +15596,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488605</v>
+        <v>488595</v>
       </c>
       <c r="R122" t="n">
-        <v>7014461</v>
+        <v>7014471</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15665,7 +15660,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15675,7 +15670,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -5792,38 +5792,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129077994</v>
+        <v>129076866</v>
       </c>
       <c r="B46" t="n">
-        <v>100857</v>
+        <v>91818</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5832,13 +5832,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488544</v>
+        <v>488575</v>
       </c>
       <c r="R46" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5870,6 +5870,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5882,6 +5887,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5899,10 +5924,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129076866</v>
+        <v>129080537</v>
       </c>
       <c r="B47" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5910,42 +5935,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488575</v>
+        <v>488632</v>
       </c>
       <c r="R47" t="n">
-        <v>7014596</v>
+        <v>7014478</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5979,7 +5999,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6008,12 +6028,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6031,7 +6051,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129080537</v>
+        <v>129072070</v>
       </c>
       <c r="B48" t="n">
         <v>79039</v>
@@ -6066,10 +6086,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488632</v>
+        <v>488455</v>
       </c>
       <c r="R48" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -6102,11 +6122,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6158,48 +6173,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129072070</v>
+        <v>129077994</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>100857</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488455</v>
+        <v>488544</v>
       </c>
       <c r="R49" t="n">
         <v>7014457</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6243,26 +6263,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6549,38 +6549,43 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129072360</v>
+        <v>129079479</v>
       </c>
       <c r="B52" t="n">
-        <v>100857</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6589,13 +6594,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488465</v>
+        <v>488806</v>
       </c>
       <c r="R52" t="n">
-        <v>7014498</v>
+        <v>7014416</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6627,6 +6632,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6639,6 +6649,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6656,43 +6686,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129079479</v>
+        <v>129072360</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>100857</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6701,13 +6726,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488806</v>
+        <v>488465</v>
       </c>
       <c r="R53" t="n">
-        <v>7014416</v>
+        <v>7014498</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6739,11 +6764,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6756,26 +6776,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6925,10 +6925,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129077981</v>
+        <v>129071923</v>
       </c>
       <c r="B55" t="n">
-        <v>98669</v>
+        <v>91988</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6936,36 +6936,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6974,13 +6965,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488516</v>
+        <v>488400</v>
       </c>
       <c r="R55" t="n">
-        <v>7014462</v>
+        <v>7014435</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7007,26 +6998,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7039,6 +7015,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7056,10 +7052,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129071923</v>
+        <v>129077981</v>
       </c>
       <c r="B56" t="n">
-        <v>91988</v>
+        <v>98669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,27 +7063,36 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7096,13 +7101,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488400</v>
+        <v>488516</v>
       </c>
       <c r="R56" t="n">
-        <v>7014435</v>
+        <v>7014462</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7129,11 +7134,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7146,26 +7166,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129073198</v>
+        <v>129073935</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7443,47 +7443,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488422</v>
+        <v>488409</v>
       </c>
       <c r="R59" t="n">
-        <v>7014530</v>
+        <v>7014521</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7515,11 +7505,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7534,14 +7519,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7681,10 +7676,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129073935</v>
+        <v>129073198</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7692,37 +7687,47 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488409</v>
+        <v>488422</v>
       </c>
       <c r="R61" t="n">
-        <v>7014521</v>
+        <v>7014530</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7754,6 +7759,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7768,24 +7778,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -10136,45 +10136,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129212598</v>
+        <v>129212656</v>
       </c>
       <c r="B80" t="n">
-        <v>79039</v>
+        <v>100857</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488580</v>
+        <v>488569</v>
       </c>
       <c r="R80" t="n">
-        <v>7014484</v>
+        <v>7014485</v>
       </c>
       <c r="S80" t="n">
         <v>9</v>
@@ -10206,7 +10211,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10216,12 +10221,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10236,26 +10236,6 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10273,7 +10253,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129211802</v>
+        <v>129212598</v>
       </c>
       <c r="B81" t="n">
         <v>79039</v>
@@ -10308,13 +10288,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488591</v>
+        <v>488580</v>
       </c>
       <c r="R81" t="n">
-        <v>7014632</v>
+        <v>7014484</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10343,7 +10323,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10353,7 +10333,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10382,12 +10367,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10405,10 +10390,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129214932</v>
+        <v>129211802</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10416,42 +10401,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488526</v>
+        <v>488591</v>
       </c>
       <c r="R82" t="n">
-        <v>7014439</v>
+        <v>7014632</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10480,7 +10460,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10490,12 +10470,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10524,12 +10499,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10547,38 +10522,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129212656</v>
+        <v>129214932</v>
       </c>
       <c r="B83" t="n">
-        <v>100857</v>
+        <v>57725</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10587,13 +10562,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488569</v>
+        <v>488526</v>
       </c>
       <c r="R83" t="n">
-        <v>7014485</v>
+        <v>7014439</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10622,7 +10597,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10632,7 +10607,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10647,6 +10627,26 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12259,50 +12259,64 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129210843</v>
+        <v>129214807</v>
       </c>
       <c r="B97" t="n">
-        <v>100857</v>
+        <v>98669</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488496</v>
+        <v>488555</v>
       </c>
       <c r="R97" t="n">
-        <v>7014638</v>
+        <v>7014416</v>
       </c>
       <c r="S97" t="n">
         <v>9</v>
@@ -12334,7 +12348,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12344,7 +12358,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12376,47 +12395,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129212481</v>
+        <v>129210843</v>
       </c>
       <c r="B98" t="n">
-        <v>57722</v>
+        <v>100857</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12425,13 +12435,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488604</v>
+        <v>488496</v>
       </c>
       <c r="R98" t="n">
-        <v>7014527</v>
+        <v>7014638</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12460,7 +12470,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12470,12 +12480,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12507,47 +12512,42 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129214807</v>
+        <v>129212481</v>
       </c>
       <c r="B99" t="n">
-        <v>98669</v>
+        <v>57722</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -12561,13 +12561,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488555</v>
+        <v>488604</v>
       </c>
       <c r="R99" t="n">
-        <v>7014416</v>
+        <v>7014527</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -15204,48 +15204,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129212992</v>
+        <v>129210698</v>
       </c>
       <c r="B119" t="n">
-        <v>79039</v>
+        <v>92471</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488605</v>
+        <v>488475</v>
       </c>
       <c r="R119" t="n">
-        <v>7014461</v>
+        <v>7014707</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15274,7 +15279,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15284,7 +15289,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15299,26 +15304,6 @@
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15336,38 +15321,38 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129210698</v>
+        <v>129214468</v>
       </c>
       <c r="B120" t="n">
-        <v>92471</v>
+        <v>57725</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15376,13 +15361,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488475</v>
+        <v>488595</v>
       </c>
       <c r="R120" t="n">
-        <v>7014707</v>
+        <v>7014471</v>
       </c>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15411,7 +15396,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15421,7 +15406,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15436,6 +15426,26 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15585,10 +15595,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129214468</v>
+        <v>129212992</v>
       </c>
       <c r="B122" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15596,42 +15606,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488595</v>
+        <v>488605</v>
       </c>
       <c r="R122" t="n">
-        <v>7014471</v>
+        <v>7014461</v>
       </c>
       <c r="S122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15660,7 +15665,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15670,12 +15675,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129057979</v>
+        <v>129057988</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>100864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488344</v>
+        <v>488339</v>
       </c>
       <c r="R2" t="n">
-        <v>7014426</v>
+        <v>7014419</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129057988</v>
+        <v>129057979</v>
       </c>
       <c r="B3" t="n">
-        <v>100857</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488339</v>
+        <v>488344</v>
       </c>
       <c r="R3" t="n">
-        <v>7014419</v>
+        <v>7014426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129076254</v>
+        <v>129074673</v>
       </c>
       <c r="B14" t="n">
         <v>79039</v>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488581</v>
+        <v>488470</v>
       </c>
       <c r="R14" t="n">
-        <v>7014597</v>
+        <v>7014593</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,11 +1982,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2003,12 +1998,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2018,7 +2013,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2036,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129080431</v>
+        <v>129079967</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -2071,13 +2066,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488667</v>
+        <v>488745</v>
       </c>
       <c r="R15" t="n">
-        <v>7014453</v>
+        <v>7014497</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2158,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129074673</v>
+        <v>129074228</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,37 +2164,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488470</v>
+        <v>488431</v>
       </c>
       <c r="R16" t="n">
-        <v>7014593</v>
+        <v>7014633</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2226,11 +2231,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2257,12 +2277,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2280,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079967</v>
+        <v>129076254</v>
       </c>
       <c r="B17" t="n">
         <v>79039</v>
@@ -2315,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488745</v>
+        <v>488581</v>
       </c>
       <c r="R17" t="n">
-        <v>7014497</v>
+        <v>7014597</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2353,6 +2373,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2369,12 +2394,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -2384,7 +2409,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2402,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074228</v>
+        <v>129080431</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,47 +2438,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488431</v>
+        <v>488667</v>
       </c>
       <c r="R18" t="n">
-        <v>7014633</v>
+        <v>7014453</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2480,26 +2495,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129078715</v>
+        <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>100857</v>
+        <v>97547</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,42 +2560,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488611</v>
+        <v>488522</v>
       </c>
       <c r="R19" t="n">
-        <v>7014397</v>
+        <v>7014485</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,6 +2620,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129077751</v>
+        <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>97540</v>
+        <v>100864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,37 +2667,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488522</v>
+        <v>488611</v>
       </c>
       <c r="R20" t="n">
-        <v>7014485</v>
+        <v>7014397</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2727,11 +2732,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3289,7 +3289,7 @@
         <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129078582</v>
       </c>
       <c r="B28" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129076105</v>
+        <v>129078041</v>
       </c>
       <c r="B32" t="n">
-        <v>100857</v>
+        <v>99010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4161,27 +4161,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4190,13 +4190,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488531</v>
+        <v>488550</v>
       </c>
       <c r="R32" t="n">
-        <v>7014566</v>
+        <v>7014460</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4257,10 +4257,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129073989</v>
+        <v>129076105</v>
       </c>
       <c r="B33" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488436</v>
+        <v>488531</v>
       </c>
       <c r="R33" t="n">
-        <v>7014587</v>
+        <v>7014566</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129081210</v>
+        <v>129073989</v>
       </c>
       <c r="B34" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,13 +4404,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488580</v>
+        <v>488436</v>
       </c>
       <c r="R34" t="n">
-        <v>7014585</v>
+        <v>7014587</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4471,10 +4471,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129074467</v>
+        <v>129081210</v>
       </c>
       <c r="B35" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4511,13 +4511,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488447</v>
+        <v>488580</v>
       </c>
       <c r="R35" t="n">
-        <v>7014717</v>
+        <v>7014585</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129078041</v>
+        <v>129074467</v>
       </c>
       <c r="B36" t="n">
-        <v>99003</v>
+        <v>100864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4589,27 +4589,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4618,13 +4618,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488550</v>
+        <v>488447</v>
       </c>
       <c r="R36" t="n">
-        <v>7014460</v>
+        <v>7014717</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>129076866</v>
       </c>
       <c r="B46" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>129077994</v>
       </c>
       <c r="B49" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6417,38 +6417,43 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129081155</v>
+        <v>129079479</v>
       </c>
       <c r="B51" t="n">
-        <v>80180</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6457,13 +6462,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488569</v>
+        <v>488806</v>
       </c>
       <c r="R51" t="n">
-        <v>7014529</v>
+        <v>7014416</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6497,7 +6502,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6516,22 +6521,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6549,43 +6554,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129079479</v>
+        <v>129072360</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>100864</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6594,13 +6594,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488806</v>
+        <v>488465</v>
       </c>
       <c r="R52" t="n">
-        <v>7014416</v>
+        <v>7014498</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6632,11 +6632,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6649,26 +6644,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6686,10 +6661,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129072360</v>
+        <v>129081155</v>
       </c>
       <c r="B53" t="n">
-        <v>100857</v>
+        <v>80180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6697,27 +6672,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6726,10 +6701,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488465</v>
+        <v>488569</v>
       </c>
       <c r="R53" t="n">
-        <v>7014498</v>
+        <v>7014529</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -6764,6 +6739,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +6756,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6796,7 +6796,7 @@
         <v>129071884</v>
       </c>
       <c r="B54" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>129071923</v>
       </c>
       <c r="B55" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>129077981</v>
       </c>
       <c r="B56" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7183,48 +7183,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>92240</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R57" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7282,12 +7287,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7305,53 +7310,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B58" t="n">
-        <v>92233</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R58" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7432,48 +7432,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129073935</v>
+        <v>129070439</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>103198</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488409</v>
+        <v>488363</v>
       </c>
       <c r="R59" t="n">
-        <v>7014521</v>
+        <v>7014442</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7500,11 +7505,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7517,26 +7537,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7554,53 +7554,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129070439</v>
+        <v>129073935</v>
       </c>
       <c r="B60" t="n">
-        <v>103191</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488363</v>
+        <v>488409</v>
       </c>
       <c r="R60" t="n">
-        <v>7014442</v>
+        <v>7014521</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7627,26 +7622,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7659,6 +7639,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129074640</v>
+        <v>129073694</v>
       </c>
       <c r="B63" t="n">
-        <v>57725</v>
+        <v>100864</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488472</v>
+        <v>488426</v>
       </c>
       <c r="R63" t="n">
-        <v>7014599</v>
+        <v>7014494</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8008,11 +8008,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8025,26 +8020,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8062,43 +8037,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129078537</v>
+        <v>129072652</v>
       </c>
       <c r="B64" t="n">
-        <v>57725</v>
+        <v>100864</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8107,13 +8077,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488573</v>
+        <v>488514</v>
       </c>
       <c r="R64" t="n">
-        <v>7014399</v>
+        <v>7014547</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8145,11 +8115,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8162,26 +8127,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8199,7 +8144,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129079063</v>
+        <v>129074640</v>
       </c>
       <c r="B65" t="n">
         <v>57725</v>
@@ -8239,13 +8184,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488655</v>
+        <v>488472</v>
       </c>
       <c r="R65" t="n">
-        <v>7014417</v>
+        <v>7014599</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8279,7 +8224,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8331,38 +8276,43 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129078147</v>
+        <v>129078537</v>
       </c>
       <c r="B66" t="n">
-        <v>103191</v>
+        <v>57725</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8371,13 +8321,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488557</v>
+        <v>488573</v>
       </c>
       <c r="R66" t="n">
-        <v>7014445</v>
+        <v>7014399</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8404,19 +8354,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8431,6 +8376,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8448,38 +8413,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129073694</v>
+        <v>129079063</v>
       </c>
       <c r="B67" t="n">
-        <v>100857</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8488,10 +8453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488426</v>
+        <v>488655</v>
       </c>
       <c r="R67" t="n">
-        <v>7014494</v>
+        <v>7014417</v>
       </c>
       <c r="S67" t="n">
         <v>11</v>
@@ -8526,6 +8491,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8538,6 +8508,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8555,10 +8545,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129072652</v>
+        <v>129078147</v>
       </c>
       <c r="B68" t="n">
-        <v>100857</v>
+        <v>103198</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8566,27 +8556,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8595,13 +8585,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488514</v>
+        <v>488557</v>
       </c>
       <c r="R68" t="n">
-        <v>7014547</v>
+        <v>7014445</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8628,9 +8618,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8797,7 +8797,7 @@
         <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98568</v>
+        <v>98575</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129213773</v>
+        <v>129213412</v>
       </c>
       <c r="B75" t="n">
-        <v>91988</v>
+        <v>98676</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9453,27 +9453,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9482,13 +9496,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488662</v>
+        <v>488623</v>
       </c>
       <c r="R75" t="n">
-        <v>7014466</v>
+        <v>7014540</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9517,7 +9531,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9527,7 +9541,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9542,26 +9561,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9579,48 +9578,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215411</v>
+        <v>129213773</v>
       </c>
       <c r="B76" t="n">
-        <v>79039</v>
+        <v>91995</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488525</v>
+        <v>488662</v>
       </c>
       <c r="R76" t="n">
-        <v>7014363</v>
+        <v>7014466</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9649,7 +9653,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9659,12 +9663,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9693,12 +9692,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9716,10 +9715,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129210501</v>
+        <v>129215411</v>
       </c>
       <c r="B77" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9727,47 +9726,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488472</v>
+        <v>488525</v>
       </c>
       <c r="R77" t="n">
-        <v>7014695</v>
+        <v>7014363</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9796,7 +9785,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9806,12 +9795,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9840,12 +9829,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9863,47 +9852,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129213412</v>
+        <v>129210501</v>
       </c>
       <c r="B78" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -9913,17 +9893,17 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488623</v>
+        <v>488472</v>
       </c>
       <c r="R78" t="n">
-        <v>7014540</v>
+        <v>7014695</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9952,7 +9932,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9962,12 +9942,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9982,6 +9962,26 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10136,50 +10136,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129212656</v>
+        <v>129212598</v>
       </c>
       <c r="B80" t="n">
-        <v>100857</v>
+        <v>79039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488569</v>
+        <v>488580</v>
       </c>
       <c r="R80" t="n">
-        <v>7014485</v>
+        <v>7014484</v>
       </c>
       <c r="S80" t="n">
         <v>9</v>
@@ -10211,7 +10206,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10221,7 +10216,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10236,6 +10236,26 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10253,7 +10273,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129212598</v>
+        <v>129211802</v>
       </c>
       <c r="B81" t="n">
         <v>79039</v>
@@ -10288,13 +10308,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488580</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7014484</v>
+        <v>7014632</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10323,7 +10343,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10333,12 +10353,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10367,12 +10382,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10390,10 +10405,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129211802</v>
+        <v>129214932</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10401,37 +10416,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488591</v>
+        <v>488526</v>
       </c>
       <c r="R82" t="n">
-        <v>7014632</v>
+        <v>7014439</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10460,7 +10480,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10470,7 +10490,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10499,12 +10524,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10522,38 +10547,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129214932</v>
+        <v>129212656</v>
       </c>
       <c r="B83" t="n">
-        <v>57725</v>
+        <v>100864</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10562,13 +10587,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488526</v>
+        <v>488569</v>
       </c>
       <c r="R83" t="n">
-        <v>7014439</v>
+        <v>7014485</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10597,7 +10622,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10607,12 +10632,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10627,26 +10647,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11655,52 +11655,38 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129211354</v>
+        <v>129213105</v>
       </c>
       <c r="B92" t="n">
-        <v>98669</v>
+        <v>100864</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11709,13 +11695,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488586</v>
+        <v>488627</v>
       </c>
       <c r="R92" t="n">
-        <v>7014612</v>
+        <v>7014454</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11744,7 +11730,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11754,12 +11740,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11791,10 +11772,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129213105</v>
+        <v>129214590</v>
       </c>
       <c r="B93" t="n">
-        <v>100857</v>
+        <v>99010</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11802,27 +11783,27 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11831,10 +11812,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488627</v>
+        <v>488566</v>
       </c>
       <c r="R93" t="n">
-        <v>7014454</v>
+        <v>7014423</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11866,7 +11847,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11876,7 +11857,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11908,38 +11889,52 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129214590</v>
+        <v>129211354</v>
       </c>
       <c r="B94" t="n">
-        <v>99003</v>
+        <v>98676</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11948,13 +11943,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488566</v>
+        <v>488586</v>
       </c>
       <c r="R94" t="n">
-        <v>7014423</v>
+        <v>7014612</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11983,7 +11978,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11993,7 +11988,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12028,7 +12028,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12259,47 +12259,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129214807</v>
+        <v>129212481</v>
       </c>
       <c r="B97" t="n">
-        <v>98669</v>
+        <v>57722</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -12313,13 +12308,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488555</v>
+        <v>488604</v>
       </c>
       <c r="R97" t="n">
-        <v>7014416</v>
+        <v>7014527</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12348,7 +12343,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12358,12 +12353,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12398,7 +12393,7 @@
         <v>129210843</v>
       </c>
       <c r="B98" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12512,42 +12507,47 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129212481</v>
+        <v>129214807</v>
       </c>
       <c r="B99" t="n">
-        <v>57722</v>
+        <v>98676</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -12561,13 +12561,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488604</v>
+        <v>488555</v>
       </c>
       <c r="R99" t="n">
-        <v>7014527</v>
+        <v>7014416</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12646,7 +12646,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>129212827</v>
       </c>
       <c r="B104" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>129209238</v>
       </c>
       <c r="B107" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13720,48 +13720,67 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129213440</v>
+        <v>129214838</v>
       </c>
       <c r="B108" t="n">
-        <v>79039</v>
+        <v>98580</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488638</v>
+        <v>488552</v>
       </c>
       <c r="R108" t="n">
-        <v>7014529</v>
+        <v>7014410</v>
       </c>
       <c r="S108" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13790,7 +13809,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13800,7 +13819,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>1 planta med fröställning.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13815,26 +13839,6 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13852,67 +13856,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129214838</v>
+        <v>129213440</v>
       </c>
       <c r="B109" t="n">
-        <v>98573</v>
+        <v>79039</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488552</v>
+        <v>488638</v>
       </c>
       <c r="R109" t="n">
-        <v>7014410</v>
+        <v>7014529</v>
       </c>
       <c r="S109" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13941,7 +13926,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13951,12 +13936,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>1 planta med fröställning.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13971,6 +13951,26 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14123,7 +14123,7 @@
         <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14800,64 +14800,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129211241</v>
+        <v>129212678</v>
       </c>
       <c r="B116" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488551</v>
+        <v>488572</v>
       </c>
       <c r="R116" t="n">
-        <v>7014630</v>
+        <v>7014469</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14889,7 +14870,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14899,12 +14880,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14919,6 +14895,26 @@
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14936,10 +14932,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129211912</v>
+        <v>129211241</v>
       </c>
       <c r="B117" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14966,7 +14962,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14990,10 +14986,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488586</v>
+        <v>488551</v>
       </c>
       <c r="R117" t="n">
-        <v>7014626</v>
+        <v>7014630</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15025,7 +15021,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15035,12 +15031,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15072,45 +15068,64 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129212678</v>
+        <v>129211912</v>
       </c>
       <c r="B118" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488572</v>
+        <v>488586</v>
       </c>
       <c r="R118" t="n">
-        <v>7014469</v>
+        <v>7014626</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15142,7 +15157,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15152,7 +15167,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15167,26 +15187,6 @@
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15204,38 +15204,38 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129210698</v>
+        <v>129214468</v>
       </c>
       <c r="B119" t="n">
-        <v>92471</v>
+        <v>57725</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -15244,13 +15244,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488475</v>
+        <v>488595</v>
       </c>
       <c r="R119" t="n">
-        <v>7014707</v>
+        <v>7014471</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15289,7 +15289,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15304,6 +15309,26 @@
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15321,38 +15346,38 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129214468</v>
+        <v>129210698</v>
       </c>
       <c r="B120" t="n">
-        <v>57725</v>
+        <v>92478</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15361,13 +15386,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488595</v>
+        <v>488475</v>
       </c>
       <c r="R120" t="n">
-        <v>7014471</v>
+        <v>7014707</v>
       </c>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15396,7 +15421,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15406,12 +15431,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15426,26 +15446,6 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129057988</v>
+        <v>129057979</v>
       </c>
       <c r="B2" t="n">
-        <v>100864</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488339</v>
+        <v>488344</v>
       </c>
       <c r="R2" t="n">
-        <v>7014419</v>
+        <v>7014426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129057979</v>
+        <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>100866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488344</v>
+        <v>488339</v>
       </c>
       <c r="R3" t="n">
-        <v>7014426</v>
+        <v>7014419</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>129057983</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129057978</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129057984</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129057976</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>129057982</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>129057975</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>129057981</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>129057980</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129072984</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129074673</v>
+        <v>129074228</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,37 +1920,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488470</v>
+        <v>488431</v>
       </c>
       <c r="R14" t="n">
-        <v>7014593</v>
+        <v>7014633</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,11 +1987,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2008,12 +2033,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2031,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129079967</v>
+        <v>129074673</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488745</v>
+        <v>488470</v>
       </c>
       <c r="R15" t="n">
-        <v>7014497</v>
+        <v>7014593</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129074228</v>
+        <v>129079967</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,47 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488431</v>
+        <v>488745</v>
       </c>
       <c r="R16" t="n">
-        <v>7014633</v>
+        <v>7014497</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,26 +2246,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2303,7 +2303,7 @@
         <v>129076254</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>129080431</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129079151</v>
+        <v>129081134</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,27 +2774,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488670</v>
+        <v>488567</v>
       </c>
       <c r="R21" t="n">
-        <v>7014411</v>
+        <v>7014534</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129081134</v>
+        <v>129079151</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,27 +2906,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488567</v>
+        <v>488670</v>
       </c>
       <c r="R22" t="n">
-        <v>7014534</v>
+        <v>7014411</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,22 +2994,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
         <v>129076465</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,43 +3149,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129072249</v>
+        <v>129071736</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>100866</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3194,13 +3189,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488459</v>
+        <v>488410</v>
       </c>
       <c r="R24" t="n">
-        <v>7014467</v>
+        <v>7014448</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,11 +3227,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3249,26 +3239,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3286,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129071736</v>
+        <v>129075203</v>
       </c>
       <c r="B25" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3326,13 +3296,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488410</v>
+        <v>488533</v>
       </c>
       <c r="R25" t="n">
-        <v>7014448</v>
+        <v>7014663</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3393,38 +3363,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129075203</v>
+        <v>129072249</v>
       </c>
       <c r="B26" t="n">
-        <v>100864</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3433,13 +3408,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488533</v>
+        <v>488459</v>
       </c>
       <c r="R26" t="n">
-        <v>7014663</v>
+        <v>7014467</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3471,6 +3446,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3483,6 +3463,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129078582</v>
       </c>
       <c r="B28" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>129073330</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,45 +3906,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129080078</v>
+        <v>129073989</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>100866</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488760</v>
+        <v>488436</v>
       </c>
       <c r="R30" t="n">
-        <v>7014511</v>
+        <v>7014587</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -3991,26 +3996,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4028,45 +4013,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129079878</v>
+        <v>129081210</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>100866</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488787</v>
+        <v>488580</v>
       </c>
       <c r="R31" t="n">
-        <v>7014483</v>
+        <v>7014585</v>
       </c>
       <c r="S31" t="n">
         <v>11</v>
@@ -4113,26 +4103,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4150,10 +4120,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129078041</v>
+        <v>129074467</v>
       </c>
       <c r="B32" t="n">
-        <v>99010</v>
+        <v>100866</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4161,27 +4131,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4190,13 +4160,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488550</v>
+        <v>488447</v>
       </c>
       <c r="R32" t="n">
-        <v>7014460</v>
+        <v>7014717</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4257,38 +4227,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129076105</v>
+        <v>129081091</v>
       </c>
       <c r="B33" t="n">
-        <v>100864</v>
+        <v>80147</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4297,13 +4267,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488531</v>
+        <v>488575</v>
       </c>
       <c r="R33" t="n">
-        <v>7014566</v>
+        <v>7014525</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4335,6 +4305,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4347,6 +4322,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4364,53 +4359,67 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129073989</v>
+        <v>129071599</v>
       </c>
       <c r="B34" t="n">
-        <v>100864</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488436</v>
+        <v>488409</v>
       </c>
       <c r="R34" t="n">
-        <v>7014587</v>
+        <v>7014470</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4437,9 +4446,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4471,50 +4495,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129081210</v>
+        <v>129079878</v>
       </c>
       <c r="B35" t="n">
-        <v>100864</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488580</v>
+        <v>488787</v>
       </c>
       <c r="R35" t="n">
-        <v>7014585</v>
+        <v>7014483</v>
       </c>
       <c r="S35" t="n">
         <v>11</v>
@@ -4561,6 +4580,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4578,50 +4617,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129074467</v>
+        <v>129080078</v>
       </c>
       <c r="B36" t="n">
-        <v>100864</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488447</v>
+        <v>488760</v>
       </c>
       <c r="R36" t="n">
-        <v>7014717</v>
+        <v>7014511</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4668,6 +4702,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4685,38 +4739,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129081091</v>
+        <v>129078041</v>
       </c>
       <c r="B37" t="n">
-        <v>80145</v>
+        <v>99012</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>219880</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4725,13 +4779,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488575</v>
+        <v>488550</v>
       </c>
       <c r="R37" t="n">
-        <v>7014525</v>
+        <v>7014460</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4763,11 +4817,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4780,26 +4829,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4817,64 +4846,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129071599</v>
+        <v>129076105</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>100866</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488409</v>
+        <v>488531</v>
       </c>
       <c r="R38" t="n">
-        <v>7014470</v>
+        <v>7014566</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4904,24 +4919,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4956,7 +4956,7 @@
         <v>129072614</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>129072008</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>129072477</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129076722</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>129076936</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>129076866</v>
       </c>
       <c r="B46" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>129080537</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>129072070</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>129077994</v>
       </c>
       <c r="B49" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6280,10 +6280,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129070117</v>
+        <v>129079479</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6291,34 +6291,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488317</v>
+        <v>488806</v>
       </c>
       <c r="R50" t="n">
-        <v>7014450</v>
+        <v>7014416</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6348,24 +6358,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6417,10 +6417,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129079479</v>
+        <v>129070117</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6428,44 +6428,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488806</v>
+        <v>488317</v>
       </c>
       <c r="R51" t="n">
-        <v>7014416</v>
+        <v>7014450</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6495,14 +6485,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
+          <t>I gammal granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6554,10 +6554,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129072360</v>
+        <v>129081155</v>
       </c>
       <c r="B52" t="n">
-        <v>100864</v>
+        <v>80182</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6565,27 +6565,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488465</v>
+        <v>488569</v>
       </c>
       <c r="R52" t="n">
-        <v>7014498</v>
+        <v>7014529</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -6632,6 +6632,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6644,6 +6649,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6661,10 +6686,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129081155</v>
+        <v>129072360</v>
       </c>
       <c r="B53" t="n">
-        <v>80180</v>
+        <v>100866</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6672,27 +6697,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6701,10 +6726,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488569</v>
+        <v>488465</v>
       </c>
       <c r="R53" t="n">
-        <v>7014529</v>
+        <v>7014498</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -6739,11 +6764,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6756,26 +6776,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6793,32 +6793,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129071884</v>
+        <v>129071923</v>
       </c>
       <c r="B54" t="n">
-        <v>91825</v>
+        <v>91997</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488391</v>
+        <v>488400</v>
       </c>
       <c r="R54" t="n">
-        <v>7014430</v>
+        <v>7014435</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -6869,11 +6869,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6925,32 +6920,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B55" t="n">
-        <v>91995</v>
+        <v>91827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6965,10 +6960,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R55" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S55" t="n">
         <v>7</v>
@@ -7001,6 +6996,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7055,7 +7055,7 @@
         <v>129077981</v>
       </c>
       <c r="B56" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7183,53 +7183,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B57" t="n">
-        <v>92240</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R57" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7287,12 +7282,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7310,48 +7305,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>92242</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R58" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7435,7 +7435,7 @@
         <v>129070439</v>
       </c>
       <c r="B59" t="n">
-        <v>103198</v>
+        <v>103200</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129073935</v>
+        <v>129073198</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7565,37 +7565,47 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488409</v>
+        <v>488422</v>
       </c>
       <c r="R60" t="n">
-        <v>7014521</v>
+        <v>7014530</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7627,6 +7637,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7641,24 +7656,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7676,10 +7681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129073198</v>
+        <v>129073935</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7687,47 +7692,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488422</v>
+        <v>488409</v>
       </c>
       <c r="R61" t="n">
-        <v>7014530</v>
+        <v>7014521</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7759,11 +7754,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7778,14 +7768,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
         <v>129076561</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129073694</v>
+        <v>129074640</v>
       </c>
       <c r="B63" t="n">
-        <v>100864</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488426</v>
+        <v>488472</v>
       </c>
       <c r="R63" t="n">
-        <v>7014494</v>
+        <v>7014599</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8008,6 +8008,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8020,6 +8025,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8037,38 +8062,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129072652</v>
+        <v>129078537</v>
       </c>
       <c r="B64" t="n">
-        <v>100864</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8077,13 +8107,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488514</v>
+        <v>488573</v>
       </c>
       <c r="R64" t="n">
-        <v>7014547</v>
+        <v>7014399</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8115,6 +8145,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8127,6 +8162,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8144,10 +8199,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129074640</v>
+        <v>129079063</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8184,13 +8239,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488472</v>
+        <v>488655</v>
       </c>
       <c r="R65" t="n">
-        <v>7014599</v>
+        <v>7014417</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8224,7 +8279,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8276,43 +8331,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129078537</v>
+        <v>129073694</v>
       </c>
       <c r="B66" t="n">
-        <v>57725</v>
+        <v>100866</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8321,13 +8371,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488573</v>
+        <v>488426</v>
       </c>
       <c r="R66" t="n">
-        <v>7014399</v>
+        <v>7014494</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8359,11 +8409,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8376,26 +8421,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8413,38 +8438,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129079063</v>
+        <v>129072652</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>100866</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8453,13 +8478,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488655</v>
+        <v>488514</v>
       </c>
       <c r="R67" t="n">
-        <v>7014417</v>
+        <v>7014547</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8491,11 +8516,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8508,26 +8528,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8548,7 +8548,7 @@
         <v>129078147</v>
       </c>
       <c r="B68" t="n">
-        <v>103198</v>
+        <v>103200</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>129079226</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>129074346</v>
       </c>
       <c r="B73" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98575</v>
+        <v>98577</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9442,47 +9442,38 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129213412</v>
+        <v>129210501</v>
       </c>
       <c r="B75" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -9492,17 +9483,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488623</v>
+        <v>488472</v>
       </c>
       <c r="R75" t="n">
-        <v>7014540</v>
+        <v>7014695</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9531,7 +9522,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9541,12 +9532,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9561,6 +9552,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9581,7 +9592,7 @@
         <v>129213773</v>
       </c>
       <c r="B76" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9718,7 +9729,7 @@
         <v>129215411</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9852,38 +9863,47 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129210501</v>
+        <v>129213412</v>
       </c>
       <c r="B78" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -9893,17 +9913,17 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488472</v>
+        <v>488623</v>
       </c>
       <c r="R78" t="n">
-        <v>7014695</v>
+        <v>7014540</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9932,7 +9952,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9942,12 +9962,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9962,26 +9982,6 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>129212598</v>
       </c>
       <c r="B80" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>129211802</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>129214932</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>129212656</v>
       </c>
       <c r="B83" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>129215312</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>129210249</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>129215145</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>129212289</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11294,38 +11294,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129209204</v>
+        <v>129214590</v>
       </c>
       <c r="B89" t="n">
-        <v>91558</v>
+        <v>99012</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11334,10 +11334,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488495</v>
+        <v>488566</v>
       </c>
       <c r="R89" t="n">
-        <v>7014661</v>
+        <v>7014423</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11394,26 +11394,6 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11431,45 +11411,64 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215229</v>
+        <v>129211354</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488501</v>
+        <v>488586</v>
       </c>
       <c r="R90" t="n">
-        <v>7014416</v>
+        <v>7014612</v>
       </c>
       <c r="S90" t="n">
         <v>9</v>
@@ -11501,7 +11500,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11511,7 +11510,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11543,48 +11547,53 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215504</v>
+        <v>129213105</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>100866</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488457</v>
+        <v>488627</v>
       </c>
       <c r="R91" t="n">
-        <v>7014436</v>
+        <v>7014454</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11613,7 +11622,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11623,7 +11632,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11655,38 +11664,38 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129213105</v>
+        <v>129209204</v>
       </c>
       <c r="B92" t="n">
-        <v>100864</v>
+        <v>91560</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11695,10 +11704,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488627</v>
+        <v>488495</v>
       </c>
       <c r="R92" t="n">
-        <v>7014454</v>
+        <v>7014661</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11730,7 +11739,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11740,7 +11749,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11755,6 +11764,26 @@
       <c r="AH92" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11772,53 +11801,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129214590</v>
+        <v>129215229</v>
       </c>
       <c r="B93" t="n">
-        <v>99010</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488566</v>
+        <v>488501</v>
       </c>
       <c r="R93" t="n">
-        <v>7014423</v>
+        <v>7014416</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11847,7 +11871,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11857,7 +11881,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11889,67 +11913,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129211354</v>
+        <v>129215504</v>
       </c>
       <c r="B94" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488586</v>
+        <v>488457</v>
       </c>
       <c r="R94" t="n">
-        <v>7014612</v>
+        <v>7014436</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11978,7 +11983,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11988,12 +11993,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12028,7 +12028,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>129212481</v>
       </c>
       <c r="B97" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12390,50 +12390,64 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129210843</v>
+        <v>129214807</v>
       </c>
       <c r="B98" t="n">
-        <v>100864</v>
+        <v>98678</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488496</v>
+        <v>488555</v>
       </c>
       <c r="R98" t="n">
-        <v>7014638</v>
+        <v>7014416</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12465,7 +12479,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12475,7 +12489,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12507,64 +12526,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129214807</v>
+        <v>129210843</v>
       </c>
       <c r="B99" t="n">
-        <v>98676</v>
+        <v>100866</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488555</v>
+        <v>488496</v>
       </c>
       <c r="R99" t="n">
-        <v>7014416</v>
+        <v>7014638</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -12596,7 +12601,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12606,12 +12611,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12646,7 +12646,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13187,53 +13187,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129212827</v>
+        <v>129213534</v>
       </c>
       <c r="B104" t="n">
-        <v>91995</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488535</v>
+        <v>488675</v>
       </c>
       <c r="R104" t="n">
-        <v>7014455</v>
+        <v>7014494</v>
       </c>
       <c r="S104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13262,7 +13257,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13272,7 +13267,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13301,12 +13296,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13324,48 +13319,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129213534</v>
+        <v>129212827</v>
       </c>
       <c r="B105" t="n">
-        <v>79039</v>
+        <v>91997</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488675</v>
+        <v>488535</v>
       </c>
       <c r="R105" t="n">
-        <v>7014494</v>
+        <v>7014455</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13459,7 +13459,7 @@
         <v>129213886</v>
       </c>
       <c r="B106" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>129209238</v>
       </c>
       <c r="B107" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>129214838</v>
       </c>
       <c r="B108" t="n">
-        <v>98580</v>
+        <v>98582</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>129213440</v>
       </c>
       <c r="B109" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>129213171</v>
       </c>
       <c r="B110" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>129209979</v>
       </c>
       <c r="B112" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>129214896</v>
       </c>
       <c r="B113" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>129214402</v>
       </c>
       <c r="B115" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>129212678</v>
       </c>
       <c r="B116" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>129211241</v>
       </c>
       <c r="B117" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>129211912</v>
       </c>
       <c r="B118" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15204,38 +15204,38 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129214468</v>
+        <v>129210698</v>
       </c>
       <c r="B119" t="n">
-        <v>57725</v>
+        <v>92480</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -15244,13 +15244,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488595</v>
+        <v>488475</v>
       </c>
       <c r="R119" t="n">
-        <v>7014471</v>
+        <v>7014707</v>
       </c>
       <c r="S119" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15289,12 +15289,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15309,26 +15304,6 @@
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15346,38 +15321,38 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129210698</v>
+        <v>129214468</v>
       </c>
       <c r="B120" t="n">
-        <v>92478</v>
+        <v>57727</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15386,13 +15361,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488475</v>
+        <v>488595</v>
       </c>
       <c r="R120" t="n">
-        <v>7014707</v>
+        <v>7014471</v>
       </c>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15421,7 +15396,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15431,7 +15406,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15446,6 +15426,26 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15466,7 +15466,7 @@
         <v>129209446</v>
       </c>
       <c r="B121" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>129212992</v>
       </c>
       <c r="B122" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>129211708</v>
       </c>
       <c r="B123" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY123"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129057979</v>
+        <v>129057988</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488344</v>
+        <v>488339</v>
       </c>
       <c r="R2" t="n">
-        <v>7014426</v>
+        <v>7014419</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129057988</v>
+        <v>129057979</v>
       </c>
       <c r="B3" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488339</v>
+        <v>488344</v>
       </c>
       <c r="R3" t="n">
-        <v>7014419</v>
+        <v>7014426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129074673</v>
+        <v>129076254</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488470</v>
+        <v>488581</v>
       </c>
       <c r="R15" t="n">
-        <v>7014593</v>
+        <v>7014597</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2129,6 +2129,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2145,12 +2150,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2160,7 +2165,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2178,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129079967</v>
+        <v>129080431</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2213,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488745</v>
+        <v>488667</v>
       </c>
       <c r="R16" t="n">
-        <v>7014497</v>
+        <v>7014453</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129076254</v>
+        <v>129074673</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2335,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488581</v>
+        <v>488470</v>
       </c>
       <c r="R17" t="n">
-        <v>7014597</v>
+        <v>7014593</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,11 +2378,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129080431</v>
+        <v>129079967</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488667</v>
+        <v>488745</v>
       </c>
       <c r="R18" t="n">
-        <v>7014453</v>
+        <v>7014497</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3149,38 +3149,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129071736</v>
+        <v>129072249</v>
       </c>
       <c r="B24" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3189,13 +3194,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488410</v>
+        <v>488459</v>
       </c>
       <c r="R24" t="n">
-        <v>7014448</v>
+        <v>7014467</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3227,6 +3232,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3239,6 +3249,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3256,7 +3286,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129075203</v>
+        <v>129071736</v>
       </c>
       <c r="B25" t="n">
         <v>100866</v>
@@ -3296,13 +3326,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488533</v>
+        <v>488410</v>
       </c>
       <c r="R25" t="n">
-        <v>7014663</v>
+        <v>7014448</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,43 +3393,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129072249</v>
+        <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3408,13 +3433,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488459</v>
+        <v>488533</v>
       </c>
       <c r="R26" t="n">
-        <v>7014467</v>
+        <v>7014663</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,11 +3471,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3463,26 +3483,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3906,38 +3906,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129073989</v>
+        <v>129081091</v>
       </c>
       <c r="B30" t="n">
-        <v>100866</v>
+        <v>80147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3946,13 +3946,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488436</v>
+        <v>488575</v>
       </c>
       <c r="R30" t="n">
-        <v>7014587</v>
+        <v>7014525</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3984,6 +3984,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3996,6 +4001,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4013,53 +4038,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129081210</v>
+        <v>129080078</v>
       </c>
       <c r="B31" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488580</v>
+        <v>488760</v>
       </c>
       <c r="R31" t="n">
-        <v>7014585</v>
+        <v>7014511</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4103,6 +4123,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4120,53 +4160,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129074467</v>
+        <v>129079878</v>
       </c>
       <c r="B32" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488447</v>
+        <v>488787</v>
       </c>
       <c r="R32" t="n">
-        <v>7014717</v>
+        <v>7014483</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4210,6 +4245,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4227,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129081091</v>
+        <v>129071599</v>
       </c>
       <c r="B33" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4238,42 +4293,56 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488575</v>
+        <v>488409</v>
       </c>
       <c r="R33" t="n">
-        <v>7014525</v>
+        <v>7014470</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4300,14 +4369,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,26 +4401,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4359,64 +4418,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129071599</v>
+        <v>129076105</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488409</v>
+        <v>488531</v>
       </c>
       <c r="R34" t="n">
-        <v>7014470</v>
+        <v>7014566</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4446,24 +4491,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4495,48 +4525,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129079878</v>
+        <v>129073989</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488787</v>
+        <v>488436</v>
       </c>
       <c r="R35" t="n">
-        <v>7014483</v>
+        <v>7014587</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4580,26 +4615,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4617,48 +4632,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129080078</v>
+        <v>129081210</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488760</v>
+        <v>488580</v>
       </c>
       <c r="R36" t="n">
-        <v>7014511</v>
+        <v>7014585</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4702,26 +4722,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129078041</v>
+        <v>129074467</v>
       </c>
       <c r="B37" t="n">
-        <v>99012</v>
+        <v>100866</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4750,27 +4750,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488550</v>
+        <v>488447</v>
       </c>
       <c r="R37" t="n">
-        <v>7014460</v>
+        <v>7014717</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129076105</v>
+        <v>129078041</v>
       </c>
       <c r="B38" t="n">
-        <v>100866</v>
+        <v>99012</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,27 +4857,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488531</v>
+        <v>488550</v>
       </c>
       <c r="R38" t="n">
-        <v>7014566</v>
+        <v>7014460</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129076722</v>
+        <v>129076936</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5476,13 +5476,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488602</v>
+        <v>488552</v>
       </c>
       <c r="R43" t="n">
-        <v>7014595</v>
+        <v>7014587</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129076936</v>
+        <v>129076722</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488552</v>
+        <v>488602</v>
       </c>
       <c r="R44" t="n">
-        <v>7014587</v>
+        <v>7014595</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5792,10 +5792,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129076866</v>
+        <v>129080537</v>
       </c>
       <c r="B46" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5803,42 +5803,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488575</v>
+        <v>488632</v>
       </c>
       <c r="R46" t="n">
-        <v>7014596</v>
+        <v>7014478</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5872,7 +5867,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5901,12 +5896,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5924,7 +5919,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080537</v>
+        <v>129072070</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5959,10 +5954,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488632</v>
+        <v>488455</v>
       </c>
       <c r="R47" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5995,11 +5990,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6051,10 +6041,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129072070</v>
+        <v>129076866</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6062,37 +6052,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488455</v>
+        <v>488575</v>
       </c>
       <c r="R48" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6124,6 +6119,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7183,48 +7183,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R57" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7282,12 +7287,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7305,53 +7310,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B58" t="n">
-        <v>92242</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R58" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7432,53 +7432,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129070439</v>
+        <v>129073935</v>
       </c>
       <c r="B59" t="n">
-        <v>103200</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488363</v>
+        <v>488409</v>
       </c>
       <c r="R59" t="n">
-        <v>7014442</v>
+        <v>7014521</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7505,26 +7500,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7537,6 +7517,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7681,48 +7681,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129073935</v>
+        <v>129070439</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>103200</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488409</v>
+        <v>488363</v>
       </c>
       <c r="R61" t="n">
-        <v>7014521</v>
+        <v>7014442</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7749,11 +7754,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7766,26 +7786,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129074640</v>
+        <v>129073694</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488472</v>
+        <v>488426</v>
       </c>
       <c r="R63" t="n">
-        <v>7014599</v>
+        <v>7014494</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8008,11 +8008,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8025,26 +8020,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8062,43 +8037,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129078537</v>
+        <v>129072652</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8107,13 +8077,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488573</v>
+        <v>488514</v>
       </c>
       <c r="R64" t="n">
-        <v>7014399</v>
+        <v>7014547</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8145,11 +8115,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8162,26 +8127,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8199,38 +8144,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129079063</v>
+        <v>129078147</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>103200</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8239,13 +8184,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488655</v>
+        <v>488557</v>
       </c>
       <c r="R65" t="n">
-        <v>7014417</v>
+        <v>7014445</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8272,14 +8217,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8294,26 +8244,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8331,38 +8261,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129073694</v>
+        <v>129074640</v>
       </c>
       <c r="B66" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8371,13 +8301,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488426</v>
+        <v>488472</v>
       </c>
       <c r="R66" t="n">
-        <v>7014494</v>
+        <v>7014599</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8409,6 +8339,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8421,6 +8356,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8438,38 +8393,43 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129072652</v>
+        <v>129078537</v>
       </c>
       <c r="B67" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8478,13 +8438,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488514</v>
+        <v>488573</v>
       </c>
       <c r="R67" t="n">
-        <v>7014547</v>
+        <v>7014399</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8516,6 +8476,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8528,6 +8493,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8545,38 +8530,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129078147</v>
+        <v>129079063</v>
       </c>
       <c r="B68" t="n">
-        <v>103200</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8585,13 +8570,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488557</v>
+        <v>488655</v>
       </c>
       <c r="R68" t="n">
-        <v>7014445</v>
+        <v>7014417</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8618,19 +8603,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8645,6 +8625,26 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129210501</v>
+        <v>129215411</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9453,47 +9453,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488472</v>
+        <v>488525</v>
       </c>
       <c r="R75" t="n">
-        <v>7014695</v>
+        <v>7014363</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9522,7 +9512,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9532,12 +9522,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9566,12 +9556,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9726,10 +9716,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215411</v>
+        <v>129210501</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9737,37 +9727,47 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488525</v>
+        <v>488472</v>
       </c>
       <c r="R77" t="n">
-        <v>7014363</v>
+        <v>7014695</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10136,7 +10136,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129212598</v>
+        <v>129211802</v>
       </c>
       <c r="B80" t="n">
         <v>79041</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488580</v>
+        <v>488591</v>
       </c>
       <c r="R80" t="n">
-        <v>7014484</v>
+        <v>7014632</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10216,12 +10216,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10250,12 +10245,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10273,7 +10268,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129211802</v>
+        <v>129212598</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -10308,13 +10303,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488591</v>
+        <v>488580</v>
       </c>
       <c r="R81" t="n">
-        <v>7014632</v>
+        <v>7014484</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10343,7 +10338,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10353,7 +10348,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10382,12 +10382,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215312</v>
+        <v>129212289</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R85" t="n">
-        <v>7014397</v>
+        <v>7014544</v>
       </c>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10901,6 +10901,26 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11162,7 +11182,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129212289</v>
+        <v>129215312</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -11197,13 +11217,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488615</v>
+        <v>488534</v>
       </c>
       <c r="R88" t="n">
-        <v>7014544</v>
+        <v>7014397</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11232,7 +11252,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11242,7 +11262,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11257,26 +11277,6 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11294,38 +11294,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129214590</v>
+        <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>99012</v>
+        <v>91560</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11334,10 +11334,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488566</v>
+        <v>488495</v>
       </c>
       <c r="R89" t="n">
-        <v>7014423</v>
+        <v>7014661</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11394,6 +11394,26 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11411,52 +11431,38 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129211354</v>
+        <v>129214590</v>
       </c>
       <c r="B90" t="n">
-        <v>98678</v>
+        <v>99012</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11465,13 +11471,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488586</v>
+        <v>488566</v>
       </c>
       <c r="R90" t="n">
-        <v>7014612</v>
+        <v>7014423</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11500,7 +11506,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11510,12 +11516,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11547,38 +11548,52 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129213105</v>
+        <v>129211354</v>
       </c>
       <c r="B91" t="n">
-        <v>100866</v>
+        <v>98678</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11587,13 +11602,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488627</v>
+        <v>488586</v>
       </c>
       <c r="R91" t="n">
-        <v>7014454</v>
+        <v>7014612</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11622,7 +11637,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11632,7 +11647,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11664,10 +11684,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129209204</v>
+        <v>129215504</v>
       </c>
       <c r="B92" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11675,42 +11695,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488495</v>
+        <v>488457</v>
       </c>
       <c r="R92" t="n">
-        <v>7014661</v>
+        <v>7014436</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11739,7 +11754,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11749,7 +11764,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11764,26 +11779,6 @@
       <c r="AH92" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11913,48 +11908,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215504</v>
+        <v>129213105</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488457</v>
+        <v>488627</v>
       </c>
       <c r="R94" t="n">
-        <v>7014436</v>
+        <v>7014454</v>
       </c>
       <c r="S94" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13187,48 +13187,53 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129213534</v>
+        <v>129212827</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>91997</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488675</v>
+        <v>488535</v>
       </c>
       <c r="R104" t="n">
-        <v>7014494</v>
+        <v>7014455</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13257,7 +13262,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13267,7 +13272,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13296,12 +13301,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13319,38 +13324,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129212827</v>
+        <v>129209238</v>
       </c>
       <c r="B105" t="n">
-        <v>91997</v>
+        <v>100866</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -13359,13 +13364,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488535</v>
+        <v>488489</v>
       </c>
       <c r="R105" t="n">
-        <v>7014455</v>
+        <v>7014656</v>
       </c>
       <c r="S105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13394,7 +13399,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13404,7 +13409,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13419,26 +13424,6 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13456,10 +13441,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129213886</v>
+        <v>129213534</v>
       </c>
       <c r="B106" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13467,47 +13452,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488671</v>
+        <v>488675</v>
       </c>
       <c r="R106" t="n">
-        <v>7014435</v>
+        <v>7014494</v>
       </c>
       <c r="S106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13536,7 +13511,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13546,12 +13521,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13580,12 +13550,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13603,38 +13573,43 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129209238</v>
+        <v>129213886</v>
       </c>
       <c r="B107" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13643,13 +13618,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488489</v>
+        <v>488671</v>
       </c>
       <c r="R107" t="n">
-        <v>7014656</v>
+        <v>7014435</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13678,7 +13653,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13688,7 +13663,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13703,6 +13683,26 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13720,67 +13720,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129214838</v>
+        <v>129213440</v>
       </c>
       <c r="B108" t="n">
-        <v>98582</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488552</v>
+        <v>488638</v>
       </c>
       <c r="R108" t="n">
-        <v>7014410</v>
+        <v>7014529</v>
       </c>
       <c r="S108" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13809,7 +13790,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13819,12 +13800,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>1 planta med fröställning.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13839,6 +13815,26 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13856,48 +13852,67 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129213440</v>
+        <v>129214838</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>98582</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488638</v>
+        <v>488552</v>
       </c>
       <c r="R109" t="n">
-        <v>7014529</v>
+        <v>7014410</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13926,7 +13941,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13936,7 +13951,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>1 planta med fröställning.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13951,26 +13971,6 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14404,38 +14404,43 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129214896</v>
+        <v>129214819</v>
       </c>
       <c r="B113" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14444,13 +14449,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488525</v>
+        <v>488543</v>
       </c>
       <c r="R113" t="n">
-        <v>7014424</v>
+        <v>7014418</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14479,7 +14484,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14489,12 +14494,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14509,26 +14509,6 @@
       <c r="AH113" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14546,43 +14526,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B114" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14591,13 +14566,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R114" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14626,7 +14601,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14636,7 +14611,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14651,6 +14631,26 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15321,10 +15321,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129214468</v>
+        <v>129212992</v>
       </c>
       <c r="B120" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15332,42 +15332,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488595</v>
+        <v>488605</v>
       </c>
       <c r="R120" t="n">
-        <v>7014471</v>
+        <v>7014461</v>
       </c>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15396,7 +15391,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15406,12 +15401,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15440,12 +15430,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15595,10 +15585,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129212992</v>
+        <v>129214468</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15606,37 +15596,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488605</v>
+        <v>488595</v>
       </c>
       <c r="R122" t="n">
-        <v>7014461</v>
+        <v>7014471</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15665,7 +15660,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15675,7 +15670,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15704,12 +15704,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15862,6 +15862,156 @@
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>129349154</v>
+      </c>
+      <c r="B124" t="n">
+        <v>92215</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>898</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Väster om Kläppe naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>488533</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7014478</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Minst en drygt meterlång fruktkropp på en delvis avbarkad granlåga.</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>Gammal granskog med bitvis stora mängder liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -3149,43 +3149,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129072249</v>
+        <v>129071736</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3194,13 +3189,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488459</v>
+        <v>488410</v>
       </c>
       <c r="R24" t="n">
-        <v>7014467</v>
+        <v>7014448</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,11 +3227,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3249,26 +3239,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3286,7 +3256,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129071736</v>
+        <v>129075203</v>
       </c>
       <c r="B25" t="n">
         <v>100866</v>
@@ -3326,13 +3296,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488410</v>
+        <v>488533</v>
       </c>
       <c r="R25" t="n">
-        <v>7014448</v>
+        <v>7014663</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3393,38 +3363,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129075203</v>
+        <v>129072249</v>
       </c>
       <c r="B26" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3433,13 +3408,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488533</v>
+        <v>488459</v>
       </c>
       <c r="R26" t="n">
-        <v>7014663</v>
+        <v>7014467</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3471,6 +3446,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3483,6 +3463,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129076105</v>
+        <v>129074467</v>
       </c>
       <c r="B34" t="n">
         <v>100866</v>
@@ -4458,13 +4458,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488531</v>
+        <v>488447</v>
       </c>
       <c r="R34" t="n">
-        <v>7014566</v>
+        <v>7014717</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129073989</v>
+        <v>129078041</v>
       </c>
       <c r="B35" t="n">
-        <v>100866</v>
+        <v>99012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4536,27 +4536,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4565,13 +4565,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488436</v>
+        <v>488550</v>
       </c>
       <c r="R35" t="n">
-        <v>7014587</v>
+        <v>7014460</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129081210</v>
+        <v>129076105</v>
       </c>
       <c r="B36" t="n">
         <v>100866</v>
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488580</v>
+        <v>488531</v>
       </c>
       <c r="R36" t="n">
-        <v>7014585</v>
+        <v>7014566</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129074467</v>
+        <v>129073989</v>
       </c>
       <c r="B37" t="n">
         <v>100866</v>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488447</v>
+        <v>488436</v>
       </c>
       <c r="R37" t="n">
-        <v>7014717</v>
+        <v>7014587</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129078041</v>
+        <v>129081210</v>
       </c>
       <c r="B38" t="n">
-        <v>99012</v>
+        <v>100866</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,27 +4857,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488550</v>
+        <v>488580</v>
       </c>
       <c r="R38" t="n">
-        <v>7014460</v>
+        <v>7014585</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5441,48 +5441,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129076936</v>
+        <v>129073539</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488552</v>
+        <v>488418</v>
       </c>
       <c r="R43" t="n">
-        <v>7014587</v>
+        <v>7014546</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5526,26 +5531,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5685,53 +5670,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129073539</v>
+        <v>129076936</v>
       </c>
       <c r="B45" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488418</v>
+        <v>488552</v>
       </c>
       <c r="R45" t="n">
-        <v>7014546</v>
+        <v>7014587</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5775,6 +5755,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5792,48 +5792,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080537</v>
+        <v>129077994</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488632</v>
+        <v>488544</v>
       </c>
       <c r="R46" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5865,11 +5870,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5882,26 +5882,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5919,10 +5899,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129072070</v>
+        <v>129076866</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5930,37 +5910,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488455</v>
+        <v>488575</v>
       </c>
       <c r="R47" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5992,6 +5977,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6018,12 +6008,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6041,10 +6031,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129076866</v>
+        <v>129080537</v>
       </c>
       <c r="B48" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6052,42 +6042,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488575</v>
+        <v>488632</v>
       </c>
       <c r="R48" t="n">
-        <v>7014596</v>
+        <v>7014478</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6121,7 +6106,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6150,12 +6135,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6173,53 +6158,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129077994</v>
+        <v>129072070</v>
       </c>
       <c r="B49" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488544</v>
+        <v>488455</v>
       </c>
       <c r="R49" t="n">
         <v>7014457</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6263,6 +6243,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6417,48 +6417,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129070117</v>
+        <v>129072360</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488317</v>
+        <v>488465</v>
       </c>
       <c r="R51" t="n">
-        <v>7014450</v>
+        <v>7014498</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6485,26 +6490,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I gammal granskog med gott om död ved.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6517,26 +6507,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6554,53 +6524,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129081155</v>
+        <v>129070117</v>
       </c>
       <c r="B52" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488569</v>
+        <v>488317</v>
       </c>
       <c r="R52" t="n">
-        <v>7014529</v>
+        <v>7014450</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6627,14 +6592,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
+          <t>I gammal granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6653,22 +6628,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6686,10 +6661,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129072360</v>
+        <v>129081155</v>
       </c>
       <c r="B53" t="n">
-        <v>100866</v>
+        <v>80182</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6697,27 +6672,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6726,10 +6701,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488465</v>
+        <v>488569</v>
       </c>
       <c r="R53" t="n">
-        <v>7014498</v>
+        <v>7014529</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -6764,6 +6739,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +6756,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7432,48 +7432,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129073935</v>
+        <v>129070439</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>103200</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488409</v>
+        <v>488363</v>
       </c>
       <c r="R59" t="n">
-        <v>7014521</v>
+        <v>7014442</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7500,11 +7505,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7517,26 +7537,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129073198</v>
+        <v>129073935</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7565,47 +7565,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488422</v>
+        <v>488409</v>
       </c>
       <c r="R60" t="n">
-        <v>7014530</v>
+        <v>7014521</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7637,11 +7627,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7656,14 +7641,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7681,53 +7676,58 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129070439</v>
+        <v>129073198</v>
       </c>
       <c r="B61" t="n">
-        <v>103200</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488363</v>
+        <v>488422</v>
       </c>
       <c r="R61" t="n">
-        <v>7014442</v>
+        <v>7014530</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7754,24 +7754,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7786,6 +7776,16 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8662,38 +8662,52 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129079226</v>
+        <v>129077294</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8702,13 +8716,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488679</v>
+        <v>488548</v>
       </c>
       <c r="R69" t="n">
-        <v>7014391</v>
+        <v>7014573</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8735,14 +8749,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8757,26 +8781,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8794,52 +8798,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129077294</v>
+        <v>129079226</v>
       </c>
       <c r="B70" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8848,13 +8838,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488548</v>
+        <v>488679</v>
       </c>
       <c r="R70" t="n">
-        <v>7014573</v>
+        <v>7014391</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8881,24 +8871,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8913,6 +8893,26 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9442,48 +9442,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215411</v>
+        <v>129213773</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>91997</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488525</v>
+        <v>488662</v>
       </c>
       <c r="R75" t="n">
-        <v>7014363</v>
+        <v>7014466</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9512,7 +9517,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9522,12 +9527,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9579,53 +9579,58 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129213773</v>
+        <v>129210501</v>
       </c>
       <c r="B76" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488662</v>
+        <v>488472</v>
       </c>
       <c r="R76" t="n">
-        <v>7014466</v>
+        <v>7014695</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9654,7 +9659,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9664,7 +9669,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9693,12 +9703,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9716,38 +9726,47 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129210501</v>
+        <v>129213412</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -9757,17 +9776,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488472</v>
+        <v>488623</v>
       </c>
       <c r="R77" t="n">
-        <v>7014695</v>
+        <v>7014540</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9796,7 +9815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9806,12 +9825,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9826,26 +9845,6 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9863,64 +9862,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129213412</v>
+        <v>129215411</v>
       </c>
       <c r="B78" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488623</v>
+        <v>488525</v>
       </c>
       <c r="R78" t="n">
-        <v>7014540</v>
+        <v>7014363</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9952,7 +9932,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9962,12 +9942,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9982,6 +9962,26 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10136,48 +10136,53 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129211802</v>
+        <v>129212656</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488591</v>
+        <v>488569</v>
       </c>
       <c r="R80" t="n">
-        <v>7014632</v>
+        <v>7014485</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10206,7 +10211,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10216,7 +10221,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10231,26 +10236,6 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10268,10 +10253,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129212598</v>
+        <v>129214932</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10279,37 +10264,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488580</v>
+        <v>488526</v>
       </c>
       <c r="R81" t="n">
-        <v>7014484</v>
+        <v>7014439</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10338,7 +10328,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10348,12 +10338,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10382,12 +10372,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10405,10 +10395,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129214932</v>
+        <v>129211802</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10416,42 +10406,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488526</v>
+        <v>488591</v>
       </c>
       <c r="R82" t="n">
-        <v>7014439</v>
+        <v>7014632</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10480,7 +10465,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10490,12 +10475,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10524,12 +10504,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10547,50 +10527,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129212656</v>
+        <v>129212598</v>
       </c>
       <c r="B83" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488569</v>
+        <v>488580</v>
       </c>
       <c r="R83" t="n">
-        <v>7014485</v>
+        <v>7014484</v>
       </c>
       <c r="S83" t="n">
         <v>9</v>
@@ -10622,7 +10597,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10632,7 +10607,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10647,6 +10627,26 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11294,10 +11294,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129209204</v>
+        <v>129215504</v>
       </c>
       <c r="B89" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11305,42 +11305,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488495</v>
+        <v>488457</v>
       </c>
       <c r="R89" t="n">
-        <v>7014661</v>
+        <v>7014436</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11369,7 +11364,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11379,7 +11374,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11394,26 +11389,6 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11431,53 +11406,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129214590</v>
+        <v>129215229</v>
       </c>
       <c r="B90" t="n">
-        <v>99012</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488566</v>
+        <v>488501</v>
       </c>
       <c r="R90" t="n">
-        <v>7014423</v>
+        <v>7014416</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11506,7 +11476,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11516,7 +11486,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11548,52 +11518,38 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129211354</v>
+        <v>129213105</v>
       </c>
       <c r="B91" t="n">
-        <v>98678</v>
+        <v>100866</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11602,13 +11558,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488586</v>
+        <v>488627</v>
       </c>
       <c r="R91" t="n">
-        <v>7014612</v>
+        <v>7014454</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11637,7 +11593,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11647,12 +11603,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11684,10 +11635,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215504</v>
+        <v>129209204</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11695,37 +11646,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488457</v>
+        <v>488495</v>
       </c>
       <c r="R92" t="n">
-        <v>7014436</v>
+        <v>7014661</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11754,7 +11710,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11764,7 +11720,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11779,6 +11735,26 @@
       <c r="AH92" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11796,48 +11772,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215229</v>
+        <v>129214590</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>99012</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488501</v>
+        <v>488566</v>
       </c>
       <c r="R93" t="n">
-        <v>7014416</v>
+        <v>7014423</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11866,7 +11847,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11876,7 +11857,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11908,38 +11889,52 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129213105</v>
+        <v>129211354</v>
       </c>
       <c r="B94" t="n">
-        <v>100866</v>
+        <v>98678</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11948,13 +11943,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488627</v>
+        <v>488586</v>
       </c>
       <c r="R94" t="n">
-        <v>7014454</v>
+        <v>7014612</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11983,7 +11978,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11993,7 +11988,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13324,38 +13324,43 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129209238</v>
+        <v>129213886</v>
       </c>
       <c r="B105" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -13364,13 +13369,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488489</v>
+        <v>488671</v>
       </c>
       <c r="R105" t="n">
-        <v>7014656</v>
+        <v>7014435</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13399,7 +13404,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13409,7 +13414,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13424,6 +13434,26 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13573,43 +13603,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129213886</v>
+        <v>129209238</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13618,13 +13643,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488671</v>
+        <v>488489</v>
       </c>
       <c r="R107" t="n">
-        <v>7014435</v>
+        <v>7014656</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13653,7 +13678,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13663,12 +13688,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13683,26 +13703,6 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14404,43 +14404,38 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B113" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14449,13 +14444,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R113" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14484,7 +14479,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14494,7 +14489,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14509,6 +14509,26 @@
       <c r="AH113" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14526,38 +14546,43 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214896</v>
+        <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>57727</v>
+        <v>100866</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14566,13 +14591,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488525</v>
+        <v>488543</v>
       </c>
       <c r="R114" t="n">
-        <v>7014424</v>
+        <v>7014418</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14601,7 +14626,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14611,12 +14636,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14631,26 +14651,6 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15204,53 +15204,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129210698</v>
+        <v>129212992</v>
       </c>
       <c r="B119" t="n">
-        <v>92480</v>
+        <v>79041</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488475</v>
+        <v>488605</v>
       </c>
       <c r="R119" t="n">
-        <v>7014707</v>
+        <v>7014461</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15279,7 +15274,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15289,7 +15284,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15304,6 +15299,26 @@
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15321,7 +15336,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129212992</v>
+        <v>129209446</v>
       </c>
       <c r="B120" t="n">
         <v>79041</v>
@@ -15356,10 +15371,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488605</v>
+        <v>488454</v>
       </c>
       <c r="R120" t="n">
-        <v>7014461</v>
+        <v>7014635</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15391,7 +15406,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15401,7 +15416,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15430,12 +15445,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15453,10 +15468,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129209446</v>
+        <v>129214468</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15464,37 +15479,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488454</v>
+        <v>488595</v>
       </c>
       <c r="R121" t="n">
-        <v>7014635</v>
+        <v>7014471</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15523,7 +15543,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15533,7 +15553,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15562,12 +15587,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15585,38 +15610,38 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129214468</v>
+        <v>129210698</v>
       </c>
       <c r="B122" t="n">
-        <v>57727</v>
+        <v>92480</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -15625,13 +15650,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488595</v>
+        <v>488475</v>
       </c>
       <c r="R122" t="n">
-        <v>7014471</v>
+        <v>7014707</v>
       </c>
       <c r="S122" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15660,7 +15685,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15670,12 +15695,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15690,26 +15710,6 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129057988</v>
+        <v>129057979</v>
       </c>
       <c r="B2" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488339</v>
+        <v>488344</v>
       </c>
       <c r="R2" t="n">
-        <v>7014419</v>
+        <v>7014426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129057979</v>
+        <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>100892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488344</v>
+        <v>488339</v>
       </c>
       <c r="R3" t="n">
-        <v>7014426</v>
+        <v>7014419</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129057981</v>
+        <v>129057980</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488325</v>
+        <v>488330</v>
       </c>
       <c r="R10" t="n">
-        <v>7014409</v>
+        <v>7014417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,7 +1588,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129057980</v>
+        <v>129057981</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488330</v>
+        <v>488325</v>
       </c>
       <c r="R11" t="n">
-        <v>7014417</v>
+        <v>7014409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129074228</v>
+        <v>129076254</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,47 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488431</v>
+        <v>488581</v>
       </c>
       <c r="R14" t="n">
-        <v>7014633</v>
+        <v>7014597</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,24 +1977,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2023,22 +2003,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2056,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129076254</v>
+        <v>129080431</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2091,13 +2071,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488581</v>
+        <v>488667</v>
       </c>
       <c r="R15" t="n">
-        <v>7014597</v>
+        <v>7014453</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2129,11 +2109,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2150,12 +2125,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2165,7 +2140,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2183,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129080431</v>
+        <v>129074673</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2218,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488667</v>
+        <v>488470</v>
       </c>
       <c r="R16" t="n">
-        <v>7014453</v>
+        <v>7014593</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
@@ -2305,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074673</v>
+        <v>129079967</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2340,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488470</v>
+        <v>488745</v>
       </c>
       <c r="R17" t="n">
-        <v>7014593</v>
+        <v>7014497</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2427,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129079967</v>
+        <v>129074228</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,37 +2413,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488745</v>
+        <v>488431</v>
       </c>
       <c r="R18" t="n">
-        <v>7014497</v>
+        <v>7014633</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,11 +2480,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2552,7 +2552,7 @@
         <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3149,38 +3149,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129071736</v>
+        <v>129072249</v>
       </c>
       <c r="B24" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3189,13 +3194,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488410</v>
+        <v>488459</v>
       </c>
       <c r="R24" t="n">
-        <v>7014448</v>
+        <v>7014467</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3227,6 +3232,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3239,6 +3249,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3256,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129075203</v>
+        <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,13 +3326,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488533</v>
+        <v>488410</v>
       </c>
       <c r="R25" t="n">
-        <v>7014663</v>
+        <v>7014448</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,43 +3393,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129072249</v>
+        <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>100892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3408,13 +3433,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488459</v>
+        <v>488533</v>
       </c>
       <c r="R26" t="n">
-        <v>7014467</v>
+        <v>7014663</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,11 +3471,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3463,26 +3483,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,12 +3520,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3642,53 +3642,58 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129078582</v>
+        <v>129073330</v>
       </c>
       <c r="B28" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488570</v>
+        <v>488408</v>
       </c>
       <c r="R28" t="n">
-        <v>7014409</v>
+        <v>7014549</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3720,6 +3725,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3746,12 +3756,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3769,58 +3779,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129073330</v>
+        <v>129078582</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488408</v>
+        <v>488570</v>
       </c>
       <c r="R29" t="n">
-        <v>7014549</v>
+        <v>7014409</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3852,11 +3857,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3906,38 +3906,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129081091</v>
+        <v>129078041</v>
       </c>
       <c r="B30" t="n">
-        <v>80147</v>
+        <v>99038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>219880</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3946,13 +3946,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488575</v>
+        <v>488550</v>
       </c>
       <c r="R30" t="n">
-        <v>7014525</v>
+        <v>7014460</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3984,11 +3984,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4001,26 +3996,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4038,48 +4013,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129080078</v>
+        <v>129076105</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>100892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488760</v>
+        <v>488531</v>
       </c>
       <c r="R31" t="n">
-        <v>7014511</v>
+        <v>7014566</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4123,26 +4103,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4160,48 +4120,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129079878</v>
+        <v>129073989</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>100892</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488787</v>
+        <v>488436</v>
       </c>
       <c r="R32" t="n">
-        <v>7014483</v>
+        <v>7014587</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4245,26 +4210,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4282,67 +4227,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129071599</v>
+        <v>129081210</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>100892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488409</v>
+        <v>488580</v>
       </c>
       <c r="R33" t="n">
-        <v>7014470</v>
+        <v>7014585</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4369,24 +4300,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4421,7 +4337,7 @@
         <v>129074467</v>
       </c>
       <c r="B34" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4525,38 +4441,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129078041</v>
+        <v>129081091</v>
       </c>
       <c r="B35" t="n">
-        <v>99012</v>
+        <v>80147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219880</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4565,13 +4481,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488550</v>
+        <v>488575</v>
       </c>
       <c r="R35" t="n">
-        <v>7014460</v>
+        <v>7014525</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4603,6 +4519,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4615,6 +4536,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4632,53 +4573,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129076105</v>
+        <v>129080078</v>
       </c>
       <c r="B36" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488531</v>
+        <v>488760</v>
       </c>
       <c r="R36" t="n">
-        <v>7014566</v>
+        <v>7014511</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4722,6 +4658,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4739,53 +4695,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129073989</v>
+        <v>129079878</v>
       </c>
       <c r="B37" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488436</v>
+        <v>488787</v>
       </c>
       <c r="R37" t="n">
-        <v>7014587</v>
+        <v>7014483</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4829,6 +4780,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4846,53 +4817,67 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129081210</v>
+        <v>129071599</v>
       </c>
       <c r="B38" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488580</v>
+        <v>488409</v>
       </c>
       <c r="R38" t="n">
-        <v>7014585</v>
+        <v>7014470</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4919,9 +4904,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129073539</v>
       </c>
       <c r="B43" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5792,53 +5792,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129077994</v>
+        <v>129080537</v>
       </c>
       <c r="B46" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488544</v>
+        <v>488632</v>
       </c>
       <c r="R46" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5870,6 +5865,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5882,6 +5882,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5899,10 +5919,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129076866</v>
+        <v>129072070</v>
       </c>
       <c r="B47" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5910,42 +5930,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488575</v>
+        <v>488455</v>
       </c>
       <c r="R47" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5977,11 +5992,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6008,12 +6018,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6031,48 +6041,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129080537</v>
+        <v>129077994</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>100892</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488632</v>
+        <v>488544</v>
       </c>
       <c r="R48" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6104,11 +6119,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6121,26 +6131,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6158,10 +6148,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129072070</v>
+        <v>129076866</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>91837</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6169,37 +6159,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488455</v>
+        <v>488575</v>
       </c>
       <c r="R49" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6231,6 +6226,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129079479</v>
+        <v>129070117</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6291,44 +6291,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488806</v>
+        <v>488317</v>
       </c>
       <c r="R50" t="n">
-        <v>7014416</v>
+        <v>7014450</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6358,14 +6348,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
+          <t>I gammal granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6417,10 +6417,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129072360</v>
+        <v>129081155</v>
       </c>
       <c r="B51" t="n">
-        <v>100866</v>
+        <v>80182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6428,27 +6428,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488465</v>
+        <v>488569</v>
       </c>
       <c r="R51" t="n">
-        <v>7014498</v>
+        <v>7014529</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -6495,6 +6495,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6507,6 +6512,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6524,10 +6549,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129070117</v>
+        <v>129079479</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,34 +6560,44 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488317</v>
+        <v>488806</v>
       </c>
       <c r="R52" t="n">
-        <v>7014450</v>
+        <v>7014416</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6592,24 +6627,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6638,12 +6663,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6661,10 +6686,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129081155</v>
+        <v>129072360</v>
       </c>
       <c r="B53" t="n">
-        <v>80182</v>
+        <v>100892</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6672,27 +6697,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6701,10 +6726,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488569</v>
+        <v>488465</v>
       </c>
       <c r="R53" t="n">
-        <v>7014529</v>
+        <v>7014498</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -6739,11 +6764,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6756,26 +6776,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6793,32 +6793,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B54" t="n">
-        <v>91997</v>
+        <v>91837</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R54" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -6869,6 +6869,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6920,32 +6925,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129071884</v>
+        <v>129071923</v>
       </c>
       <c r="B55" t="n">
-        <v>91827</v>
+        <v>91992</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6960,10 +6965,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488391</v>
+        <v>488400</v>
       </c>
       <c r="R55" t="n">
-        <v>7014430</v>
+        <v>7014435</v>
       </c>
       <c r="S55" t="n">
         <v>7</v>
@@ -6996,11 +7001,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7055,7 +7055,7 @@
         <v>129077981</v>
       </c>
       <c r="B56" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7432,53 +7432,58 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129070439</v>
+        <v>129073198</v>
       </c>
       <c r="B59" t="n">
-        <v>103200</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488363</v>
+        <v>488422</v>
       </c>
       <c r="R59" t="n">
-        <v>7014442</v>
+        <v>7014530</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7505,24 +7510,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7537,6 +7532,16 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7554,48 +7559,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129073935</v>
+        <v>129070439</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>103226</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488409</v>
+        <v>488363</v>
       </c>
       <c r="R60" t="n">
-        <v>7014521</v>
+        <v>7014442</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7622,11 +7632,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7639,26 +7664,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7676,10 +7681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129073198</v>
+        <v>129073935</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7687,47 +7692,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488422</v>
+        <v>488409</v>
       </c>
       <c r="R61" t="n">
-        <v>7014530</v>
+        <v>7014521</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7759,11 +7754,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7778,14 +7768,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7933,7 +7933,7 @@
         <v>129073694</v>
       </c>
       <c r="B63" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129072652</v>
+        <v>129078147</v>
       </c>
       <c r="B64" t="n">
-        <v>100866</v>
+        <v>103226</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8048,27 +8048,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488514</v>
+        <v>488557</v>
       </c>
       <c r="R64" t="n">
-        <v>7014547</v>
+        <v>7014445</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8110,9 +8110,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8144,38 +8154,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129078147</v>
+        <v>129074640</v>
       </c>
       <c r="B65" t="n">
-        <v>103200</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8184,13 +8194,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488557</v>
+        <v>488472</v>
       </c>
       <c r="R65" t="n">
-        <v>7014445</v>
+        <v>7014599</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8217,19 +8227,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8244,6 +8249,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8261,7 +8286,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129074640</v>
+        <v>129078537</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -8295,19 +8320,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488472</v>
+        <v>488573</v>
       </c>
       <c r="R66" t="n">
-        <v>7014599</v>
+        <v>7014399</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8341,7 +8371,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8370,12 +8400,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8393,7 +8423,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129078537</v>
+        <v>129079063</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -8427,24 +8457,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488573</v>
+        <v>488655</v>
       </c>
       <c r="R67" t="n">
-        <v>7014399</v>
+        <v>7014417</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8478,7 +8503,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8507,12 +8532,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8530,38 +8555,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129079063</v>
+        <v>129072652</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>100892</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8570,13 +8595,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488655</v>
+        <v>488514</v>
       </c>
       <c r="R68" t="n">
-        <v>7014417</v>
+        <v>7014547</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8608,11 +8633,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8625,26 +8645,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8662,52 +8662,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129077294</v>
+        <v>129079226</v>
       </c>
       <c r="B69" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8716,13 +8702,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488548</v>
+        <v>488679</v>
       </c>
       <c r="R69" t="n">
-        <v>7014573</v>
+        <v>7014391</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8749,24 +8735,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8781,6 +8757,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8798,38 +8794,52 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129079226</v>
+        <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8838,13 +8848,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488679</v>
+        <v>488548</v>
       </c>
       <c r="R70" t="n">
-        <v>7014391</v>
+        <v>7014573</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8871,14 +8881,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8893,26 +8913,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98577</v>
+        <v>98603</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129213773</v>
       </c>
       <c r="B75" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9462,12 +9462,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129210501</v>
+        <v>129215411</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9590,47 +9590,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488472</v>
+        <v>488525</v>
       </c>
       <c r="R76" t="n">
-        <v>7014695</v>
+        <v>7014363</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9659,7 +9649,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9669,12 +9659,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9703,12 +9693,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9726,47 +9716,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129213412</v>
+        <v>129210501</v>
       </c>
       <c r="B77" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -9776,17 +9757,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488623</v>
+        <v>488472</v>
       </c>
       <c r="R77" t="n">
-        <v>7014540</v>
+        <v>7014695</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9815,7 +9796,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9825,12 +9806,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9845,6 +9826,26 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9862,45 +9863,64 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215411</v>
+        <v>129213412</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488525</v>
+        <v>488623</v>
       </c>
       <c r="R78" t="n">
-        <v>7014363</v>
+        <v>7014540</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9932,7 +9952,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9942,12 +9962,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9962,26 +9982,6 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10019,12 +10019,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10136,50 +10136,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129212656</v>
+        <v>129212598</v>
       </c>
       <c r="B80" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488569</v>
+        <v>488580</v>
       </c>
       <c r="R80" t="n">
-        <v>7014485</v>
+        <v>7014484</v>
       </c>
       <c r="S80" t="n">
         <v>9</v>
@@ -10211,7 +10206,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10221,7 +10216,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10236,6 +10236,26 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10253,10 +10273,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129214932</v>
+        <v>129211802</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10264,42 +10284,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488526</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7014439</v>
+        <v>7014632</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10328,7 +10343,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10338,12 +10353,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10372,12 +10382,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10395,10 +10405,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129211802</v>
+        <v>129214932</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10406,37 +10416,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488591</v>
+        <v>488526</v>
       </c>
       <c r="R82" t="n">
-        <v>7014632</v>
+        <v>7014439</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10465,7 +10480,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10475,7 +10490,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10504,12 +10524,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10527,45 +10547,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129212598</v>
+        <v>129212656</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>100892</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488580</v>
+        <v>488569</v>
       </c>
       <c r="R83" t="n">
-        <v>7014484</v>
+        <v>7014485</v>
       </c>
       <c r="S83" t="n">
         <v>9</v>
@@ -10597,7 +10622,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10607,12 +10632,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10627,26 +10647,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10684,12 +10684,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129212289</v>
+        <v>129215312</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488615</v>
+        <v>488534</v>
       </c>
       <c r="R85" t="n">
-        <v>7014544</v>
+        <v>7014397</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10901,26 +10901,6 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11182,7 +11162,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215312</v>
+        <v>129212289</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -11217,13 +11197,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R88" t="n">
-        <v>7014397</v>
+        <v>7014544</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11252,7 +11232,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11262,7 +11242,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11277,6 +11257,26 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215504</v>
+        <v>129215229</v>
       </c>
       <c r="B89" t="n">
         <v>79041</v>
@@ -11329,13 +11329,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488457</v>
+        <v>488501</v>
       </c>
       <c r="R89" t="n">
-        <v>7014436</v>
+        <v>7014416</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11406,7 +11406,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215229</v>
+        <v>129215504</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -11441,13 +11441,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488501</v>
+        <v>488457</v>
       </c>
       <c r="R90" t="n">
-        <v>7014416</v>
+        <v>7014436</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11518,38 +11518,52 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129213105</v>
+        <v>129211354</v>
       </c>
       <c r="B91" t="n">
-        <v>100866</v>
+        <v>98704</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11558,13 +11572,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488627</v>
+        <v>488586</v>
       </c>
       <c r="R91" t="n">
-        <v>7014454</v>
+        <v>7014612</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11593,7 +11607,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11603,7 +11617,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11635,38 +11654,38 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129209204</v>
+        <v>129214590</v>
       </c>
       <c r="B92" t="n">
-        <v>91560</v>
+        <v>99038</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11675,10 +11694,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488495</v>
+        <v>488566</v>
       </c>
       <c r="R92" t="n">
-        <v>7014661</v>
+        <v>7014423</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11710,7 +11729,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11720,7 +11739,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11735,26 +11754,6 @@
       <c r="AH92" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11772,38 +11771,38 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129214590</v>
+        <v>129209204</v>
       </c>
       <c r="B93" t="n">
-        <v>99012</v>
+        <v>91558</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11812,10 +11811,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488566</v>
+        <v>488495</v>
       </c>
       <c r="R93" t="n">
-        <v>7014423</v>
+        <v>7014661</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11847,7 +11846,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11857,7 +11856,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11872,6 +11871,26 @@
       <c r="AH93" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11889,52 +11908,38 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129211354</v>
+        <v>129213105</v>
       </c>
       <c r="B94" t="n">
-        <v>98678</v>
+        <v>100892</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11943,13 +11948,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488586</v>
+        <v>488627</v>
       </c>
       <c r="R94" t="n">
-        <v>7014612</v>
+        <v>7014454</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11978,7 +11983,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11988,12 +11993,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12028,7 +12028,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12390,64 +12390,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129214807</v>
+        <v>129210843</v>
       </c>
       <c r="B98" t="n">
-        <v>98678</v>
+        <v>100892</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488555</v>
+        <v>488496</v>
       </c>
       <c r="R98" t="n">
-        <v>7014416</v>
+        <v>7014638</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12479,7 +12465,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12489,12 +12475,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12526,50 +12507,64 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129210843</v>
+        <v>129214807</v>
       </c>
       <c r="B99" t="n">
-        <v>100866</v>
+        <v>98704</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488496</v>
+        <v>488555</v>
       </c>
       <c r="R99" t="n">
-        <v>7014638</v>
+        <v>7014416</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -12601,7 +12596,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12611,7 +12606,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12646,7 +12646,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12915,10 +12915,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129210160</v>
+        <v>129209724</v>
       </c>
       <c r="B102" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12969,10 +12969,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488446</v>
+        <v>488435</v>
       </c>
       <c r="R102" t="n">
-        <v>7014684</v>
+        <v>7014641</v>
       </c>
       <c r="S102" t="n">
         <v>9</v>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13014,12 +13014,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Minst 76 plantor inom ca 2,5 m2 yta.</t>
+          <t>Minst 80 plantor inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13051,10 +13051,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129209724</v>
+        <v>129210160</v>
       </c>
       <c r="B103" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488435</v>
+        <v>488446</v>
       </c>
       <c r="R103" t="n">
-        <v>7014641</v>
+        <v>7014684</v>
       </c>
       <c r="S103" t="n">
         <v>9</v>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13150,12 +13150,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 1,5 m2 yta.</t>
+          <t>Minst 76 plantor inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13187,53 +13187,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129212827</v>
+        <v>129213534</v>
       </c>
       <c r="B104" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488535</v>
+        <v>488675</v>
       </c>
       <c r="R104" t="n">
-        <v>7014455</v>
+        <v>7014494</v>
       </c>
       <c r="S104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13262,7 +13257,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13272,7 +13267,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13301,12 +13296,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13471,45 +13466,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129213534</v>
+        <v>129209238</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>100892</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488675</v>
+        <v>488489</v>
       </c>
       <c r="R106" t="n">
-        <v>7014494</v>
+        <v>7014656</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13566,26 +13566,6 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13603,38 +13583,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129209238</v>
+        <v>129212827</v>
       </c>
       <c r="B107" t="n">
-        <v>100866</v>
+        <v>91992</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13643,13 +13623,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488489</v>
+        <v>488535</v>
       </c>
       <c r="R107" t="n">
-        <v>7014656</v>
+        <v>7014455</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13678,7 +13658,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13688,7 +13668,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13703,6 +13683,26 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13855,7 +13855,7 @@
         <v>129214838</v>
       </c>
       <c r="B109" t="n">
-        <v>98582</v>
+        <v>98608</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>129211241</v>
       </c>
       <c r="B117" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>129211912</v>
       </c>
       <c r="B118" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15204,10 +15204,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129212992</v>
+        <v>129214468</v>
       </c>
       <c r="B119" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15215,37 +15215,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488605</v>
+        <v>488595</v>
       </c>
       <c r="R119" t="n">
-        <v>7014461</v>
+        <v>7014471</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15274,7 +15279,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15284,7 +15289,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15313,12 +15323,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15336,48 +15346,53 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129209446</v>
+        <v>129210698</v>
       </c>
       <c r="B120" t="n">
-        <v>79041</v>
+        <v>92494</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488454</v>
+        <v>488475</v>
       </c>
       <c r="R120" t="n">
-        <v>7014635</v>
+        <v>7014707</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15406,7 +15421,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15416,7 +15431,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15431,26 +15446,6 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15468,10 +15463,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129214468</v>
+        <v>129209446</v>
       </c>
       <c r="B121" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15479,42 +15474,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488595</v>
+        <v>488454</v>
       </c>
       <c r="R121" t="n">
-        <v>7014471</v>
+        <v>7014635</v>
       </c>
       <c r="S121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15543,7 +15533,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15553,12 +15543,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15587,12 +15572,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15610,53 +15595,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129210698</v>
+        <v>129212992</v>
       </c>
       <c r="B122" t="n">
-        <v>92480</v>
+        <v>79041</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488475</v>
+        <v>488605</v>
       </c>
       <c r="R122" t="n">
-        <v>7014707</v>
+        <v>7014461</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15685,7 +15665,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15695,7 +15675,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15710,6 +15690,26 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15867,7 +15867,7 @@
         <v>129349154</v>
       </c>
       <c r="B124" t="n">
-        <v>92215</v>
+        <v>92230</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129057980</v>
+        <v>129057981</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488330</v>
+        <v>488325</v>
       </c>
       <c r="R10" t="n">
-        <v>7014417</v>
+        <v>7014409</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,7 +1588,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129057981</v>
+        <v>129057980</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488325</v>
+        <v>488330</v>
       </c>
       <c r="R11" t="n">
-        <v>7014409</v>
+        <v>7014417</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129081134</v>
+        <v>129079151</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,27 +2774,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488567</v>
+        <v>488670</v>
       </c>
       <c r="R21" t="n">
-        <v>7014534</v>
+        <v>7014411</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129079151</v>
+        <v>129081134</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,27 +2906,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488670</v>
+        <v>488567</v>
       </c>
       <c r="R22" t="n">
-        <v>7014411</v>
+        <v>7014534</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,22 +2994,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3289,7 +3289,7 @@
         <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,58 +3642,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129073330</v>
+        <v>129078582</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488408</v>
+        <v>488570</v>
       </c>
       <c r="R28" t="n">
-        <v>7014549</v>
+        <v>7014409</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3725,11 +3720,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3756,12 +3746,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3779,53 +3769,58 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129078582</v>
+        <v>129073330</v>
       </c>
       <c r="B29" t="n">
-        <v>91992</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488570</v>
+        <v>488408</v>
       </c>
       <c r="R29" t="n">
-        <v>7014409</v>
+        <v>7014549</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3857,6 +3852,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3906,38 +3906,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129078041</v>
+        <v>129081091</v>
       </c>
       <c r="B30" t="n">
-        <v>99038</v>
+        <v>80147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3946,13 +3946,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488550</v>
+        <v>488575</v>
       </c>
       <c r="R30" t="n">
-        <v>7014460</v>
+        <v>7014525</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3984,6 +3984,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3996,6 +4001,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4016,7 +4041,7 @@
         <v>129076105</v>
       </c>
       <c r="B31" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4123,7 +4148,7 @@
         <v>129073989</v>
       </c>
       <c r="B32" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4230,7 +4255,7 @@
         <v>129081210</v>
       </c>
       <c r="B33" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4337,7 +4362,7 @@
         <v>129074467</v>
       </c>
       <c r="B34" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4441,10 +4466,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129081091</v>
+        <v>129080078</v>
       </c>
       <c r="B35" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4452,42 +4477,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488575</v>
+        <v>488760</v>
       </c>
       <c r="R35" t="n">
-        <v>7014525</v>
+        <v>7014511</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4519,11 +4539,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4540,22 +4555,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4573,7 +4588,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129080078</v>
+        <v>129079878</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4608,13 +4623,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488760</v>
+        <v>488787</v>
       </c>
       <c r="R36" t="n">
-        <v>7014511</v>
+        <v>7014483</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4695,10 +4710,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129079878</v>
+        <v>129071599</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4706,37 +4721,56 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488787</v>
+        <v>488409</v>
       </c>
       <c r="R37" t="n">
-        <v>7014483</v>
+        <v>7014470</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4763,11 +4797,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4780,26 +4829,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4817,67 +4846,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129071599</v>
+        <v>129078041</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>99039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488409</v>
+        <v>488550</v>
       </c>
       <c r="R38" t="n">
-        <v>7014470</v>
+        <v>7014460</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4904,24 +4919,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5441,53 +5441,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129073539</v>
+        <v>129076722</v>
       </c>
       <c r="B43" t="n">
-        <v>100892</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488418</v>
+        <v>488602</v>
       </c>
       <c r="R43" t="n">
-        <v>7014546</v>
+        <v>7014595</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5531,6 +5526,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5548,7 +5563,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129076722</v>
+        <v>129076936</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -5583,13 +5598,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488602</v>
+        <v>488552</v>
       </c>
       <c r="R44" t="n">
-        <v>7014595</v>
+        <v>7014587</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5670,48 +5685,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129076936</v>
+        <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>100894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488552</v>
+        <v>488418</v>
       </c>
       <c r="R45" t="n">
-        <v>7014587</v>
+        <v>7014546</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5755,26 +5775,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080537</v>
+        <v>129076866</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>91838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5803,37 +5803,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488632</v>
+        <v>488575</v>
       </c>
       <c r="R46" t="n">
-        <v>7014478</v>
+        <v>7014596</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5867,7 +5872,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5896,12 +5901,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5919,48 +5924,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129072070</v>
+        <v>129077994</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>100894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488455</v>
+        <v>488544</v>
       </c>
       <c r="R47" t="n">
         <v>7014457</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6004,26 +6014,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6041,53 +6031,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129077994</v>
+        <v>129080537</v>
       </c>
       <c r="B48" t="n">
-        <v>100892</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488544</v>
+        <v>488632</v>
       </c>
       <c r="R48" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6119,6 +6104,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6131,6 +6121,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6148,10 +6158,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129076866</v>
+        <v>129072070</v>
       </c>
       <c r="B49" t="n">
-        <v>91837</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6159,42 +6169,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488575</v>
+        <v>488455</v>
       </c>
       <c r="R49" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6226,11 +6231,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6689,7 +6689,7 @@
         <v>129072360</v>
       </c>
       <c r="B53" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6793,38 +6793,47 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129071884</v>
+        <v>129077981</v>
       </c>
       <c r="B54" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6833,13 +6842,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488391</v>
+        <v>488516</v>
       </c>
       <c r="R54" t="n">
-        <v>7014430</v>
+        <v>7014462</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6866,14 +6875,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6888,26 +6907,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6925,32 +6924,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B55" t="n">
-        <v>91992</v>
+        <v>91838</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6965,10 +6964,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R55" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S55" t="n">
         <v>7</v>
@@ -7001,6 +7000,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7052,10 +7056,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129077981</v>
+        <v>129071923</v>
       </c>
       <c r="B56" t="n">
-        <v>98704</v>
+        <v>91993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7063,36 +7067,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7101,13 +7096,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488516</v>
+        <v>488400</v>
       </c>
       <c r="R56" t="n">
-        <v>7014462</v>
+        <v>7014435</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7134,26 +7129,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7166,6 +7146,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7186,7 +7186,7 @@
         <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>129070439</v>
       </c>
       <c r="B60" t="n">
-        <v>103226</v>
+        <v>103228</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>129073694</v>
       </c>
       <c r="B63" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129078147</v>
+        <v>129072652</v>
       </c>
       <c r="B64" t="n">
-        <v>103226</v>
+        <v>100894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8048,27 +8048,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488557</v>
+        <v>488514</v>
       </c>
       <c r="R64" t="n">
-        <v>7014445</v>
+        <v>7014547</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8110,19 +8110,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8154,38 +8144,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129074640</v>
+        <v>129078147</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>103228</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8194,13 +8184,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488472</v>
+        <v>488557</v>
       </c>
       <c r="R65" t="n">
-        <v>7014599</v>
+        <v>7014445</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8227,14 +8217,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8249,26 +8244,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8286,7 +8261,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129078537</v>
+        <v>129074640</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -8320,24 +8295,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488573</v>
+        <v>488472</v>
       </c>
       <c r="R66" t="n">
-        <v>7014399</v>
+        <v>7014599</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8371,7 +8341,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8400,12 +8370,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8423,7 +8393,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129079063</v>
+        <v>129078537</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -8457,19 +8427,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488655</v>
+        <v>488573</v>
       </c>
       <c r="R67" t="n">
-        <v>7014417</v>
+        <v>7014399</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8503,7 +8478,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8532,12 +8507,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8555,38 +8530,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129072652</v>
+        <v>129079063</v>
       </c>
       <c r="B68" t="n">
-        <v>100892</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8595,13 +8570,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488514</v>
+        <v>488655</v>
       </c>
       <c r="R68" t="n">
-        <v>7014547</v>
+        <v>7014417</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8633,6 +8608,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8645,6 +8625,26 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8797,7 +8797,7 @@
         <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98603</v>
+        <v>98604</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129213773</v>
+        <v>129213412</v>
       </c>
       <c r="B75" t="n">
-        <v>91992</v>
+        <v>98705</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9453,27 +9453,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9482,13 +9496,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488662</v>
+        <v>488623</v>
       </c>
       <c r="R75" t="n">
-        <v>7014466</v>
+        <v>7014540</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9517,7 +9531,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9527,7 +9541,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9542,26 +9561,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9716,58 +9715,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129210501</v>
+        <v>129213773</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488472</v>
+        <v>488662</v>
       </c>
       <c r="R77" t="n">
-        <v>7014695</v>
+        <v>7014466</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9796,7 +9790,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9806,12 +9800,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9840,12 +9829,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9863,47 +9852,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129213412</v>
+        <v>129210501</v>
       </c>
       <c r="B78" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -9913,17 +9893,17 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488623</v>
+        <v>488472</v>
       </c>
       <c r="R78" t="n">
-        <v>7014540</v>
+        <v>7014695</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9952,7 +9932,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9962,12 +9942,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9982,6 +9962,26 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10136,45 +10136,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129212598</v>
+        <v>129212656</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>100894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488580</v>
+        <v>488569</v>
       </c>
       <c r="R80" t="n">
-        <v>7014484</v>
+        <v>7014485</v>
       </c>
       <c r="S80" t="n">
         <v>9</v>
@@ -10206,7 +10211,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10216,12 +10221,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10236,26 +10236,6 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10405,10 +10385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129214932</v>
+        <v>129212598</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10416,42 +10396,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488526</v>
+        <v>488580</v>
       </c>
       <c r="R82" t="n">
-        <v>7014439</v>
+        <v>7014484</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10480,7 +10455,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10490,12 +10465,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10524,12 +10499,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10547,38 +10522,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129212656</v>
+        <v>129214932</v>
       </c>
       <c r="B83" t="n">
-        <v>100892</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10587,13 +10562,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488569</v>
+        <v>488526</v>
       </c>
       <c r="R83" t="n">
-        <v>7014485</v>
+        <v>7014439</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10622,7 +10597,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10632,7 +10607,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10647,6 +10627,26 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215312</v>
+        <v>129212289</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R85" t="n">
-        <v>7014397</v>
+        <v>7014544</v>
       </c>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10901,6 +10901,26 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11162,7 +11182,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129212289</v>
+        <v>129215312</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -11197,13 +11217,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488615</v>
+        <v>488534</v>
       </c>
       <c r="R88" t="n">
-        <v>7014544</v>
+        <v>7014397</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11232,7 +11252,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11242,7 +11262,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11257,26 +11277,6 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11294,10 +11294,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215229</v>
+        <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11305,37 +11305,38 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488501</v>
+        <v>488495</v>
       </c>
       <c r="R89" t="n">
-        <v>7014416</v>
+        <v>7014661</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11364,7 +11365,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11374,7 +11375,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11389,6 +11390,26 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11518,64 +11539,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129211354</v>
+        <v>129215229</v>
       </c>
       <c r="B91" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488586</v>
+        <v>488501</v>
       </c>
       <c r="R91" t="n">
-        <v>7014612</v>
+        <v>7014416</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
@@ -11607,7 +11609,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11617,12 +11619,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11657,7 +11654,7 @@
         <v>129214590</v>
       </c>
       <c r="B92" t="n">
-        <v>99038</v>
+        <v>99039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11771,38 +11768,52 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129209204</v>
+        <v>129211354</v>
       </c>
       <c r="B93" t="n">
-        <v>91558</v>
+        <v>98705</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11811,13 +11822,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488495</v>
+        <v>488586</v>
       </c>
       <c r="R93" t="n">
-        <v>7014661</v>
+        <v>7014612</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11846,7 +11857,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11856,7 +11867,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11871,26 +11887,6 @@
       <c r="AH93" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11911,7 +11907,7 @@
         <v>129213105</v>
       </c>
       <c r="B94" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12028,7 +12024,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12145,7 +12141,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12393,7 +12389,7 @@
         <v>129210843</v>
       </c>
       <c r="B98" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12510,7 +12506,7 @@
         <v>129214807</v>
       </c>
       <c r="B99" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12646,7 +12642,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12782,7 +12778,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12915,10 +12911,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129209724</v>
+        <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12945,7 +12941,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12969,10 +12965,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488435</v>
+        <v>488446</v>
       </c>
       <c r="R102" t="n">
-        <v>7014641</v>
+        <v>7014684</v>
       </c>
       <c r="S102" t="n">
         <v>9</v>
@@ -13004,7 +13000,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13014,12 +13010,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 1,5 m2 yta.</t>
+          <t>Minst 76 plantor inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13051,10 +13047,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129210160</v>
+        <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13081,7 +13077,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13105,10 +13101,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488446</v>
+        <v>488435</v>
       </c>
       <c r="R103" t="n">
-        <v>7014684</v>
+        <v>7014641</v>
       </c>
       <c r="S103" t="n">
         <v>9</v>
@@ -13140,7 +13136,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13150,12 +13146,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Minst 76 plantor inom ca 2,5 m2 yta.</t>
+          <t>Minst 80 plantor inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13187,48 +13183,53 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129213534</v>
+        <v>129212827</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>91993</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488675</v>
+        <v>488535</v>
       </c>
       <c r="R104" t="n">
-        <v>7014494</v>
+        <v>7014455</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13257,7 +13258,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13267,7 +13268,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13296,12 +13297,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13319,43 +13320,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129213886</v>
+        <v>129209238</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>100894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -13364,13 +13360,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488671</v>
+        <v>488489</v>
       </c>
       <c r="R105" t="n">
-        <v>7014435</v>
+        <v>7014656</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13399,7 +13395,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13409,12 +13405,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13429,26 +13420,6 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13466,50 +13437,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129209238</v>
+        <v>129213534</v>
       </c>
       <c r="B106" t="n">
-        <v>100892</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488489</v>
+        <v>488675</v>
       </c>
       <c r="R106" t="n">
-        <v>7014656</v>
+        <v>7014494</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13541,7 +13507,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13551,7 +13517,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13566,6 +13532,26 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13583,38 +13569,43 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129212827</v>
+        <v>129213886</v>
       </c>
       <c r="B107" t="n">
-        <v>91992</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13623,13 +13614,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488535</v>
+        <v>488671</v>
       </c>
       <c r="R107" t="n">
-        <v>7014455</v>
+        <v>7014435</v>
       </c>
       <c r="S107" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13658,7 +13649,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13668,7 +13659,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13697,12 +13693,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13855,7 +13851,7 @@
         <v>129214838</v>
       </c>
       <c r="B109" t="n">
-        <v>98608</v>
+        <v>98609</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14549,7 +14545,7 @@
         <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14935,7 +14931,7 @@
         <v>129211241</v>
       </c>
       <c r="B117" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15071,7 +15067,7 @@
         <v>129211912</v>
       </c>
       <c r="B118" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15204,10 +15200,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129214468</v>
+        <v>129212992</v>
       </c>
       <c r="B119" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15215,42 +15211,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488595</v>
+        <v>488605</v>
       </c>
       <c r="R119" t="n">
-        <v>7014471</v>
+        <v>7014461</v>
       </c>
       <c r="S119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15279,7 +15270,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15289,12 +15280,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15323,12 +15309,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15346,38 +15332,38 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129210698</v>
+        <v>129214468</v>
       </c>
       <c r="B120" t="n">
-        <v>92494</v>
+        <v>57727</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15386,13 +15372,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488475</v>
+        <v>488595</v>
       </c>
       <c r="R120" t="n">
-        <v>7014707</v>
+        <v>7014471</v>
       </c>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15421,7 +15407,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15431,7 +15417,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15446,6 +15437,26 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15595,48 +15606,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129212992</v>
+        <v>129210698</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>92495</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488605</v>
+        <v>488475</v>
       </c>
       <c r="R122" t="n">
-        <v>7014461</v>
+        <v>7014707</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15665,7 +15681,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15675,7 +15691,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15690,26 +15706,6 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15867,7 +15863,7 @@
         <v>129349154</v>
       </c>
       <c r="B124" t="n">
-        <v>92230</v>
+        <v>92231</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129076254</v>
+        <v>129074228</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,37 +1920,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488581</v>
+        <v>488431</v>
       </c>
       <c r="R14" t="n">
-        <v>7014597</v>
+        <v>7014633</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,14 +1987,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,22 +2023,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2036,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129080431</v>
+        <v>129076254</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2071,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488667</v>
+        <v>488581</v>
       </c>
       <c r="R15" t="n">
-        <v>7014453</v>
+        <v>7014597</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2109,6 +2129,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2125,12 +2150,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2140,7 +2165,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2158,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129074673</v>
+        <v>129080431</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2193,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488470</v>
+        <v>488667</v>
       </c>
       <c r="R16" t="n">
-        <v>7014593</v>
+        <v>7014453</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
@@ -2280,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079967</v>
+        <v>129074673</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2315,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488745</v>
+        <v>488470</v>
       </c>
       <c r="R17" t="n">
-        <v>7014497</v>
+        <v>7014593</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074228</v>
+        <v>129079967</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,47 +2438,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488431</v>
+        <v>488745</v>
       </c>
       <c r="R18" t="n">
-        <v>7014633</v>
+        <v>7014497</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2480,26 +2495,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2552,7 +2552,7 @@
         <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129076105</v>
+        <v>129078041</v>
       </c>
       <c r="B31" t="n">
-        <v>100894</v>
+        <v>99040</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4049,27 +4049,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4078,13 +4078,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488531</v>
+        <v>488550</v>
       </c>
       <c r="R31" t="n">
-        <v>7014566</v>
+        <v>7014460</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4145,53 +4145,67 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129073989</v>
+        <v>129071599</v>
       </c>
       <c r="B32" t="n">
-        <v>100894</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488436</v>
+        <v>488409</v>
       </c>
       <c r="R32" t="n">
-        <v>7014587</v>
+        <v>7014470</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4218,9 +4232,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4252,53 +4281,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129081210</v>
+        <v>129080078</v>
       </c>
       <c r="B33" t="n">
-        <v>100894</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488580</v>
+        <v>488760</v>
       </c>
       <c r="R33" t="n">
-        <v>7014585</v>
+        <v>7014511</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4342,6 +4366,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4359,53 +4403,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129074467</v>
+        <v>129079878</v>
       </c>
       <c r="B34" t="n">
-        <v>100894</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488447</v>
+        <v>488787</v>
       </c>
       <c r="R34" t="n">
-        <v>7014717</v>
+        <v>7014483</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4449,6 +4488,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4466,48 +4525,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129080078</v>
+        <v>129076105</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>100895</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488760</v>
+        <v>488531</v>
       </c>
       <c r="R35" t="n">
-        <v>7014511</v>
+        <v>7014566</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4551,26 +4615,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4588,48 +4632,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129079878</v>
+        <v>129073989</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>100895</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488787</v>
+        <v>488436</v>
       </c>
       <c r="R36" t="n">
-        <v>7014483</v>
+        <v>7014587</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4673,26 +4722,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4710,67 +4739,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129071599</v>
+        <v>129081210</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>100895</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488409</v>
+        <v>488580</v>
       </c>
       <c r="R37" t="n">
-        <v>7014470</v>
+        <v>7014585</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4797,24 +4812,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129078041</v>
+        <v>129074467</v>
       </c>
       <c r="B38" t="n">
-        <v>99039</v>
+        <v>100895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,27 +4857,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488550</v>
+        <v>488447</v>
       </c>
       <c r="R38" t="n">
-        <v>7014460</v>
+        <v>7014717</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5924,53 +5924,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129077994</v>
+        <v>129072070</v>
       </c>
       <c r="B47" t="n">
-        <v>100894</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488544</v>
+        <v>488455</v>
       </c>
       <c r="R47" t="n">
         <v>7014457</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6014,6 +6009,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6158,48 +6173,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129072070</v>
+        <v>129077994</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>100895</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488455</v>
+        <v>488544</v>
       </c>
       <c r="R49" t="n">
         <v>7014457</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6243,26 +6263,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129070117</v>
+        <v>129079479</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6291,34 +6291,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488317</v>
+        <v>488806</v>
       </c>
       <c r="R50" t="n">
-        <v>7014450</v>
+        <v>7014416</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6348,24 +6358,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6549,43 +6549,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129079479</v>
+        <v>129072360</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>100895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6594,13 +6589,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488806</v>
+        <v>488465</v>
       </c>
       <c r="R52" t="n">
-        <v>7014416</v>
+        <v>7014498</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6632,11 +6627,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6649,26 +6639,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6686,53 +6656,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129072360</v>
+        <v>129070117</v>
       </c>
       <c r="B53" t="n">
-        <v>100894</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488465</v>
+        <v>488317</v>
       </c>
       <c r="R53" t="n">
-        <v>7014498</v>
+        <v>7014450</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6759,11 +6724,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>I gammal granskog med gott om död ved.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +6756,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129077981</v>
+        <v>129071923</v>
       </c>
       <c r="B54" t="n">
-        <v>98705</v>
+        <v>91993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,36 +6804,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6842,13 +6833,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488516</v>
+        <v>488400</v>
       </c>
       <c r="R54" t="n">
-        <v>7014462</v>
+        <v>7014435</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6875,26 +6866,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6907,6 +6883,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6924,38 +6920,47 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129071884</v>
+        <v>129077981</v>
       </c>
       <c r="B55" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6964,13 +6969,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488391</v>
+        <v>488516</v>
       </c>
       <c r="R55" t="n">
-        <v>7014430</v>
+        <v>7014462</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6997,14 +7002,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7019,26 +7034,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7056,32 +7051,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B56" t="n">
-        <v>91993</v>
+        <v>91838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7096,10 +7091,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R56" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -7132,6 +7127,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7559,53 +7559,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129070439</v>
+        <v>129073935</v>
       </c>
       <c r="B60" t="n">
-        <v>103228</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488363</v>
+        <v>488409</v>
       </c>
       <c r="R60" t="n">
-        <v>7014442</v>
+        <v>7014521</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7632,26 +7627,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7664,6 +7644,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7681,48 +7681,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129073935</v>
+        <v>129070439</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>103229</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488409</v>
+        <v>488363</v>
       </c>
       <c r="R61" t="n">
-        <v>7014521</v>
+        <v>7014442</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7749,11 +7754,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Växer intill blåsippa, smultron och kransmossa på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7766,26 +7786,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129073694</v>
+        <v>129074640</v>
       </c>
       <c r="B63" t="n">
-        <v>100894</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488426</v>
+        <v>488472</v>
       </c>
       <c r="R63" t="n">
-        <v>7014494</v>
+        <v>7014599</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8008,6 +8008,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8020,6 +8025,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8037,38 +8062,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129072652</v>
+        <v>129078537</v>
       </c>
       <c r="B64" t="n">
-        <v>100894</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8077,13 +8107,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488514</v>
+        <v>488573</v>
       </c>
       <c r="R64" t="n">
-        <v>7014547</v>
+        <v>7014399</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8115,6 +8145,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8127,6 +8162,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8144,38 +8199,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129078147</v>
+        <v>129079063</v>
       </c>
       <c r="B65" t="n">
-        <v>103228</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8184,13 +8239,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488557</v>
+        <v>488655</v>
       </c>
       <c r="R65" t="n">
-        <v>7014445</v>
+        <v>7014417</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8217,19 +8272,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8244,6 +8294,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8261,38 +8331,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129074640</v>
+        <v>129078147</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>103229</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8301,13 +8371,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488472</v>
+        <v>488557</v>
       </c>
       <c r="R66" t="n">
-        <v>7014599</v>
+        <v>7014445</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8334,14 +8404,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8356,26 +8431,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8393,43 +8448,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129078537</v>
+        <v>129073694</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>100895</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8438,13 +8488,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488573</v>
+        <v>488426</v>
       </c>
       <c r="R67" t="n">
-        <v>7014399</v>
+        <v>7014494</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8476,11 +8526,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8493,26 +8538,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8530,38 +8555,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129079063</v>
+        <v>129072652</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>100895</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8570,13 +8595,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488655</v>
+        <v>488514</v>
       </c>
       <c r="R68" t="n">
-        <v>7014417</v>
+        <v>7014547</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8608,11 +8633,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8625,26 +8645,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8797,7 +8797,7 @@
         <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98604</v>
+        <v>98605</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9442,47 +9442,38 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129213412</v>
+        <v>129210501</v>
       </c>
       <c r="B75" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -9492,17 +9483,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488623</v>
+        <v>488472</v>
       </c>
       <c r="R75" t="n">
-        <v>7014540</v>
+        <v>7014695</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9531,7 +9522,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9541,12 +9532,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9561,6 +9552,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9578,45 +9589,64 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215411</v>
+        <v>129213412</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488525</v>
+        <v>488623</v>
       </c>
       <c r="R76" t="n">
-        <v>7014363</v>
+        <v>7014540</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9648,7 +9678,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9658,12 +9688,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9678,26 +9708,6 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9852,10 +9862,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129210501</v>
+        <v>129215411</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9863,47 +9873,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488472</v>
+        <v>488525</v>
       </c>
       <c r="R78" t="n">
-        <v>7014695</v>
+        <v>7014363</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10136,38 +10136,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129212656</v>
+        <v>129214932</v>
       </c>
       <c r="B80" t="n">
-        <v>100894</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -10176,13 +10176,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488569</v>
+        <v>488526</v>
       </c>
       <c r="R80" t="n">
-        <v>7014485</v>
+        <v>7014439</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10221,7 +10221,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10236,6 +10241,26 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10253,48 +10278,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129211802</v>
+        <v>129212656</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>100895</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488591</v>
+        <v>488569</v>
       </c>
       <c r="R81" t="n">
-        <v>7014632</v>
+        <v>7014485</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10323,7 +10353,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10333,7 +10363,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10348,26 +10378,6 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10522,10 +10532,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129214932</v>
+        <v>129211802</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10533,42 +10543,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488526</v>
+        <v>488591</v>
       </c>
       <c r="R83" t="n">
-        <v>7014439</v>
+        <v>7014632</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10597,7 +10602,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10607,12 +10612,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129212289</v>
+        <v>129215312</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488615</v>
+        <v>488534</v>
       </c>
       <c r="R85" t="n">
-        <v>7014544</v>
+        <v>7014397</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10901,26 +10901,6 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11182,7 +11162,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215312</v>
+        <v>129212289</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -11217,13 +11197,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R88" t="n">
-        <v>7014397</v>
+        <v>7014544</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11252,7 +11232,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11262,7 +11242,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11277,6 +11257,26 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11294,34 +11294,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129209204</v>
+        <v>129214590</v>
       </c>
       <c r="B89" t="n">
-        <v>91560</v>
+        <v>99040</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11330,10 +11334,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488495</v>
+        <v>488566</v>
       </c>
       <c r="R89" t="n">
-        <v>7014661</v>
+        <v>7014423</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11365,7 +11369,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11375,7 +11379,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11390,26 +11394,6 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11427,10 +11411,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215504</v>
+        <v>129209204</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11438,37 +11422,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488457</v>
+        <v>488495</v>
       </c>
       <c r="R90" t="n">
-        <v>7014436</v>
+        <v>7014661</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11497,7 +11482,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11507,7 +11492,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11522,6 +11507,26 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11651,53 +11656,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129214590</v>
+        <v>129215504</v>
       </c>
       <c r="B92" t="n">
-        <v>99039</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488566</v>
+        <v>488457</v>
       </c>
       <c r="R92" t="n">
-        <v>7014423</v>
+        <v>7014436</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11771,7 +11771,7 @@
         <v>129211354</v>
       </c>
       <c r="B93" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>129213105</v>
       </c>
       <c r="B94" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12255,42 +12255,47 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129212481</v>
+        <v>129214807</v>
       </c>
       <c r="B97" t="n">
-        <v>57724</v>
+        <v>98706</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -12304,13 +12309,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488604</v>
+        <v>488555</v>
       </c>
       <c r="R97" t="n">
-        <v>7014527</v>
+        <v>7014416</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12339,7 +12344,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12349,12 +12354,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12389,7 +12394,7 @@
         <v>129210843</v>
       </c>
       <c r="B98" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12503,47 +12508,42 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129214807</v>
+        <v>129212481</v>
       </c>
       <c r="B99" t="n">
-        <v>98705</v>
+        <v>57724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -12557,13 +12557,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488555</v>
+        <v>488604</v>
       </c>
       <c r="R99" t="n">
-        <v>7014416</v>
+        <v>7014527</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12642,7 +12642,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13320,38 +13320,43 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129209238</v>
+        <v>129213886</v>
       </c>
       <c r="B105" t="n">
-        <v>100894</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -13360,13 +13365,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488489</v>
+        <v>488671</v>
       </c>
       <c r="R105" t="n">
-        <v>7014656</v>
+        <v>7014435</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13395,7 +13400,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13405,7 +13410,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13420,6 +13430,26 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13569,43 +13599,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129213886</v>
+        <v>129209238</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>100895</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13614,13 +13639,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488671</v>
+        <v>488489</v>
       </c>
       <c r="R107" t="n">
-        <v>7014435</v>
+        <v>7014656</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13649,7 +13674,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13659,12 +13684,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13679,26 +13699,6 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13716,48 +13716,67 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129213440</v>
+        <v>129214838</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>98610</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488638</v>
+        <v>488552</v>
       </c>
       <c r="R108" t="n">
-        <v>7014529</v>
+        <v>7014410</v>
       </c>
       <c r="S108" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13786,7 +13805,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13796,7 +13815,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>1 planta med fröställning.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13811,26 +13835,6 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13848,67 +13852,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129214838</v>
+        <v>129213440</v>
       </c>
       <c r="B109" t="n">
-        <v>98609</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488552</v>
+        <v>488638</v>
       </c>
       <c r="R109" t="n">
-        <v>7014410</v>
+        <v>7014529</v>
       </c>
       <c r="S109" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13937,7 +13922,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13947,12 +13932,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>1 planta med fröställning.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13967,6 +13947,26 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
         <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>129211241</v>
       </c>
       <c r="B117" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>129211912</v>
       </c>
       <c r="B118" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129212992</v>
+        <v>129209446</v>
       </c>
       <c r="B119" t="n">
         <v>79041</v>
@@ -15235,10 +15235,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488605</v>
+        <v>488454</v>
       </c>
       <c r="R119" t="n">
-        <v>7014461</v>
+        <v>7014635</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15309,12 +15309,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15332,10 +15332,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129214468</v>
+        <v>129212992</v>
       </c>
       <c r="B120" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15343,42 +15343,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488595</v>
+        <v>488605</v>
       </c>
       <c r="R120" t="n">
-        <v>7014471</v>
+        <v>7014461</v>
       </c>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15407,7 +15402,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15417,12 +15412,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15451,12 +15441,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15474,10 +15464,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129209446</v>
+        <v>129214468</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15485,37 +15475,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488454</v>
+        <v>488595</v>
       </c>
       <c r="R121" t="n">
-        <v>7014635</v>
+        <v>7014471</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15544,7 +15539,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15554,7 +15549,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15583,12 +15583,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129072984</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129074228</v>
+        <v>129076254</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,47 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488431</v>
+        <v>488581</v>
       </c>
       <c r="R14" t="n">
-        <v>7014633</v>
+        <v>7014597</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,24 +1977,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2023,22 +2003,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2056,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129076254</v>
+        <v>129080431</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,13 +2071,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488581</v>
+        <v>488667</v>
       </c>
       <c r="R15" t="n">
-        <v>7014597</v>
+        <v>7014453</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2129,11 +2109,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2150,12 +2125,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2165,7 +2140,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2183,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129080431</v>
+        <v>129074673</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488667</v>
+        <v>488470</v>
       </c>
       <c r="R16" t="n">
-        <v>7014453</v>
+        <v>7014593</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
@@ -2305,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074673</v>
+        <v>129079967</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488470</v>
+        <v>488745</v>
       </c>
       <c r="R17" t="n">
-        <v>7014593</v>
+        <v>7014497</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2427,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129079967</v>
+        <v>129074228</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,37 +2413,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488745</v>
+        <v>488431</v>
       </c>
       <c r="R18" t="n">
-        <v>7014497</v>
+        <v>7014633</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,11 +2480,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129077751</v>
+        <v>129078715</v>
       </c>
       <c r="B19" t="n">
-        <v>97577</v>
+        <v>100899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,37 +2560,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488522</v>
+        <v>488611</v>
       </c>
       <c r="R19" t="n">
-        <v>7014485</v>
+        <v>7014397</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,11 +2625,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129078715</v>
+        <v>129077751</v>
       </c>
       <c r="B20" t="n">
-        <v>100895</v>
+        <v>97581</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,42 +2667,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488611</v>
+        <v>488522</v>
       </c>
       <c r="R20" t="n">
-        <v>7014397</v>
+        <v>7014485</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,6 +2727,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129079151</v>
+        <v>129081134</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,27 +2774,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488670</v>
+        <v>488567</v>
       </c>
       <c r="R21" t="n">
-        <v>7014411</v>
+        <v>7014534</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129081134</v>
+        <v>129079151</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,27 +2906,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488567</v>
+        <v>488670</v>
       </c>
       <c r="R22" t="n">
-        <v>7014534</v>
+        <v>7014411</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,22 +2994,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
         <v>129076465</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3642,53 +3642,58 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129078582</v>
+        <v>129073330</v>
       </c>
       <c r="B28" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488570</v>
+        <v>488408</v>
       </c>
       <c r="R28" t="n">
-        <v>7014409</v>
+        <v>7014549</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3720,6 +3725,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3746,12 +3756,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3769,58 +3779,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129073330</v>
+        <v>129078582</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91996</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488408</v>
+        <v>488570</v>
       </c>
       <c r="R29" t="n">
-        <v>7014549</v>
+        <v>7014409</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3852,11 +3857,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129081091</v>
+        <v>129080078</v>
       </c>
       <c r="B30" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,42 +3917,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488575</v>
+        <v>488760</v>
       </c>
       <c r="R30" t="n">
-        <v>7014525</v>
+        <v>7014511</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3984,11 +3979,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4005,22 +3995,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4038,53 +4028,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129078041</v>
+        <v>129079878</v>
       </c>
       <c r="B31" t="n">
-        <v>99040</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488550</v>
+        <v>488787</v>
       </c>
       <c r="R31" t="n">
-        <v>7014460</v>
+        <v>7014483</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4128,6 +4113,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4145,10 +4150,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129071599</v>
+        <v>129081091</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,56 +4161,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488409</v>
+        <v>488575</v>
       </c>
       <c r="R32" t="n">
-        <v>7014470</v>
+        <v>7014525</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4232,24 +4223,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4264,6 +4245,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4281,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129080078</v>
+        <v>129071599</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,37 +4293,56 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488760</v>
+        <v>488409</v>
       </c>
       <c r="R33" t="n">
-        <v>7014511</v>
+        <v>7014470</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4349,11 +4369,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4366,26 +4401,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4403,48 +4418,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129079878</v>
+        <v>129076105</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>100899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488787</v>
+        <v>488531</v>
       </c>
       <c r="R34" t="n">
-        <v>7014483</v>
+        <v>7014566</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4488,26 +4508,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129076105</v>
+        <v>129073989</v>
       </c>
       <c r="B35" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4565,13 +4565,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488531</v>
+        <v>488436</v>
       </c>
       <c r="R35" t="n">
-        <v>7014566</v>
+        <v>7014587</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129073989</v>
+        <v>129081210</v>
       </c>
       <c r="B36" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488436</v>
+        <v>488580</v>
       </c>
       <c r="R36" t="n">
-        <v>7014587</v>
+        <v>7014585</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129081210</v>
+        <v>129074467</v>
       </c>
       <c r="B37" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488580</v>
+        <v>488447</v>
       </c>
       <c r="R37" t="n">
-        <v>7014585</v>
+        <v>7014717</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129074467</v>
+        <v>129078041</v>
       </c>
       <c r="B38" t="n">
-        <v>100895</v>
+        <v>99044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,27 +4857,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488447</v>
+        <v>488550</v>
       </c>
       <c r="R38" t="n">
-        <v>7014717</v>
+        <v>7014460</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129072614</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>129072008</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129076722</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>129076936</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5792,38 +5792,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129076866</v>
+        <v>129077994</v>
       </c>
       <c r="B46" t="n">
-        <v>91838</v>
+        <v>100899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5832,13 +5832,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488575</v>
+        <v>488544</v>
       </c>
       <c r="R46" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5870,11 +5870,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5887,26 +5882,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5924,10 +5899,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129072070</v>
+        <v>129080537</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5959,10 +5934,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488455</v>
+        <v>488632</v>
       </c>
       <c r="R47" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5995,6 +5970,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6046,10 +6026,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129080537</v>
+        <v>129072070</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6081,10 +6061,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488632</v>
+        <v>488455</v>
       </c>
       <c r="R48" t="n">
-        <v>7014478</v>
+        <v>7014457</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -6117,11 +6097,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6173,38 +6148,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129077994</v>
+        <v>129076866</v>
       </c>
       <c r="B49" t="n">
-        <v>100895</v>
+        <v>91841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6213,13 +6188,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488544</v>
+        <v>488575</v>
       </c>
       <c r="R49" t="n">
-        <v>7014457</v>
+        <v>7014596</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6251,6 +6226,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6263,6 +6243,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6417,10 +6417,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129081155</v>
+        <v>129072360</v>
       </c>
       <c r="B51" t="n">
-        <v>80182</v>
+        <v>100899</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6428,27 +6428,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488569</v>
+        <v>488465</v>
       </c>
       <c r="R51" t="n">
-        <v>7014529</v>
+        <v>7014498</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -6495,11 +6495,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6512,26 +6507,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6549,53 +6524,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129072360</v>
+        <v>129070117</v>
       </c>
       <c r="B52" t="n">
-        <v>100895</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488465</v>
+        <v>488317</v>
       </c>
       <c r="R52" t="n">
-        <v>7014498</v>
+        <v>7014450</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6622,11 +6592,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I gammal granskog med gott om död ved.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6639,6 +6624,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6656,48 +6661,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129070117</v>
+        <v>129081155</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>80184</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488317</v>
+        <v>488569</v>
       </c>
       <c r="R53" t="n">
-        <v>7014450</v>
+        <v>7014529</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6724,24 +6734,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6760,22 +6760,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6793,32 +6793,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B54" t="n">
-        <v>91993</v>
+        <v>91841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R54" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -6869,6 +6869,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6923,7 +6928,7 @@
         <v>129077981</v>
       </c>
       <c r="B55" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7051,32 +7056,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129071884</v>
+        <v>129071923</v>
       </c>
       <c r="B56" t="n">
-        <v>91838</v>
+        <v>91996</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7091,10 +7096,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488391</v>
+        <v>488400</v>
       </c>
       <c r="R56" t="n">
-        <v>7014430</v>
+        <v>7014435</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
@@ -7127,11 +7132,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7186,7 +7186,7 @@
         <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>129076063</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>129073935</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>129070439</v>
       </c>
       <c r="B61" t="n">
-        <v>103229</v>
+        <v>103233</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>129076561</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>129078147</v>
       </c>
       <c r="B66" t="n">
-        <v>103229</v>
+        <v>103233</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>129073694</v>
       </c>
       <c r="B67" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>129072652</v>
       </c>
       <c r="B68" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8662,38 +8662,52 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129079226</v>
+        <v>129077294</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8702,13 +8716,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488679</v>
+        <v>488548</v>
       </c>
       <c r="R69" t="n">
-        <v>7014391</v>
+        <v>7014573</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8735,14 +8749,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8757,26 +8781,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8794,52 +8798,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129077294</v>
+        <v>129079226</v>
       </c>
       <c r="B70" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8848,13 +8838,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488548</v>
+        <v>488679</v>
       </c>
       <c r="R70" t="n">
-        <v>7014573</v>
+        <v>7014391</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8881,24 +8871,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8913,6 +8893,26 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98605</v>
+        <v>98609</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129210501</v>
+        <v>129215411</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9453,47 +9453,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488472</v>
+        <v>488525</v>
       </c>
       <c r="R75" t="n">
-        <v>7014695</v>
+        <v>7014363</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9522,7 +9512,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9532,12 +9522,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9566,12 +9556,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9589,10 +9579,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129213412</v>
+        <v>129213773</v>
       </c>
       <c r="B76" t="n">
-        <v>98706</v>
+        <v>91996</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9600,41 +9590,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9643,13 +9619,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488623</v>
+        <v>488662</v>
       </c>
       <c r="R76" t="n">
-        <v>7014540</v>
+        <v>7014466</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9678,7 +9654,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9688,12 +9664,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9708,6 +9679,26 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9725,53 +9716,58 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129213773</v>
+        <v>129210501</v>
       </c>
       <c r="B77" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488662</v>
+        <v>488472</v>
       </c>
       <c r="R77" t="n">
-        <v>7014466</v>
+        <v>7014695</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9800,7 +9796,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9810,7 +9806,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9839,12 +9840,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9862,45 +9863,64 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215411</v>
+        <v>129213412</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488525</v>
+        <v>488623</v>
       </c>
       <c r="R78" t="n">
-        <v>7014363</v>
+        <v>7014540</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9932,7 +9952,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9942,12 +9962,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>Minst 6 plantor inom ca 0,5 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9962,26 +9982,6 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10136,10 +10136,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129214932</v>
+        <v>129212598</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10147,42 +10147,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488526</v>
+        <v>488580</v>
       </c>
       <c r="R80" t="n">
-        <v>7014439</v>
+        <v>7014484</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10211,7 +10206,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10221,12 +10216,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10255,12 +10250,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10278,53 +10273,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129212656</v>
+        <v>129211802</v>
       </c>
       <c r="B81" t="n">
-        <v>100895</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488569</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7014485</v>
+        <v>7014632</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10353,7 +10343,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10363,7 +10353,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10378,6 +10368,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10395,45 +10405,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129212598</v>
+        <v>129212656</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>100899</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488580</v>
+        <v>488569</v>
       </c>
       <c r="R82" t="n">
-        <v>7014484</v>
+        <v>7014485</v>
       </c>
       <c r="S82" t="n">
         <v>9</v>
@@ -10465,7 +10480,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10475,12 +10490,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10495,26 +10505,6 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10532,10 +10522,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129211802</v>
+        <v>129214932</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10543,37 +10533,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488591</v>
+        <v>488526</v>
       </c>
       <c r="R83" t="n">
-        <v>7014632</v>
+        <v>7014439</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10602,7 +10597,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10612,7 +10607,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>129215312</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>129210249</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>129215145</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>129212289</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11294,38 +11294,34 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129214590</v>
+        <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>99040</v>
+        <v>91563</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11334,10 +11330,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488566</v>
+        <v>488495</v>
       </c>
       <c r="R89" t="n">
-        <v>7014423</v>
+        <v>7014661</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11369,7 +11365,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11379,7 +11375,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11394,6 +11390,26 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11411,10 +11427,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129209204</v>
+        <v>129215229</v>
       </c>
       <c r="B90" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11422,38 +11438,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488495</v>
+        <v>488501</v>
       </c>
       <c r="R90" t="n">
-        <v>7014661</v>
+        <v>7014416</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11482,7 +11497,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11492,7 +11507,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11507,26 +11522,6 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11544,10 +11539,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215229</v>
+        <v>129215504</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11579,13 +11574,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488501</v>
+        <v>488457</v>
       </c>
       <c r="R91" t="n">
-        <v>7014416</v>
+        <v>7014436</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11614,7 +11609,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11624,7 +11619,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11656,48 +11651,53 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215504</v>
+        <v>129214590</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>99044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488457</v>
+        <v>488566</v>
       </c>
       <c r="R92" t="n">
-        <v>7014436</v>
+        <v>7014423</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11771,7 +11771,7 @@
         <v>129211354</v>
       </c>
       <c r="B93" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>129213105</v>
       </c>
       <c r="B94" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12255,47 +12255,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129214807</v>
+        <v>129212481</v>
       </c>
       <c r="B97" t="n">
-        <v>98706</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -12309,13 +12304,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488555</v>
+        <v>488604</v>
       </c>
       <c r="R97" t="n">
-        <v>7014416</v>
+        <v>7014527</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12344,7 +12339,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12354,12 +12349,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12391,50 +12386,64 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129210843</v>
+        <v>129214807</v>
       </c>
       <c r="B98" t="n">
-        <v>100895</v>
+        <v>98710</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488496</v>
+        <v>488555</v>
       </c>
       <c r="R98" t="n">
-        <v>7014638</v>
+        <v>7014416</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12466,7 +12475,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12476,7 +12485,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12508,47 +12522,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129212481</v>
+        <v>129210843</v>
       </c>
       <c r="B99" t="n">
-        <v>57724</v>
+        <v>100899</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12557,13 +12562,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488604</v>
+        <v>488496</v>
       </c>
       <c r="R99" t="n">
-        <v>7014527</v>
+        <v>7014638</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12592,7 +12597,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12602,12 +12607,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Observerad i gammal granskog med gott om död ved i olika dimensioner.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12642,7 +12642,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>129212827</v>
       </c>
       <c r="B104" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13320,43 +13320,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129213886</v>
+        <v>129209238</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>100899</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -13365,13 +13360,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488671</v>
+        <v>488489</v>
       </c>
       <c r="R105" t="n">
-        <v>7014435</v>
+        <v>7014656</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13400,7 +13395,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13410,12 +13405,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13430,26 +13420,6 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13470,7 +13440,7 @@
         <v>129213534</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13599,38 +13569,43 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129209238</v>
+        <v>129213886</v>
       </c>
       <c r="B107" t="n">
-        <v>100895</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13639,13 +13614,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488489</v>
+        <v>488671</v>
       </c>
       <c r="R107" t="n">
-        <v>7014656</v>
+        <v>7014435</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13674,7 +13649,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13684,7 +13659,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13699,6 +13679,26 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13716,67 +13716,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129214838</v>
+        <v>129213440</v>
       </c>
       <c r="B108" t="n">
-        <v>98610</v>
+        <v>79043</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488552</v>
+        <v>488638</v>
       </c>
       <c r="R108" t="n">
-        <v>7014410</v>
+        <v>7014529</v>
       </c>
       <c r="S108" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13805,7 +13786,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13815,12 +13796,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>1 planta med fröställning.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13835,6 +13811,26 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13852,48 +13848,67 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129213440</v>
+        <v>129214838</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>98614</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488638</v>
+        <v>488552</v>
       </c>
       <c r="R109" t="n">
-        <v>7014529</v>
+        <v>7014410</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13922,7 +13937,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13932,7 +13947,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>1 planta med fröställning.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13947,26 +13967,6 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -13987,7 +13987,7 @@
         <v>129213171</v>
       </c>
       <c r="B110" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>129214402</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14796,45 +14796,64 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129212678</v>
+        <v>129211241</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488572</v>
+        <v>488551</v>
       </c>
       <c r="R116" t="n">
-        <v>7014469</v>
+        <v>7014630</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14866,7 +14885,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14876,7 +14895,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14891,26 +14915,6 @@
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14928,10 +14932,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129211241</v>
+        <v>129211912</v>
       </c>
       <c r="B117" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14958,7 +14962,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14982,10 +14986,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488551</v>
+        <v>488586</v>
       </c>
       <c r="R117" t="n">
-        <v>7014630</v>
+        <v>7014626</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15017,7 +15021,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15027,12 +15031,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15064,64 +15068,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129211912</v>
+        <v>129212678</v>
       </c>
       <c r="B118" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488586</v>
+        <v>488572</v>
       </c>
       <c r="R118" t="n">
-        <v>7014626</v>
+        <v>7014469</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15153,7 +15138,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15163,12 +15148,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15183,6 +15163,26 @@
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15203,7 +15203,7 @@
         <v>129209446</v>
       </c>
       <c r="B119" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>129212992</v>
       </c>
       <c r="B120" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>129210698</v>
       </c>
       <c r="B122" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>129349154</v>
       </c>
       <c r="B124" t="n">
-        <v>92231</v>
+        <v>92234</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -2763,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129081134</v>
+        <v>129079151</v>
       </c>
       <c r="B21" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,27 +2774,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488567</v>
+        <v>488670</v>
       </c>
       <c r="R21" t="n">
-        <v>7014534</v>
+        <v>7014411</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129079151</v>
+        <v>129081134</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,27 +2906,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488670</v>
+        <v>488567</v>
       </c>
       <c r="R22" t="n">
-        <v>7014411</v>
+        <v>7014534</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,22 +2994,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3642,58 +3642,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129073330</v>
+        <v>129078582</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91996</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488408</v>
+        <v>488570</v>
       </c>
       <c r="R28" t="n">
-        <v>7014549</v>
+        <v>7014409</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3725,11 +3720,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3756,12 +3746,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3779,53 +3769,58 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129078582</v>
+        <v>129073330</v>
       </c>
       <c r="B29" t="n">
-        <v>91996</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488570</v>
+        <v>488408</v>
       </c>
       <c r="R29" t="n">
-        <v>7014409</v>
+        <v>7014549</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3857,6 +3852,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129080078</v>
+        <v>129081091</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,37 +3917,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488760</v>
+        <v>488575</v>
       </c>
       <c r="R30" t="n">
-        <v>7014511</v>
+        <v>7014525</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3979,6 +3984,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3995,22 +4005,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4028,10 +4038,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129079878</v>
+        <v>129071599</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,37 +4049,56 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488787</v>
+        <v>488409</v>
       </c>
       <c r="R31" t="n">
-        <v>7014483</v>
+        <v>7014470</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4096,11 +4125,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4113,26 +4157,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4150,10 +4174,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129081091</v>
+        <v>129080078</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4161,42 +4185,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488575</v>
+        <v>488760</v>
       </c>
       <c r="R32" t="n">
-        <v>7014525</v>
+        <v>7014511</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4228,11 +4247,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4249,22 +4263,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4282,10 +4296,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129071599</v>
+        <v>129079878</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4293,56 +4307,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488409</v>
+        <v>488787</v>
       </c>
       <c r="R33" t="n">
-        <v>7014470</v>
+        <v>7014483</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4369,26 +4364,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4401,6 +4381,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -13716,48 +13716,67 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129213440</v>
+        <v>129214838</v>
       </c>
       <c r="B108" t="n">
-        <v>79043</v>
+        <v>98614</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488638</v>
+        <v>488552</v>
       </c>
       <c r="R108" t="n">
-        <v>7014529</v>
+        <v>7014410</v>
       </c>
       <c r="S108" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13786,7 +13805,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13796,7 +13815,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>1 planta med fröställning.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13811,26 +13835,6 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13848,67 +13852,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129214838</v>
+        <v>129213440</v>
       </c>
       <c r="B109" t="n">
-        <v>98614</v>
+        <v>79043</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488552</v>
+        <v>488638</v>
       </c>
       <c r="R109" t="n">
-        <v>7014410</v>
+        <v>7014529</v>
       </c>
       <c r="S109" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13937,7 +13922,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13947,12 +13932,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>1 planta med fröställning.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13967,6 +13947,26 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14400,38 +14400,43 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129214896</v>
+        <v>129214819</v>
       </c>
       <c r="B113" t="n">
-        <v>57727</v>
+        <v>100899</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14440,13 +14445,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488525</v>
+        <v>488543</v>
       </c>
       <c r="R113" t="n">
-        <v>7014424</v>
+        <v>7014418</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14475,7 +14480,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14485,12 +14490,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14505,26 +14505,6 @@
       <c r="AH113" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14542,43 +14522,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B114" t="n">
-        <v>100899</v>
+        <v>57727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14587,13 +14562,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R114" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14622,7 +14597,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14632,7 +14607,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14647,6 +14627,26 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14796,64 +14796,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129211241</v>
+        <v>129212678</v>
       </c>
       <c r="B116" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488551</v>
+        <v>488572</v>
       </c>
       <c r="R116" t="n">
-        <v>7014630</v>
+        <v>7014469</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14885,7 +14866,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14895,12 +14876,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14915,6 +14891,26 @@
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14932,7 +14928,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129211912</v>
+        <v>129211241</v>
       </c>
       <c r="B117" t="n">
         <v>98710</v>
@@ -14962,7 +14958,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14986,10 +14982,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488586</v>
+        <v>488551</v>
       </c>
       <c r="R117" t="n">
-        <v>7014626</v>
+        <v>7014630</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15021,7 +15017,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15031,12 +15027,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15068,45 +15064,64 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129212678</v>
+        <v>129211912</v>
       </c>
       <c r="B118" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488572</v>
+        <v>488586</v>
       </c>
       <c r="R118" t="n">
-        <v>7014469</v>
+        <v>7014626</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15138,7 +15153,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15148,7 +15163,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15163,26 +15183,6 @@
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129072984</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129076254</v>
+        <v>129074228</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,37 +1920,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488581</v>
+        <v>488431</v>
       </c>
       <c r="R14" t="n">
-        <v>7014597</v>
+        <v>7014633</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,14 +1987,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,22 +2023,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2036,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129080431</v>
+        <v>129076254</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,13 +2091,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488667</v>
+        <v>488581</v>
       </c>
       <c r="R15" t="n">
-        <v>7014453</v>
+        <v>7014597</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2109,6 +2129,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2125,12 +2150,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2140,7 +2165,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2158,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129074673</v>
+        <v>129080431</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488470</v>
+        <v>488667</v>
       </c>
       <c r="R16" t="n">
-        <v>7014593</v>
+        <v>7014453</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
@@ -2280,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079967</v>
+        <v>129074673</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488745</v>
+        <v>488470</v>
       </c>
       <c r="R17" t="n">
-        <v>7014497</v>
+        <v>7014593</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074228</v>
+        <v>129079967</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,47 +2438,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488431</v>
+        <v>488745</v>
       </c>
       <c r="R18" t="n">
-        <v>7014633</v>
+        <v>7014497</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2480,26 +2495,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129078715</v>
+        <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>100899</v>
+        <v>97583</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,42 +2560,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488611</v>
+        <v>488522</v>
       </c>
       <c r="R19" t="n">
-        <v>7014397</v>
+        <v>7014485</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,6 +2620,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129077751</v>
+        <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>97581</v>
+        <v>100901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,37 +2667,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488522</v>
+        <v>488611</v>
       </c>
       <c r="R20" t="n">
-        <v>7014485</v>
+        <v>7014397</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2727,11 +2732,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,7 +2898,7 @@
         <v>129081134</v>
       </c>
       <c r="B22" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>129076465</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129078582</v>
       </c>
       <c r="B28" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129081091</v>
+        <v>129071599</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,42 +3917,56 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488575</v>
+        <v>488409</v>
       </c>
       <c r="R30" t="n">
-        <v>7014525</v>
+        <v>7014470</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3979,14 +3993,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4001,26 +4025,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4038,10 +4042,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129071599</v>
+        <v>129080078</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4049,56 +4053,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488409</v>
+        <v>488760</v>
       </c>
       <c r="R31" t="n">
-        <v>7014470</v>
+        <v>7014511</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4125,26 +4110,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4157,6 +4127,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4174,10 +4164,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129080078</v>
+        <v>129079878</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4209,13 +4199,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488760</v>
+        <v>488787</v>
       </c>
       <c r="R32" t="n">
-        <v>7014511</v>
+        <v>7014483</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4296,10 +4286,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129079878</v>
+        <v>129081091</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4307,37 +4297,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488787</v>
+        <v>488575</v>
       </c>
       <c r="R33" t="n">
-        <v>7014483</v>
+        <v>7014525</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4369,6 +4364,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4385,22 +4385,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129076105</v>
+        <v>129078041</v>
       </c>
       <c r="B34" t="n">
-        <v>100899</v>
+        <v>99046</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4429,27 +4429,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4458,13 +4458,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488531</v>
+        <v>488550</v>
       </c>
       <c r="R34" t="n">
-        <v>7014566</v>
+        <v>7014460</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129073989</v>
+        <v>129076105</v>
       </c>
       <c r="B35" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4565,13 +4565,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488436</v>
+        <v>488531</v>
       </c>
       <c r="R35" t="n">
-        <v>7014587</v>
+        <v>7014566</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129081210</v>
+        <v>129073989</v>
       </c>
       <c r="B36" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488580</v>
+        <v>488436</v>
       </c>
       <c r="R36" t="n">
-        <v>7014585</v>
+        <v>7014587</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129074467</v>
+        <v>129081210</v>
       </c>
       <c r="B37" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488447</v>
+        <v>488580</v>
       </c>
       <c r="R37" t="n">
-        <v>7014717</v>
+        <v>7014585</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129078041</v>
+        <v>129074467</v>
       </c>
       <c r="B38" t="n">
-        <v>99044</v>
+        <v>100901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,27 +4857,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488550</v>
+        <v>488447</v>
       </c>
       <c r="R38" t="n">
-        <v>7014460</v>
+        <v>7014717</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129072614</v>
+        <v>129072477</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4964,34 +4964,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488504</v>
+        <v>488495</v>
       </c>
       <c r="R39" t="n">
-        <v>7014520</v>
+        <v>7014499</v>
       </c>
       <c r="S39" t="n">
         <v>8</v>
@@ -5028,7 +5033,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5057,12 +5062,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5080,10 +5085,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129072008</v>
+        <v>129072614</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5115,13 +5120,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488442</v>
+        <v>488504</v>
       </c>
       <c r="R40" t="n">
-        <v>7014464</v>
+        <v>7014520</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5151,6 +5156,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5202,10 +5212,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129072477</v>
+        <v>129072008</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5213,42 +5223,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488495</v>
+        <v>488442</v>
       </c>
       <c r="R41" t="n">
-        <v>7014499</v>
+        <v>7014464</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5280,11 +5285,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129076722</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>129076936</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>129077994</v>
       </c>
       <c r="B46" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080537</v>
+        <v>129076866</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>91843</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5910,37 +5910,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488632</v>
+        <v>488575</v>
       </c>
       <c r="R47" t="n">
-        <v>7014478</v>
+        <v>7014596</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5974,7 +5979,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6003,12 +6008,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6026,10 +6031,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129072070</v>
+        <v>129080537</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6061,10 +6066,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488455</v>
+        <v>488632</v>
       </c>
       <c r="R48" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -6097,6 +6102,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6148,10 +6158,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129076866</v>
+        <v>129072070</v>
       </c>
       <c r="B49" t="n">
-        <v>91841</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6159,42 +6169,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488575</v>
+        <v>488455</v>
       </c>
       <c r="R49" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6226,11 +6231,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6417,10 +6417,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129072360</v>
+        <v>129081155</v>
       </c>
       <c r="B51" t="n">
-        <v>100899</v>
+        <v>80185</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6428,27 +6428,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488465</v>
+        <v>488569</v>
       </c>
       <c r="R51" t="n">
-        <v>7014498</v>
+        <v>7014529</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -6495,6 +6495,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6507,6 +6512,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6527,7 +6552,7 @@
         <v>129070117</v>
       </c>
       <c r="B52" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6661,10 +6686,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129081155</v>
+        <v>129072360</v>
       </c>
       <c r="B53" t="n">
-        <v>80184</v>
+        <v>100901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6672,27 +6697,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6701,10 +6726,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488569</v>
+        <v>488465</v>
       </c>
       <c r="R53" t="n">
-        <v>7014529</v>
+        <v>7014498</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -6739,11 +6764,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6756,26 +6776,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6793,38 +6793,47 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129071884</v>
+        <v>129077981</v>
       </c>
       <c r="B54" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6833,13 +6842,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488391</v>
+        <v>488516</v>
       </c>
       <c r="R54" t="n">
-        <v>7014430</v>
+        <v>7014462</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6866,14 +6875,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6888,26 +6907,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6925,47 +6924,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129077981</v>
+        <v>129071884</v>
       </c>
       <c r="B55" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6974,13 +6964,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488516</v>
+        <v>488391</v>
       </c>
       <c r="R55" t="n">
-        <v>7014462</v>
+        <v>7014430</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7007,24 +6997,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7039,6 +7019,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
         <v>129071923</v>
       </c>
       <c r="B56" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7183,53 +7183,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B57" t="n">
-        <v>92261</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R57" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7287,12 +7282,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7310,48 +7305,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>92263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R58" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7562,7 +7562,7 @@
         <v>129073935</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>129070439</v>
       </c>
       <c r="B61" t="n">
-        <v>103233</v>
+        <v>103235</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>129076561</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129074640</v>
+        <v>129073694</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>100901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488472</v>
+        <v>488426</v>
       </c>
       <c r="R63" t="n">
-        <v>7014599</v>
+        <v>7014494</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8008,11 +8008,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8025,26 +8020,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8062,43 +8037,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129078537</v>
+        <v>129072652</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>100901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8107,13 +8077,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488573</v>
+        <v>488514</v>
       </c>
       <c r="R64" t="n">
-        <v>7014399</v>
+        <v>7014547</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8145,11 +8115,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8162,26 +8127,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8199,38 +8144,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129079063</v>
+        <v>129078147</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>103235</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8239,13 +8184,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488655</v>
+        <v>488557</v>
       </c>
       <c r="R65" t="n">
-        <v>7014417</v>
+        <v>7014445</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8272,14 +8217,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8294,26 +8244,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8331,38 +8261,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129078147</v>
+        <v>129074640</v>
       </c>
       <c r="B66" t="n">
-        <v>103233</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8371,13 +8301,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488557</v>
+        <v>488472</v>
       </c>
       <c r="R66" t="n">
-        <v>7014445</v>
+        <v>7014599</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8404,19 +8334,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8431,6 +8356,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8448,38 +8393,43 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129073694</v>
+        <v>129078537</v>
       </c>
       <c r="B67" t="n">
-        <v>100899</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8488,13 +8438,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488426</v>
+        <v>488573</v>
       </c>
       <c r="R67" t="n">
-        <v>7014494</v>
+        <v>7014399</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8526,6 +8476,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8538,6 +8493,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8555,38 +8530,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129072652</v>
+        <v>129079063</v>
       </c>
       <c r="B68" t="n">
-        <v>100899</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8595,13 +8570,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488514</v>
+        <v>488655</v>
       </c>
       <c r="R68" t="n">
-        <v>7014547</v>
+        <v>7014417</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8633,6 +8608,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8645,6 +8625,26 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8662,52 +8662,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129077294</v>
+        <v>129079226</v>
       </c>
       <c r="B69" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8716,13 +8702,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488548</v>
+        <v>488679</v>
       </c>
       <c r="R69" t="n">
-        <v>7014573</v>
+        <v>7014391</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8749,24 +8735,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8781,6 +8757,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8798,38 +8794,52 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129079226</v>
+        <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8838,13 +8848,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488679</v>
+        <v>488548</v>
       </c>
       <c r="R70" t="n">
-        <v>7014391</v>
+        <v>7014573</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8871,14 +8881,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>Minst 62 plantor och 1 fröställning inom ca 2 m2 yta i gammal flerskiktad granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8893,26 +8913,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98609</v>
+        <v>98611</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9442,48 +9442,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215411</v>
+        <v>129213773</v>
       </c>
       <c r="B75" t="n">
-        <v>79043</v>
+        <v>91998</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488525</v>
+        <v>488662</v>
       </c>
       <c r="R75" t="n">
-        <v>7014363</v>
+        <v>7014466</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9512,7 +9517,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9522,12 +9527,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9579,53 +9579,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129213773</v>
+        <v>129215411</v>
       </c>
       <c r="B76" t="n">
-        <v>91996</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488662</v>
+        <v>488525</v>
       </c>
       <c r="R76" t="n">
-        <v>7014466</v>
+        <v>7014363</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9654,7 +9649,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9664,7 +9659,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9866,7 +9866,7 @@
         <v>129213412</v>
       </c>
       <c r="B78" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>129212598</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>129211802</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10405,38 +10405,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129212656</v>
+        <v>129214932</v>
       </c>
       <c r="B82" t="n">
-        <v>100899</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10445,13 +10445,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488569</v>
+        <v>488526</v>
       </c>
       <c r="R82" t="n">
-        <v>7014485</v>
+        <v>7014439</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10490,7 +10490,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10505,6 +10510,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10522,38 +10547,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129214932</v>
+        <v>129212656</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>100901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10562,13 +10587,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488526</v>
+        <v>488569</v>
       </c>
       <c r="R83" t="n">
-        <v>7014439</v>
+        <v>7014485</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10597,7 +10622,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10607,12 +10632,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10627,26 +10647,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>129215312</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>129210249</v>
       </c>
       <c r="B86" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>129215145</v>
       </c>
       <c r="B87" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>129212289</v>
       </c>
       <c r="B88" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>129215229</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>129215504</v>
       </c>
       <c r="B91" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11651,38 +11651,52 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129214590</v>
+        <v>129211354</v>
       </c>
       <c r="B92" t="n">
-        <v>99044</v>
+        <v>98712</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11691,13 +11705,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488566</v>
+        <v>488586</v>
       </c>
       <c r="R92" t="n">
-        <v>7014423</v>
+        <v>7014612</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11726,7 +11740,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11736,7 +11750,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11768,52 +11787,38 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129211354</v>
+        <v>129213105</v>
       </c>
       <c r="B93" t="n">
-        <v>98710</v>
+        <v>100901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11822,13 +11827,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488586</v>
+        <v>488627</v>
       </c>
       <c r="R93" t="n">
-        <v>7014612</v>
+        <v>7014454</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11857,7 +11862,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11867,12 +11872,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11904,10 +11904,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129213105</v>
+        <v>129214590</v>
       </c>
       <c r="B94" t="n">
-        <v>100899</v>
+        <v>99046</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11915,27 +11915,27 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11944,10 +11944,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488627</v>
+        <v>488566</v>
       </c>
       <c r="R94" t="n">
-        <v>7014454</v>
+        <v>7014423</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12024,7 +12024,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>129214807</v>
       </c>
       <c r="B98" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>129210843</v>
       </c>
       <c r="B99" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>129212827</v>
       </c>
       <c r="B104" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13320,50 +13320,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129209238</v>
+        <v>129213534</v>
       </c>
       <c r="B105" t="n">
-        <v>100899</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488489</v>
+        <v>488675</v>
       </c>
       <c r="R105" t="n">
-        <v>7014656</v>
+        <v>7014494</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13395,7 +13390,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13405,7 +13400,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13420,6 +13415,26 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13437,45 +13452,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129213534</v>
+        <v>129209238</v>
       </c>
       <c r="B106" t="n">
-        <v>79043</v>
+        <v>100901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488675</v>
+        <v>488489</v>
       </c>
       <c r="R106" t="n">
-        <v>7014494</v>
+        <v>7014656</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13507,7 +13527,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13517,7 +13537,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13532,26 +13552,6 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13719,7 +13719,7 @@
         <v>129214838</v>
       </c>
       <c r="B108" t="n">
-        <v>98614</v>
+        <v>98616</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>129213440</v>
       </c>
       <c r="B109" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>129213171</v>
       </c>
       <c r="B110" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14400,43 +14400,38 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B113" t="n">
-        <v>100899</v>
+        <v>57727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14445,13 +14440,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R113" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14480,7 +14475,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14490,7 +14485,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14505,6 +14505,26 @@
       <c r="AH113" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14522,38 +14542,43 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214896</v>
+        <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>57727</v>
+        <v>100901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14562,13 +14587,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488525</v>
+        <v>488543</v>
       </c>
       <c r="R114" t="n">
-        <v>7014424</v>
+        <v>7014418</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14597,7 +14622,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14607,12 +14632,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14627,26 +14647,6 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14667,7 +14667,7 @@
         <v>129214402</v>
       </c>
       <c r="B115" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>129212678</v>
       </c>
       <c r="B116" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>129211241</v>
       </c>
       <c r="B117" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>129211912</v>
       </c>
       <c r="B118" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15200,48 +15200,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129209446</v>
+        <v>129210698</v>
       </c>
       <c r="B119" t="n">
-        <v>79043</v>
+        <v>92500</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488454</v>
+        <v>488475</v>
       </c>
       <c r="R119" t="n">
-        <v>7014635</v>
+        <v>7014707</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15270,7 +15275,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15280,7 +15285,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15295,26 +15300,6 @@
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15332,10 +15317,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129212992</v>
+        <v>129209446</v>
       </c>
       <c r="B120" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15367,10 +15352,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488605</v>
+        <v>488454</v>
       </c>
       <c r="R120" t="n">
-        <v>7014461</v>
+        <v>7014635</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15402,7 +15387,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15412,7 +15397,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15441,12 +15426,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15464,10 +15449,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129214468</v>
+        <v>129212992</v>
       </c>
       <c r="B121" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15475,42 +15460,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488595</v>
+        <v>488605</v>
       </c>
       <c r="R121" t="n">
-        <v>7014471</v>
+        <v>7014461</v>
       </c>
       <c r="S121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15539,7 +15519,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15549,12 +15529,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15583,12 +15558,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15606,38 +15581,38 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129210698</v>
+        <v>129214468</v>
       </c>
       <c r="B122" t="n">
-        <v>92498</v>
+        <v>57727</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -15646,13 +15621,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488475</v>
+        <v>488595</v>
       </c>
       <c r="R122" t="n">
-        <v>7014707</v>
+        <v>7014471</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15681,7 +15656,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15691,7 +15666,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15706,6 +15686,26 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15863,7 +15863,7 @@
         <v>129349154</v>
       </c>
       <c r="B124" t="n">
-        <v>92234</v>
+        <v>92236</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129074228</v>
+        <v>129076254</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,47 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488431</v>
+        <v>488581</v>
       </c>
       <c r="R14" t="n">
-        <v>7014633</v>
+        <v>7014597</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,24 +1977,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2023,22 +2003,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2056,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129076254</v>
+        <v>129080431</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2091,13 +2071,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488581</v>
+        <v>488667</v>
       </c>
       <c r="R15" t="n">
-        <v>7014597</v>
+        <v>7014453</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2129,11 +2109,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2150,12 +2125,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2165,7 +2140,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2183,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129080431</v>
+        <v>129074673</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2218,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488667</v>
+        <v>488470</v>
       </c>
       <c r="R16" t="n">
-        <v>7014453</v>
+        <v>7014593</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
@@ -2305,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129074673</v>
+        <v>129079967</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2340,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488470</v>
+        <v>488745</v>
       </c>
       <c r="R17" t="n">
-        <v>7014593</v>
+        <v>7014497</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2427,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129079967</v>
+        <v>129074228</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,37 +2413,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488745</v>
+        <v>488431</v>
       </c>
       <c r="R18" t="n">
-        <v>7014497</v>
+        <v>7014633</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,11 +2480,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2552,7 +2552,7 @@
         <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129079151</v>
+        <v>129081134</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,27 +2774,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488670</v>
+        <v>488567</v>
       </c>
       <c r="R21" t="n">
-        <v>7014411</v>
+        <v>7014534</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129081134</v>
+        <v>129079151</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,27 +2906,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488567</v>
+        <v>488670</v>
       </c>
       <c r="R22" t="n">
-        <v>7014534</v>
+        <v>7014411</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,22 +2994,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3289,7 +3289,7 @@
         <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129078582</v>
       </c>
       <c r="B28" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129071599</v>
+        <v>129081091</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,56 +3917,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488409</v>
+        <v>488575</v>
       </c>
       <c r="R30" t="n">
-        <v>7014470</v>
+        <v>7014525</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3993,24 +3979,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4025,6 +4001,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4042,7 +4038,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129080078</v>
+        <v>129079878</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -4077,13 +4073,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488760</v>
+        <v>488787</v>
       </c>
       <c r="R31" t="n">
-        <v>7014511</v>
+        <v>7014483</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4164,7 +4160,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129079878</v>
+        <v>129080078</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -4199,13 +4195,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488787</v>
+        <v>488760</v>
       </c>
       <c r="R32" t="n">
-        <v>7014483</v>
+        <v>7014511</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4286,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129081091</v>
+        <v>129071599</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,42 +4293,56 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488575</v>
+        <v>488409</v>
       </c>
       <c r="R33" t="n">
-        <v>7014525</v>
+        <v>7014470</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4359,14 +4369,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4381,26 +4401,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4421,7 +4421,7 @@
         <v>129078041</v>
       </c>
       <c r="B34" t="n">
-        <v>99046</v>
+        <v>99050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>129076105</v>
       </c>
       <c r="B35" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>129073989</v>
       </c>
       <c r="B36" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>129081210</v>
       </c>
       <c r="B37" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>129074467</v>
       </c>
       <c r="B38" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129072477</v>
+        <v>129072614</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4964,39 +4964,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488495</v>
+        <v>488504</v>
       </c>
       <c r="R39" t="n">
-        <v>7014499</v>
+        <v>7014520</v>
       </c>
       <c r="S39" t="n">
         <v>8</v>
@@ -5033,7 +5028,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5062,12 +5057,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5085,7 +5080,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129072614</v>
+        <v>129072008</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -5120,13 +5115,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488504</v>
+        <v>488442</v>
       </c>
       <c r="R40" t="n">
-        <v>7014520</v>
+        <v>7014464</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5156,11 +5151,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5212,10 +5202,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129072008</v>
+        <v>129072477</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,37 +5213,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488442</v>
+        <v>488495</v>
       </c>
       <c r="R41" t="n">
-        <v>7014464</v>
+        <v>7014499</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5285,6 +5280,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5337,7 +5337,7 @@
         <v>129074733</v>
       </c>
       <c r="B42" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129076722</v>
+        <v>129076936</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5476,13 +5476,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488602</v>
+        <v>488552</v>
       </c>
       <c r="R43" t="n">
-        <v>7014595</v>
+        <v>7014587</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129076936</v>
+        <v>129076722</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488552</v>
+        <v>488602</v>
       </c>
       <c r="R44" t="n">
-        <v>7014587</v>
+        <v>7014595</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5792,53 +5792,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129077994</v>
+        <v>129080537</v>
       </c>
       <c r="B46" t="n">
-        <v>100901</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488544</v>
+        <v>488632</v>
       </c>
       <c r="R46" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5870,6 +5865,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5882,6 +5882,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5899,10 +5919,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129076866</v>
+        <v>129072070</v>
       </c>
       <c r="B47" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5910,42 +5930,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488575</v>
+        <v>488455</v>
       </c>
       <c r="R47" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5977,11 +5992,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6008,12 +6018,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6031,10 +6041,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129080537</v>
+        <v>129076866</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6042,37 +6052,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488632</v>
+        <v>488575</v>
       </c>
       <c r="R48" t="n">
-        <v>7014478</v>
+        <v>7014596</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6106,7 +6121,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6135,12 +6150,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6158,48 +6173,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129072070</v>
+        <v>129077994</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>100905</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488455</v>
+        <v>488544</v>
       </c>
       <c r="R49" t="n">
         <v>7014457</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6243,26 +6263,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6280,43 +6280,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129079479</v>
+        <v>129081155</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>80185</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6325,13 +6320,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488806</v>
+        <v>488569</v>
       </c>
       <c r="R50" t="n">
-        <v>7014416</v>
+        <v>7014529</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6365,7 +6360,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6384,22 +6379,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6417,38 +6412,43 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129081155</v>
+        <v>129079479</v>
       </c>
       <c r="B51" t="n">
-        <v>80185</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6457,13 +6457,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488569</v>
+        <v>488806</v>
       </c>
       <c r="R51" t="n">
-        <v>7014529</v>
+        <v>7014416</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6516,22 +6516,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6689,7 +6689,7 @@
         <v>129072360</v>
       </c>
       <c r="B53" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6793,10 +6793,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129077981</v>
+        <v>129071923</v>
       </c>
       <c r="B54" t="n">
-        <v>98712</v>
+        <v>92002</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,36 +6804,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6842,13 +6833,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488516</v>
+        <v>488400</v>
       </c>
       <c r="R54" t="n">
-        <v>7014462</v>
+        <v>7014435</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6875,26 +6866,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6907,6 +6883,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6927,7 +6923,7 @@
         <v>129071884</v>
       </c>
       <c r="B55" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7056,10 +7052,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129071923</v>
+        <v>129077981</v>
       </c>
       <c r="B56" t="n">
-        <v>91998</v>
+        <v>98716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7067,27 +7063,36 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7096,13 +7101,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488400</v>
+        <v>488516</v>
       </c>
       <c r="R56" t="n">
-        <v>7014435</v>
+        <v>7014462</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7129,11 +7134,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7146,26 +7166,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7183,48 +7183,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>92267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R57" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7282,12 +7287,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7305,53 +7310,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B58" t="n">
-        <v>92263</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R58" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7684,7 +7684,7 @@
         <v>129070439</v>
       </c>
       <c r="B61" t="n">
-        <v>103235</v>
+        <v>103239</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129073694</v>
+        <v>129074640</v>
       </c>
       <c r="B63" t="n">
-        <v>100901</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488426</v>
+        <v>488472</v>
       </c>
       <c r="R63" t="n">
-        <v>7014494</v>
+        <v>7014599</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8008,6 +8008,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8020,6 +8025,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8037,38 +8062,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129072652</v>
+        <v>129078537</v>
       </c>
       <c r="B64" t="n">
-        <v>100901</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8077,13 +8107,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488514</v>
+        <v>488573</v>
       </c>
       <c r="R64" t="n">
-        <v>7014547</v>
+        <v>7014399</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8115,6 +8145,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8127,6 +8162,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8144,38 +8199,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129078147</v>
+        <v>129079063</v>
       </c>
       <c r="B65" t="n">
-        <v>103235</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8184,13 +8239,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488557</v>
+        <v>488655</v>
       </c>
       <c r="R65" t="n">
-        <v>7014445</v>
+        <v>7014417</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8217,19 +8272,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8244,6 +8294,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8261,38 +8331,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129074640</v>
+        <v>129073694</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>100905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8301,13 +8371,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488472</v>
+        <v>488426</v>
       </c>
       <c r="R66" t="n">
-        <v>7014599</v>
+        <v>7014494</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8339,11 +8409,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8356,26 +8421,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8393,43 +8438,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129078537</v>
+        <v>129072652</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>100905</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8438,13 +8478,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488573</v>
+        <v>488514</v>
       </c>
       <c r="R67" t="n">
-        <v>7014399</v>
+        <v>7014547</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8476,11 +8516,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8493,26 +8528,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8530,38 +8545,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129079063</v>
+        <v>129078147</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>103239</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8570,13 +8585,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488655</v>
+        <v>488557</v>
       </c>
       <c r="R68" t="n">
-        <v>7014417</v>
+        <v>7014445</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8603,14 +8618,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8625,26 +8645,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8797,7 +8797,7 @@
         <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98611</v>
+        <v>98615</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129213773</v>
       </c>
       <c r="B75" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>129213412</v>
       </c>
       <c r="B78" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>129212656</v>
       </c>
       <c r="B83" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11651,52 +11651,38 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129211354</v>
+        <v>129214590</v>
       </c>
       <c r="B92" t="n">
-        <v>98712</v>
+        <v>99050</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11705,13 +11691,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488586</v>
+        <v>488566</v>
       </c>
       <c r="R92" t="n">
-        <v>7014612</v>
+        <v>7014423</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11740,7 +11726,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11750,12 +11736,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11787,38 +11768,52 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129213105</v>
+        <v>129211354</v>
       </c>
       <c r="B93" t="n">
-        <v>100901</v>
+        <v>98716</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11827,13 +11822,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488627</v>
+        <v>488586</v>
       </c>
       <c r="R93" t="n">
-        <v>7014454</v>
+        <v>7014612</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11862,7 +11857,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11872,7 +11867,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11904,10 +11904,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129214590</v>
+        <v>129213105</v>
       </c>
       <c r="B94" t="n">
-        <v>99046</v>
+        <v>100905</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11915,27 +11915,27 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11944,10 +11944,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488566</v>
+        <v>488627</v>
       </c>
       <c r="R94" t="n">
-        <v>7014423</v>
+        <v>7014454</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12024,7 +12024,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>129214807</v>
       </c>
       <c r="B98" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>129210843</v>
       </c>
       <c r="B99" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13183,53 +13183,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129212827</v>
+        <v>129213534</v>
       </c>
       <c r="B104" t="n">
-        <v>91998</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488535</v>
+        <v>488675</v>
       </c>
       <c r="R104" t="n">
-        <v>7014455</v>
+        <v>7014494</v>
       </c>
       <c r="S104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13258,7 +13253,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13268,7 +13263,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13297,12 +13292,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13320,48 +13315,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129213534</v>
+        <v>129212827</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>92002</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488675</v>
+        <v>488535</v>
       </c>
       <c r="R105" t="n">
-        <v>7014494</v>
+        <v>7014455</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13452,38 +13452,43 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129209238</v>
+        <v>129213886</v>
       </c>
       <c r="B106" t="n">
-        <v>100901</v>
+        <v>57727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -13492,13 +13497,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488489</v>
+        <v>488671</v>
       </c>
       <c r="R106" t="n">
-        <v>7014656</v>
+        <v>7014435</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13527,7 +13532,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13537,7 +13542,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13552,6 +13562,26 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -13569,43 +13599,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129213886</v>
+        <v>129209238</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>100905</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -13614,13 +13639,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488671</v>
+        <v>488489</v>
       </c>
       <c r="R107" t="n">
-        <v>7014435</v>
+        <v>7014656</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13649,7 +13674,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13659,12 +13684,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13679,26 +13699,6 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -13716,67 +13716,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129214838</v>
+        <v>129213440</v>
       </c>
       <c r="B108" t="n">
-        <v>98616</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488552</v>
+        <v>488638</v>
       </c>
       <c r="R108" t="n">
-        <v>7014410</v>
+        <v>7014529</v>
       </c>
       <c r="S108" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13805,7 +13786,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13815,12 +13796,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>1 planta med fröställning.</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13835,6 +13811,26 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13852,48 +13848,67 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129213440</v>
+        <v>129214838</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>98620</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488638</v>
+        <v>488552</v>
       </c>
       <c r="R109" t="n">
-        <v>7014529</v>
+        <v>7014410</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13922,7 +13937,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13932,7 +13947,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>1 planta med fröställning.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13947,26 +13967,6 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14119,7 +14119,7 @@
         <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14796,45 +14796,64 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129212678</v>
+        <v>129211241</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488572</v>
+        <v>488551</v>
       </c>
       <c r="R116" t="n">
-        <v>7014469</v>
+        <v>7014630</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14866,7 +14885,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14876,7 +14895,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14891,26 +14915,6 @@
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14928,10 +14932,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129211241</v>
+        <v>129211912</v>
       </c>
       <c r="B117" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14958,7 +14962,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14982,10 +14986,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488551</v>
+        <v>488586</v>
       </c>
       <c r="R117" t="n">
-        <v>7014630</v>
+        <v>7014626</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15017,7 +15021,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15027,12 +15031,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15064,64 +15068,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129211912</v>
+        <v>129212678</v>
       </c>
       <c r="B118" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488586</v>
+        <v>488572</v>
       </c>
       <c r="R118" t="n">
-        <v>7014626</v>
+        <v>7014469</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15153,7 +15138,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15163,12 +15148,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15183,6 +15163,26 @@
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15203,7 +15203,7 @@
         <v>129210698</v>
       </c>
       <c r="B119" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>129349154</v>
       </c>
       <c r="B124" t="n">
-        <v>92236</v>
+        <v>92240</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129057988</v>
       </c>
       <c r="B3" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129057987</v>
       </c>
       <c r="B12" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129080431</v>
+        <v>129074673</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488667</v>
+        <v>488470</v>
       </c>
       <c r="R15" t="n">
-        <v>7014453</v>
+        <v>7014593</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129074673</v>
+        <v>129080431</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488470</v>
+        <v>488667</v>
       </c>
       <c r="R16" t="n">
-        <v>7014593</v>
+        <v>7014453</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
@@ -2552,7 +2552,7 @@
         <v>129077751</v>
       </c>
       <c r="B19" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129078715</v>
       </c>
       <c r="B20" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129081134</v>
+        <v>129079151</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,27 +2774,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488567</v>
+        <v>488670</v>
       </c>
       <c r="R21" t="n">
-        <v>7014534</v>
+        <v>7014411</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129079151</v>
+        <v>129081134</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,27 +2906,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488670</v>
+        <v>488567</v>
       </c>
       <c r="R22" t="n">
-        <v>7014411</v>
+        <v>7014534</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,22 +2994,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3289,7 +3289,7 @@
         <v>129071736</v>
       </c>
       <c r="B25" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>129075203</v>
       </c>
       <c r="B26" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129077703</v>
       </c>
       <c r="B27" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129078582</v>
       </c>
       <c r="B28" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129081091</v>
+        <v>129080078</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,42 +3917,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488575</v>
+        <v>488760</v>
       </c>
       <c r="R30" t="n">
-        <v>7014525</v>
+        <v>7014511</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3984,11 +3979,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4005,22 +3995,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4160,10 +4150,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129080078</v>
+        <v>129071599</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4171,37 +4161,56 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488760</v>
+        <v>488409</v>
       </c>
       <c r="R32" t="n">
-        <v>7014511</v>
+        <v>7014470</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4228,11 +4237,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4245,26 +4269,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4282,67 +4286,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129071599</v>
+        <v>129078041</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>99058</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488409</v>
+        <v>488550</v>
       </c>
       <c r="R33" t="n">
-        <v>7014470</v>
+        <v>7014460</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4369,24 +4359,9 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4418,10 +4393,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129078041</v>
+        <v>129076105</v>
       </c>
       <c r="B34" t="n">
-        <v>99050</v>
+        <v>100913</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4429,27 +4404,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4458,13 +4433,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488550</v>
+        <v>488531</v>
       </c>
       <c r="R34" t="n">
-        <v>7014460</v>
+        <v>7014566</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4525,10 +4500,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129076105</v>
+        <v>129073989</v>
       </c>
       <c r="B35" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4565,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488531</v>
+        <v>488436</v>
       </c>
       <c r="R35" t="n">
-        <v>7014566</v>
+        <v>7014587</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4632,10 +4607,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129073989</v>
+        <v>129081210</v>
       </c>
       <c r="B36" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4672,13 +4647,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488436</v>
+        <v>488580</v>
       </c>
       <c r="R36" t="n">
-        <v>7014587</v>
+        <v>7014585</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4739,10 +4714,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129081210</v>
+        <v>129074467</v>
       </c>
       <c r="B37" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4779,13 +4754,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488580</v>
+        <v>488447</v>
       </c>
       <c r="R37" t="n">
-        <v>7014585</v>
+        <v>7014717</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4846,38 +4821,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129074467</v>
+        <v>129081091</v>
       </c>
       <c r="B38" t="n">
-        <v>100905</v>
+        <v>80150</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4886,13 +4861,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488447</v>
+        <v>488575</v>
       </c>
       <c r="R38" t="n">
-        <v>7014717</v>
+        <v>7014525</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4924,6 +4899,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4936,6 +4916,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4953,48 +4953,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129072614</v>
+        <v>129074733</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>100913</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488504</v>
+        <v>488496</v>
       </c>
       <c r="R39" t="n">
-        <v>7014520</v>
+        <v>7014610</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5026,11 +5031,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5043,26 +5043,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5080,7 +5060,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129072008</v>
+        <v>129072614</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -5115,13 +5095,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488442</v>
+        <v>488504</v>
       </c>
       <c r="R40" t="n">
-        <v>7014464</v>
+        <v>7014520</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5151,6 +5131,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5202,10 +5187,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129072477</v>
+        <v>129072008</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5213,42 +5198,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488495</v>
+        <v>488442</v>
       </c>
       <c r="R41" t="n">
-        <v>7014499</v>
+        <v>7014464</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5280,11 +5260,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5286,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5334,38 +5309,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129074733</v>
+        <v>129072477</v>
       </c>
       <c r="B42" t="n">
-        <v>100905</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5374,13 +5349,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488496</v>
+        <v>488495</v>
       </c>
       <c r="R42" t="n">
-        <v>7014610</v>
+        <v>7014499</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5412,6 +5387,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5424,6 +5404,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129076936</v>
+        <v>129076722</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5476,13 +5476,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488552</v>
+        <v>488602</v>
       </c>
       <c r="R43" t="n">
-        <v>7014587</v>
+        <v>7014595</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129076722</v>
+        <v>129076936</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488602</v>
+        <v>488552</v>
       </c>
       <c r="R44" t="n">
-        <v>7014595</v>
+        <v>7014587</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129073539</v>
       </c>
       <c r="B45" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5792,10 +5792,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080537</v>
+        <v>129076866</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5803,37 +5803,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488632</v>
+        <v>488575</v>
       </c>
       <c r="R46" t="n">
-        <v>7014478</v>
+        <v>7014596</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5867,7 +5872,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om liggande död ved på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5896,12 +5901,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5919,7 +5924,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129072070</v>
+        <v>129080537</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5954,10 +5959,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488455</v>
+        <v>488632</v>
       </c>
       <c r="R47" t="n">
-        <v>7014457</v>
+        <v>7014478</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5990,6 +5995,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6041,10 +6051,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129076866</v>
+        <v>129072070</v>
       </c>
       <c r="B48" t="n">
-        <v>91847</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6052,42 +6062,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488575</v>
+        <v>488455</v>
       </c>
       <c r="R48" t="n">
-        <v>7014596</v>
+        <v>7014457</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6119,11 +6124,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6176,7 +6176,7 @@
         <v>129077994</v>
       </c>
       <c r="B49" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6280,53 +6280,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129081155</v>
+        <v>129070117</v>
       </c>
       <c r="B50" t="n">
-        <v>80185</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488569</v>
+        <v>488317</v>
       </c>
       <c r="R50" t="n">
-        <v>7014529</v>
+        <v>7014450</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6353,14 +6348,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
+          <t>I gammal granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6379,22 +6384,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6412,43 +6417,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129079479</v>
+        <v>129081155</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80185</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6457,13 +6457,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488806</v>
+        <v>488569</v>
       </c>
       <c r="R51" t="n">
-        <v>7014416</v>
+        <v>7014529</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6516,22 +6516,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129070117</v>
+        <v>129079479</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6560,34 +6560,44 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488317</v>
+        <v>488806</v>
       </c>
       <c r="R52" t="n">
-        <v>7014450</v>
+        <v>7014416</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6617,24 +6627,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6689,7 +6689,7 @@
         <v>129072360</v>
       </c>
       <c r="B53" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>129071923</v>
       </c>
       <c r="B54" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>129071884</v>
       </c>
       <c r="B55" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>129077981</v>
       </c>
       <c r="B56" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7183,53 +7183,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B57" t="n">
-        <v>92267</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R57" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7287,12 +7282,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7310,48 +7305,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>92268</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R58" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129073198</v>
+        <v>129073935</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7443,47 +7443,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488422</v>
+        <v>488409</v>
       </c>
       <c r="R59" t="n">
-        <v>7014530</v>
+        <v>7014521</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7515,11 +7505,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7534,14 +7519,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7559,10 +7554,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129073935</v>
+        <v>129073198</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7570,37 +7565,47 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488409</v>
+        <v>488422</v>
       </c>
       <c r="R60" t="n">
-        <v>7014521</v>
+        <v>7014530</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7632,6 +7637,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7646,24 +7656,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7684,7 +7684,7 @@
         <v>129070439</v>
       </c>
       <c r="B61" t="n">
-        <v>103239</v>
+        <v>103249</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129074640</v>
+        <v>129073694</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488472</v>
+        <v>488426</v>
       </c>
       <c r="R63" t="n">
-        <v>7014599</v>
+        <v>7014494</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8008,11 +8008,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8025,26 +8020,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8062,43 +8037,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129078537</v>
+        <v>129072652</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8107,13 +8077,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488573</v>
+        <v>488514</v>
       </c>
       <c r="R64" t="n">
-        <v>7014399</v>
+        <v>7014547</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8145,11 +8115,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8162,26 +8127,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8199,38 +8144,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129079063</v>
+        <v>129078147</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>103249</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8239,13 +8184,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488655</v>
+        <v>488557</v>
       </c>
       <c r="R65" t="n">
-        <v>7014417</v>
+        <v>7014445</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8272,14 +8217,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8294,26 +8244,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8331,38 +8261,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129073694</v>
+        <v>129079063</v>
       </c>
       <c r="B66" t="n">
-        <v>100905</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8371,10 +8301,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488426</v>
+        <v>488655</v>
       </c>
       <c r="R66" t="n">
-        <v>7014494</v>
+        <v>7014417</v>
       </c>
       <c r="S66" t="n">
         <v>11</v>
@@ -8409,6 +8339,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8421,6 +8356,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8438,38 +8393,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129072652</v>
+        <v>129074640</v>
       </c>
       <c r="B67" t="n">
-        <v>100905</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8478,13 +8433,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488514</v>
+        <v>488472</v>
       </c>
       <c r="R67" t="n">
-        <v>7014547</v>
+        <v>7014599</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8516,6 +8471,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8528,6 +8488,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8545,38 +8525,43 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129078147</v>
+        <v>129078537</v>
       </c>
       <c r="B68" t="n">
-        <v>103239</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8585,13 +8570,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488557</v>
+        <v>488573</v>
       </c>
       <c r="R68" t="n">
-        <v>7014445</v>
+        <v>7014399</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8618,19 +8603,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8645,6 +8625,26 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8797,7 +8797,7 @@
         <v>129077294</v>
       </c>
       <c r="B70" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>129073064</v>
       </c>
       <c r="B71" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>129189282</v>
       </c>
       <c r="B72" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>129074868</v>
       </c>
       <c r="B74" t="n">
-        <v>98615</v>
+        <v>98623</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9442,53 +9442,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129213773</v>
+        <v>129215411</v>
       </c>
       <c r="B75" t="n">
-        <v>92002</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488662</v>
+        <v>488525</v>
       </c>
       <c r="R75" t="n">
-        <v>7014466</v>
+        <v>7014363</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9517,7 +9512,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9527,7 +9522,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9579,48 +9579,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215411</v>
+        <v>129213773</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>92003</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488525</v>
+        <v>488662</v>
       </c>
       <c r="R76" t="n">
-        <v>7014363</v>
+        <v>7014466</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9649,7 +9654,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9659,12 +9664,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9866,7 +9866,7 @@
         <v>129213412</v>
       </c>
       <c r="B78" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>129215202</v>
       </c>
       <c r="B79" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>129212656</v>
       </c>
       <c r="B83" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>129211429</v>
       </c>
       <c r="B84" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11294,10 +11294,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129209204</v>
+        <v>129215229</v>
       </c>
       <c r="B89" t="n">
-        <v>91569</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11305,38 +11305,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488495</v>
+        <v>488501</v>
       </c>
       <c r="R89" t="n">
-        <v>7014661</v>
+        <v>7014416</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11365,7 +11364,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11375,7 +11374,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11390,26 +11389,6 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11427,7 +11406,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215229</v>
+        <v>129215504</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -11462,13 +11441,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488501</v>
+        <v>488457</v>
       </c>
       <c r="R90" t="n">
-        <v>7014416</v>
+        <v>7014436</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11497,7 +11476,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11507,7 +11486,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11539,48 +11518,53 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215504</v>
+        <v>129214590</v>
       </c>
       <c r="B91" t="n">
-        <v>79044</v>
+        <v>99058</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488457</v>
+        <v>488566</v>
       </c>
       <c r="R91" t="n">
-        <v>7014436</v>
+        <v>7014423</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11609,7 +11593,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11619,7 +11603,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11651,10 +11635,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129214590</v>
+        <v>129213105</v>
       </c>
       <c r="B92" t="n">
-        <v>99050</v>
+        <v>100913</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11662,27 +11646,27 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11691,10 +11675,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488566</v>
+        <v>488627</v>
       </c>
       <c r="R92" t="n">
-        <v>7014423</v>
+        <v>7014454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11726,7 +11710,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11736,7 +11720,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11771,7 +11755,7 @@
         <v>129211354</v>
       </c>
       <c r="B93" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11904,38 +11888,34 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129213105</v>
+        <v>129209204</v>
       </c>
       <c r="B94" t="n">
-        <v>100905</v>
+        <v>91570</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11944,10 +11924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488627</v>
+        <v>488495</v>
       </c>
       <c r="R94" t="n">
-        <v>7014454</v>
+        <v>7014661</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11979,7 +11959,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11989,7 +11969,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12004,6 +11984,26 @@
       <c r="AH94" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12024,7 +12024,7 @@
         <v>129215435</v>
       </c>
       <c r="B95" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>129215050</v>
       </c>
       <c r="B96" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12386,64 +12386,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129214807</v>
+        <v>129210843</v>
       </c>
       <c r="B98" t="n">
-        <v>98716</v>
+        <v>100913</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488555</v>
+        <v>488496</v>
       </c>
       <c r="R98" t="n">
-        <v>7014416</v>
+        <v>7014638</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12475,7 +12461,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12485,12 +12471,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12522,50 +12503,64 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129210843</v>
+        <v>129214807</v>
       </c>
       <c r="B99" t="n">
-        <v>100905</v>
+        <v>98724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488496</v>
+        <v>488555</v>
       </c>
       <c r="R99" t="n">
-        <v>7014638</v>
+        <v>7014416</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -12597,7 +12592,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12607,7 +12602,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12642,7 +12642,7 @@
         <v>129211064</v>
       </c>
       <c r="B100" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>129214278</v>
       </c>
       <c r="B101" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>129210160</v>
       </c>
       <c r="B102" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>129209724</v>
       </c>
       <c r="B103" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13183,48 +13183,53 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129213534</v>
+        <v>129212827</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>92003</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488675</v>
+        <v>488535</v>
       </c>
       <c r="R104" t="n">
-        <v>7014494</v>
+        <v>7014455</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13253,7 +13258,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13263,7 +13268,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13292,12 +13297,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13315,53 +13320,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129212827</v>
+        <v>129213534</v>
       </c>
       <c r="B105" t="n">
-        <v>92002</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488535</v>
+        <v>488675</v>
       </c>
       <c r="R105" t="n">
-        <v>7014455</v>
+        <v>7014494</v>
       </c>
       <c r="S105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13602,7 +13602,7 @@
         <v>129209238</v>
       </c>
       <c r="B107" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>129214838</v>
       </c>
       <c r="B109" t="n">
-        <v>98620</v>
+        <v>98628</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>129215256</v>
       </c>
       <c r="B111" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14400,38 +14400,43 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129214896</v>
+        <v>129214819</v>
       </c>
       <c r="B113" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14440,13 +14445,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488525</v>
+        <v>488543</v>
       </c>
       <c r="R113" t="n">
-        <v>7014424</v>
+        <v>7014418</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14475,7 +14480,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14485,12 +14490,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14505,26 +14505,6 @@
       <c r="AH113" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14542,43 +14522,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B114" t="n">
-        <v>100905</v>
+        <v>57727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14587,13 +14562,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R114" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14622,7 +14597,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14632,7 +14607,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14647,6 +14627,26 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14799,7 +14799,7 @@
         <v>129211241</v>
       </c>
       <c r="B116" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>129211912</v>
       </c>
       <c r="B117" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>129210698</v>
       </c>
       <c r="B119" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>129349154</v>
       </c>
       <c r="B124" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129076254</v>
+        <v>129074228</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,37 +1920,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488581</v>
+        <v>488431</v>
       </c>
       <c r="R14" t="n">
-        <v>7014597</v>
+        <v>7014633</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,14 +1987,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,22 +2023,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>idegran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Taxus baccata</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Taxus baccata</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2158,7 +2178,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129080431</v>
+        <v>129079967</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2193,13 +2213,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488667</v>
+        <v>488745</v>
       </c>
       <c r="R16" t="n">
-        <v>7014453</v>
+        <v>7014497</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079967</v>
+        <v>129076254</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2315,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488745</v>
+        <v>488581</v>
       </c>
       <c r="R17" t="n">
-        <v>7014497</v>
+        <v>7014597</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2353,6 +2373,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2369,12 +2394,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -2384,7 +2409,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2402,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129074228</v>
+        <v>129080431</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,47 +2438,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488431</v>
+        <v>488667</v>
       </c>
       <c r="R18" t="n">
-        <v>7014633</v>
+        <v>7014453</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2480,26 +2495,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129079151</v>
+        <v>129081134</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,27 +2774,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488670</v>
+        <v>488567</v>
       </c>
       <c r="R21" t="n">
-        <v>7014411</v>
+        <v>7014534</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
+          <t>På en relativt nyligen nedfallen asp.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129081134</v>
+        <v>129079151</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,27 +2906,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488567</v>
+        <v>488670</v>
       </c>
       <c r="R22" t="n">
-        <v>7014534</v>
+        <v>7014411</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
+          <t>Ringhack, äldre, på en gran som är naturvårdsnitslad.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,22 +2994,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3149,43 +3149,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129072249</v>
+        <v>129071736</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3194,13 +3189,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488459</v>
+        <v>488410</v>
       </c>
       <c r="R24" t="n">
-        <v>7014467</v>
+        <v>7014448</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,11 +3227,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3249,26 +3239,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3286,7 +3256,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129071736</v>
+        <v>129075203</v>
       </c>
       <c r="B25" t="n">
         <v>100913</v>
@@ -3326,13 +3296,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488410</v>
+        <v>488533</v>
       </c>
       <c r="R25" t="n">
-        <v>7014448</v>
+        <v>7014663</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3393,38 +3363,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129075203</v>
+        <v>129072249</v>
       </c>
       <c r="B26" t="n">
-        <v>100913</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3433,13 +3408,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488533</v>
+        <v>488459</v>
       </c>
       <c r="R26" t="n">
-        <v>7014663</v>
+        <v>7014467</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3471,6 +3446,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3483,6 +3463,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129080078</v>
+        <v>129081091</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,37 +3917,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488760</v>
+        <v>488575</v>
       </c>
       <c r="R30" t="n">
-        <v>7014511</v>
+        <v>7014525</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3979,6 +3984,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en relativt nyligen nedfallen asp.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3995,22 +4005,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4028,10 +4038,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129079878</v>
+        <v>129071599</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,37 +4049,56 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488787</v>
+        <v>488409</v>
       </c>
       <c r="R31" t="n">
-        <v>7014483</v>
+        <v>7014470</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4096,11 +4125,26 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4113,26 +4157,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4150,10 +4174,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129071599</v>
+        <v>129079878</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4161,56 +4185,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488409</v>
+        <v>488787</v>
       </c>
       <c r="R32" t="n">
-        <v>7014470</v>
+        <v>7014483</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4237,26 +4242,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>En hona sågs födosöka i gammal granskog med volym av stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett på platsen.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4269,6 +4259,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4286,53 +4296,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129078041</v>
+        <v>129080078</v>
       </c>
       <c r="B33" t="n">
-        <v>99058</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488550</v>
+        <v>488760</v>
       </c>
       <c r="R33" t="n">
-        <v>7014460</v>
+        <v>7014511</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4376,6 +4381,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4393,10 +4418,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129076105</v>
+        <v>129078041</v>
       </c>
       <c r="B34" t="n">
-        <v>100913</v>
+        <v>99058</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4404,27 +4429,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4433,13 +4458,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488531</v>
+        <v>488550</v>
       </c>
       <c r="R34" t="n">
-        <v>7014566</v>
+        <v>7014460</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4500,7 +4525,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129073989</v>
+        <v>129076105</v>
       </c>
       <c r="B35" t="n">
         <v>100913</v>
@@ -4540,13 +4565,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488436</v>
+        <v>488531</v>
       </c>
       <c r="R35" t="n">
-        <v>7014587</v>
+        <v>7014566</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4607,7 +4632,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129081210</v>
+        <v>129073989</v>
       </c>
       <c r="B36" t="n">
         <v>100913</v>
@@ -4647,13 +4672,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488580</v>
+        <v>488436</v>
       </c>
       <c r="R36" t="n">
-        <v>7014585</v>
+        <v>7014587</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4714,7 +4739,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129074467</v>
+        <v>129081210</v>
       </c>
       <c r="B37" t="n">
         <v>100913</v>
@@ -4754,13 +4779,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488447</v>
+        <v>488580</v>
       </c>
       <c r="R37" t="n">
-        <v>7014717</v>
+        <v>7014585</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4821,38 +4846,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129081091</v>
+        <v>129074467</v>
       </c>
       <c r="B38" t="n">
-        <v>80150</v>
+        <v>100913</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4861,13 +4886,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488575</v>
+        <v>488447</v>
       </c>
       <c r="R38" t="n">
-        <v>7014525</v>
+        <v>7014717</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4899,11 +4924,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På en relativt nyligen nedfallen asp.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4916,26 +4936,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4953,53 +4953,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129074733</v>
+        <v>129072614</v>
       </c>
       <c r="B39" t="n">
-        <v>100913</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488496</v>
+        <v>488504</v>
       </c>
       <c r="R39" t="n">
-        <v>7014610</v>
+        <v>7014520</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5031,6 +5026,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5043,6 +5043,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5060,7 +5080,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129072614</v>
+        <v>129072008</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -5095,13 +5115,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488504</v>
+        <v>488442</v>
       </c>
       <c r="R40" t="n">
-        <v>7014520</v>
+        <v>7014464</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5131,11 +5151,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5187,48 +5202,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129072008</v>
+        <v>129074733</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>100913</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488442</v>
+        <v>488496</v>
       </c>
       <c r="R41" t="n">
-        <v>7014464</v>
+        <v>7014610</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5272,26 +5292,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129070117</v>
+        <v>129079479</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6291,34 +6291,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488317</v>
+        <v>488806</v>
       </c>
       <c r="R50" t="n">
-        <v>7014450</v>
+        <v>7014416</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -6348,24 +6358,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>I gammal granskog med gott om död ved.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6417,53 +6417,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129081155</v>
+        <v>129070117</v>
       </c>
       <c r="B51" t="n">
-        <v>80185</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488569</v>
+        <v>488317</v>
       </c>
       <c r="R51" t="n">
-        <v>7014529</v>
+        <v>7014450</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6490,14 +6485,24 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På en relativt nyligen nedfallen grov asp.</t>
+          <t>I gammal granskog med gott om död ved.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6516,22 +6521,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6549,43 +6554,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129079479</v>
+        <v>129081155</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80185</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6594,13 +6594,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488806</v>
+        <v>488569</v>
       </c>
       <c r="R52" t="n">
-        <v>7014416</v>
+        <v>7014529</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran som står inbäddad bland andra granar.</t>
+          <t>På en relativt nyligen nedfallen grov asp.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6653,22 +6653,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6793,32 +6793,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129071923</v>
+        <v>129071884</v>
       </c>
       <c r="B54" t="n">
-        <v>92003</v>
+        <v>91848</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488400</v>
+        <v>488391</v>
       </c>
       <c r="R54" t="n">
-        <v>7014435</v>
+        <v>7014430</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
@@ -6869,6 +6869,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6920,32 +6925,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129071884</v>
+        <v>129071923</v>
       </c>
       <c r="B55" t="n">
-        <v>91848</v>
+        <v>92003</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6960,10 +6965,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488391</v>
+        <v>488400</v>
       </c>
       <c r="R55" t="n">
-        <v>7014430</v>
+        <v>7014435</v>
       </c>
       <c r="S55" t="n">
         <v>7</v>
@@ -6996,11 +7001,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granlåga. På fyndplatsen finns gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7183,48 +7183,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129076063</v>
+        <v>129074080</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>92268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488532</v>
+        <v>488394</v>
       </c>
       <c r="R57" t="n">
-        <v>7014618</v>
+        <v>7014593</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7282,12 +7287,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7305,53 +7310,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129074080</v>
+        <v>129076063</v>
       </c>
       <c r="B58" t="n">
-        <v>92268</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488394</v>
+        <v>488532</v>
       </c>
       <c r="R58" t="n">
-        <v>7014593</v>
+        <v>7014618</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7930,38 +7930,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129073694</v>
+        <v>129074640</v>
       </c>
       <c r="B63" t="n">
-        <v>100913</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488426</v>
+        <v>488472</v>
       </c>
       <c r="R63" t="n">
-        <v>7014494</v>
+        <v>7014599</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8008,6 +8008,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8020,6 +8025,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8037,38 +8062,43 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129072652</v>
+        <v>129078537</v>
       </c>
       <c r="B64" t="n">
-        <v>100913</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8077,13 +8107,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488514</v>
+        <v>488573</v>
       </c>
       <c r="R64" t="n">
-        <v>7014547</v>
+        <v>7014399</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8115,6 +8145,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8127,6 +8162,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8144,38 +8199,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129078147</v>
+        <v>129079063</v>
       </c>
       <c r="B65" t="n">
-        <v>103249</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222002</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8184,13 +8239,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488557</v>
+        <v>488655</v>
       </c>
       <c r="R65" t="n">
-        <v>7014445</v>
+        <v>7014417</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8217,19 +8272,14 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8244,6 +8294,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8261,38 +8331,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129079063</v>
+        <v>129073694</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8301,10 +8371,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488655</v>
+        <v>488426</v>
       </c>
       <c r="R66" t="n">
-        <v>7014417</v>
+        <v>7014494</v>
       </c>
       <c r="S66" t="n">
         <v>11</v>
@@ -8339,11 +8409,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran som är naturvårdnitslad.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8356,26 +8421,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8393,38 +8438,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129074640</v>
+        <v>129072652</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8433,13 +8478,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488472</v>
+        <v>488514</v>
       </c>
       <c r="R67" t="n">
-        <v>7014599</v>
+        <v>7014547</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8471,11 +8516,6 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8488,26 +8528,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8525,43 +8545,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129078537</v>
+        <v>129078147</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>103249</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8570,13 +8585,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488573</v>
+        <v>488557</v>
       </c>
       <c r="R68" t="n">
-        <v>7014399</v>
+        <v>7014445</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8603,14 +8618,19 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8625,26 +8645,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9442,48 +9442,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215411</v>
+        <v>129213773</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>92003</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488525</v>
+        <v>488662</v>
       </c>
       <c r="R75" t="n">
-        <v>7014363</v>
+        <v>7014466</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9512,7 +9517,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9522,12 +9527,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På en högväxt stående död gran.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9579,53 +9579,58 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129213773</v>
+        <v>129210501</v>
       </c>
       <c r="B76" t="n">
-        <v>92003</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488662</v>
+        <v>488472</v>
       </c>
       <c r="R76" t="n">
-        <v>7014466</v>
+        <v>7014695</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9654,7 +9659,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9664,7 +9669,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9693,12 +9703,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9716,10 +9726,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129210501</v>
+        <v>129215411</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9727,47 +9737,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488472</v>
+        <v>488525</v>
       </c>
       <c r="R77" t="n">
-        <v>7014695</v>
+        <v>7014363</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På en högväxt stående död gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129212598</v>
+        <v>129214932</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10147,37 +10147,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488580</v>
+        <v>488526</v>
       </c>
       <c r="R80" t="n">
-        <v>7014484</v>
+        <v>7014439</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10206,7 +10211,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10216,12 +10221,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10250,12 +10255,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10273,7 +10278,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129211802</v>
+        <v>129212598</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -10308,13 +10313,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488591</v>
+        <v>488580</v>
       </c>
       <c r="R81" t="n">
-        <v>7014632</v>
+        <v>7014484</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10343,7 +10348,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10353,7 +10358,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Växer här på en död smal gran med troliga födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10382,12 +10392,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10405,10 +10415,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129214932</v>
+        <v>129211802</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10416,42 +10426,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488526</v>
+        <v>488591</v>
       </c>
       <c r="R82" t="n">
-        <v>7014439</v>
+        <v>7014632</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10480,7 +10485,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10490,12 +10495,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10524,12 +10524,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11294,10 +11294,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215229</v>
+        <v>129209204</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11305,37 +11305,38 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488501</v>
+        <v>488495</v>
       </c>
       <c r="R89" t="n">
-        <v>7014416</v>
+        <v>7014661</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11364,7 +11365,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11374,7 +11375,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11389,6 +11390,26 @@
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11518,10 +11539,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129214590</v>
+        <v>129213105</v>
       </c>
       <c r="B91" t="n">
-        <v>99058</v>
+        <v>100913</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11529,27 +11550,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11558,10 +11579,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488566</v>
+        <v>488627</v>
       </c>
       <c r="R91" t="n">
-        <v>7014423</v>
+        <v>7014454</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11593,7 +11614,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11603,7 +11624,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11635,53 +11656,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129213105</v>
+        <v>129215229</v>
       </c>
       <c r="B92" t="n">
-        <v>100913</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488627</v>
+        <v>488501</v>
       </c>
       <c r="R92" t="n">
-        <v>7014454</v>
+        <v>7014416</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11710,7 +11726,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11720,7 +11736,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11752,52 +11768,38 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129211354</v>
+        <v>129214590</v>
       </c>
       <c r="B93" t="n">
-        <v>98724</v>
+        <v>99058</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11806,13 +11808,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488586</v>
+        <v>488566</v>
       </c>
       <c r="R93" t="n">
-        <v>7014612</v>
+        <v>7014423</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11841,7 +11843,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11851,12 +11853,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11888,34 +11885,52 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129209204</v>
+        <v>129211354</v>
       </c>
       <c r="B94" t="n">
-        <v>91570</v>
+        <v>98724</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11924,13 +11939,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488495</v>
+        <v>488586</v>
       </c>
       <c r="R94" t="n">
-        <v>7014661</v>
+        <v>7014612</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11959,7 +11974,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11969,7 +11984,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 fröställning inom ca 2 m2 yta under några smågranar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11984,26 +12004,6 @@
       <c r="AH94" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12386,50 +12386,64 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129210843</v>
+        <v>129214807</v>
       </c>
       <c r="B98" t="n">
-        <v>100913</v>
+        <v>98724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488496</v>
+        <v>488555</v>
       </c>
       <c r="R98" t="n">
-        <v>7014638</v>
+        <v>7014416</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -12461,7 +12475,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12471,7 +12485,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12503,64 +12522,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129214807</v>
+        <v>129210843</v>
       </c>
       <c r="B99" t="n">
-        <v>98724</v>
+        <v>100913</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488555</v>
+        <v>488496</v>
       </c>
       <c r="R99" t="n">
-        <v>7014416</v>
+        <v>7014638</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -12592,7 +12597,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12602,12 +12607,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:57</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 2 x 0,5 m2 yta.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -14400,43 +14400,38 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129214819</v>
+        <v>129214896</v>
       </c>
       <c r="B113" t="n">
-        <v>100913</v>
+        <v>57727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14445,13 +14440,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488543</v>
+        <v>488525</v>
       </c>
       <c r="R113" t="n">
-        <v>7014418</v>
+        <v>7014424</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14480,7 +14475,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14490,7 +14485,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14505,6 +14505,26 @@
       <c r="AH113" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14522,38 +14542,43 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129214896</v>
+        <v>129214819</v>
       </c>
       <c r="B114" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -14562,13 +14587,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488525</v>
+        <v>488543</v>
       </c>
       <c r="R114" t="n">
-        <v>7014424</v>
+        <v>7014418</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14597,7 +14622,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14607,12 +14632,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14627,26 +14647,6 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14796,64 +14796,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129211241</v>
+        <v>129212678</v>
       </c>
       <c r="B116" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488551</v>
+        <v>488572</v>
       </c>
       <c r="R116" t="n">
-        <v>7014630</v>
+        <v>7014469</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14885,7 +14866,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14895,12 +14876,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14915,6 +14891,26 @@
       <c r="AH116" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -14932,7 +14928,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129211912</v>
+        <v>129211241</v>
       </c>
       <c r="B117" t="n">
         <v>98724</v>
@@ -14962,7 +14958,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14986,10 +14982,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488586</v>
+        <v>488551</v>
       </c>
       <c r="R117" t="n">
-        <v>7014626</v>
+        <v>7014630</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15021,7 +15017,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15031,12 +15027,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
+          <t>Minst 20 plantor och 1 fröställning inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15068,45 +15064,64 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129212678</v>
+        <v>129211912</v>
       </c>
       <c r="B118" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488572</v>
+        <v>488586</v>
       </c>
       <c r="R118" t="n">
-        <v>7014469</v>
+        <v>7014626</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15138,7 +15153,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15148,7 +15163,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15163,26 +15183,6 @@
       <c r="AH118" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15200,38 +15200,38 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129210698</v>
+        <v>129214468</v>
       </c>
       <c r="B119" t="n">
-        <v>92505</v>
+        <v>57727</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -15240,13 +15240,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488475</v>
+        <v>488595</v>
       </c>
       <c r="R119" t="n">
-        <v>7014707</v>
+        <v>7014471</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15285,7 +15285,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15300,6 +15305,26 @@
       <c r="AH119" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15317,48 +15342,53 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129209446</v>
+        <v>129210698</v>
       </c>
       <c r="B120" t="n">
-        <v>79044</v>
+        <v>92505</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488454</v>
+        <v>488475</v>
       </c>
       <c r="R120" t="n">
-        <v>7014635</v>
+        <v>7014707</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15387,7 +15417,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15397,7 +15427,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15412,26 +15442,6 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15449,7 +15459,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129212992</v>
+        <v>129209446</v>
       </c>
       <c r="B121" t="n">
         <v>79044</v>
@@ -15484,10 +15494,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488605</v>
+        <v>488454</v>
       </c>
       <c r="R121" t="n">
-        <v>7014461</v>
+        <v>7014635</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15519,7 +15529,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15529,7 +15539,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15558,12 +15568,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15581,10 +15591,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129214468</v>
+        <v>129212992</v>
       </c>
       <c r="B122" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15592,42 +15602,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488595</v>
+        <v>488605</v>
       </c>
       <c r="R122" t="n">
-        <v>7014471</v>
+        <v>7014461</v>
       </c>
       <c r="S122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15656,7 +15661,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15666,12 +15671,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:46</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15700,12 +15700,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 45985-2025 artfynd.xlsx
+++ b/artfynd/A 45985-2025 artfynd.xlsx
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129074228</v>
+        <v>129074673</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,47 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Kläppe naturreservat, Arontjärnen, Kyrkås, Jmt</t>
+          <t>Väster om Kläppe naturreservat, Väster om Kläppe naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488431</v>
+        <v>488470</v>
       </c>
       <c r="R14" t="n">
-        <v>7014633</v>
+        <v>7014593</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,26 +1977,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2033,12 +2008,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2056,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129074673</v>
+        <v>129079967</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2091,13 +2066,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488470</v>
+        <v>488745</v>
       </c>
       <c r="R15" t="n">
-        <v>7014593</v>
+        <v>7014497</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129079967</v>
+        <v>129076254</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2213,13 +2188,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488745</v>
+        <v>488581</v>
       </c>
       <c r="R16" t="n">
-        <v>7014497</v>
+        <v>7014597</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,6 +2226,11 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2267,12 +2247,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>idegran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Taxus baccata</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -2282,7 +2262,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Taxus baccata</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2300,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1